--- a/research/traditional_assets/database/data/nigeria/nigeria_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_r_e_i_t.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ngse_updcreit" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.11</v>
+        <v>0.0129</v>
+      </c>
+      <c r="E2">
+        <v>0.0335</v>
       </c>
       <c r="G2">
-        <v>0.6255813953488373</v>
+        <v>1.100294985250738</v>
       </c>
       <c r="H2">
-        <v>0.6255813953488373</v>
+        <v>1.100294985250738</v>
       </c>
       <c r="I2">
-        <v>0.4813953488372094</v>
+        <v>0.7218289085545723</v>
       </c>
       <c r="J2">
-        <v>0.4787018855425964</v>
+        <v>0.7159762417284541</v>
       </c>
       <c r="K2">
-        <v>-9.728</v>
+        <v>3.088</v>
       </c>
       <c r="L2">
-        <v>-2.262325581395349</v>
+        <v>0.9109144542772861</v>
       </c>
       <c r="M2">
-        <v>0.842</v>
+        <v>0.521</v>
       </c>
       <c r="N2">
-        <v>0.02528528528528529</v>
+        <v>0.01944029850746269</v>
       </c>
       <c r="O2">
-        <v>-0.08655427631578948</v>
+        <v>0.1687176165803109</v>
       </c>
       <c r="P2">
-        <v>0.842</v>
+        <v>0.521</v>
       </c>
       <c r="Q2">
-        <v>0.02528528528528529</v>
+        <v>0.01944029850746269</v>
       </c>
       <c r="R2">
-        <v>-0.08655427631578948</v>
+        <v>0.1687176165803109</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,67 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8.33</v>
+        <v>5.86</v>
       </c>
       <c r="V2">
-        <v>0.2501501501501502</v>
+        <v>0.2186567164179105</v>
       </c>
       <c r="W2">
-        <v>-0.04677394700295463</v>
+        <v>0.03542087542087542</v>
       </c>
       <c r="X2">
-        <v>0.1267010479484583</v>
+        <v>0.1169294743483429</v>
       </c>
       <c r="Y2">
-        <v>-0.1734749949514129</v>
+        <v>-0.08150859892746747</v>
       </c>
       <c r="Z2">
-        <v>0.04211227327927292</v>
+        <v>0.04430909185967481</v>
       </c>
       <c r="AA2">
-        <v>0.02673470524068559</v>
+        <v>0.03239891242884775</v>
       </c>
       <c r="AB2">
-        <v>0.1266701715298454</v>
+        <v>0.1169167076391843</v>
       </c>
       <c r="AC2">
-        <v>-0.09993546628915984</v>
+        <v>-0.08451779521033659</v>
       </c>
       <c r="AD2">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="AG2">
-        <v>-8.292999999999999</v>
+        <v>-5.838</v>
       </c>
       <c r="AH2">
-        <v>0.001109877913429523</v>
+        <v>0.0008202222056520768</v>
       </c>
       <c r="AI2">
-        <v>0.0004361304619446702</v>
+        <v>0.0004739132307957434</v>
       </c>
       <c r="AJ2">
-        <v>-0.3316271443995681</v>
+        <v>-0.2785039595458449</v>
       </c>
       <c r="AK2">
-        <v>-0.1083953102330506</v>
+        <v>-0.1439278142103447</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN2">
-        <v>0.01644444444444444</v>
+        <v>0.008705975464978234</v>
+      </c>
+      <c r="AO2">
+        <v>815.6666666666666</v>
       </c>
       <c r="AP2">
-        <v>-3.685777777777778</v>
+        <v>-2.310249307479224</v>
+      </c>
+      <c r="AQ2">
+        <v>815.6666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Union Homes Real Estate Investment Trust PLC (NGSE:UHOMREIT)</t>
+          <t>UH Real Estate Investment Trust (NGSE:UHOMREIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,41 +723,47 @@
           <t>R.E.I.T.</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0697</v>
+      </c>
+      <c r="E3">
+        <v>0.109</v>
+      </c>
       <c r="G3">
-        <v>0.7323943661971831</v>
+        <v>1.029411764705882</v>
       </c>
       <c r="H3">
-        <v>0.7323943661971831</v>
+        <v>1.029411764705882</v>
       </c>
       <c r="I3">
-        <v>0.7112676056338029</v>
+        <v>0.7421568627450981</v>
       </c>
       <c r="J3">
-        <v>0.7033083547060593</v>
+        <v>0.7301218865924748</v>
       </c>
       <c r="K3">
-        <v>0.972</v>
+        <v>0.728</v>
       </c>
       <c r="L3">
-        <v>0.6845070422535211</v>
+        <v>0.7137254901960784</v>
       </c>
       <c r="M3">
-        <v>0.842</v>
+        <v>0.521</v>
       </c>
       <c r="N3">
-        <v>0.05467532467532468</v>
+        <v>0.06855263157894738</v>
       </c>
       <c r="O3">
-        <v>0.8662551440329218</v>
+        <v>0.7156593406593407</v>
       </c>
       <c r="P3">
-        <v>0.842</v>
+        <v>0.521</v>
       </c>
       <c r="Q3">
-        <v>0.05467532467532468</v>
+        <v>0.06855263157894738</v>
       </c>
       <c r="R3">
-        <v>0.8662551440329218</v>
+        <v>0.7156593406593407</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,31 +772,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>0.1324675324675325</v>
+        <v>0.2118421052631579</v>
       </c>
       <c r="W3">
-        <v>0.03709923664122138</v>
+        <v>0.03111111111111111</v>
       </c>
       <c r="X3">
-        <v>0.1266375007063272</v>
+        <v>0.1168981537346056</v>
       </c>
       <c r="Y3">
-        <v>-0.0895382640651058</v>
+        <v>-0.08578704262349446</v>
       </c>
       <c r="Z3">
-        <v>0.05643879173290937</v>
+        <v>0.04623753399818677</v>
       </c>
       <c r="AA3">
-        <v>0.03969387375527044</v>
+        <v>0.03375903555413982</v>
       </c>
       <c r="AB3">
-        <v>0.1266375007063272</v>
+        <v>0.1168981537346056</v>
       </c>
       <c r="AC3">
-        <v>-0.08694362695105673</v>
+        <v>-0.08313911818046577</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-2.04</v>
+        <v>-1.61</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1526946107784431</v>
+        <v>-0.2687813021702838</v>
       </c>
       <c r="AK3">
-        <v>-0.09247506799637352</v>
+        <v>-0.141352063213345</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1.961538461538461</v>
+        <v>-2.04574332909784</v>
       </c>
     </row>
     <row r="4">
@@ -835,25 +852,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.11</v>
+        <v>-0.04389999999999999</v>
+      </c>
+      <c r="E4">
+        <v>-0.042</v>
       </c>
       <c r="G4">
-        <v>0.5729166666666666</v>
+        <v>1.130801687763713</v>
       </c>
       <c r="H4">
-        <v>0.5729166666666666</v>
+        <v>1.130801687763713</v>
       </c>
       <c r="I4">
-        <v>0.3680555555555556</v>
+        <v>0.7130801687763713</v>
       </c>
       <c r="J4">
-        <v>0.3680555555555556</v>
+        <v>0.7130801687763713</v>
       </c>
       <c r="K4">
-        <v>-10.7</v>
+        <v>2.36</v>
       </c>
       <c r="L4">
-        <v>-3.715277777777778</v>
+        <v>0.9957805907172995</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,7 +882,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -871,73 +891,8851 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.29</v>
+        <v>4.25</v>
       </c>
       <c r="V4">
-        <v>0.3513966480446928</v>
+        <v>0.2213541666666667</v>
       </c>
       <c r="W4">
-        <v>-0.1306471306471306</v>
+        <v>0.03973063973063973</v>
       </c>
       <c r="X4">
-        <v>0.1267645951905894</v>
+        <v>0.1169607949620802</v>
       </c>
       <c r="Y4">
-        <v>-0.25741172583772</v>
+        <v>-0.07723015523144047</v>
       </c>
       <c r="Z4">
-        <v>0.03742787336902843</v>
+        <v>0.04352776961504556</v>
       </c>
       <c r="AA4">
-        <v>0.01377553672610074</v>
+        <v>0.03103878930355569</v>
       </c>
       <c r="AB4">
-        <v>0.1267028423533637</v>
+        <v>0.1169352615437631</v>
       </c>
       <c r="AC4">
-        <v>-0.1129273056272629</v>
+        <v>-0.08589647224020741</v>
       </c>
       <c r="AD4">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.037</v>
+        <v>0.022</v>
       </c>
       <c r="AG4">
-        <v>-6.253</v>
+        <v>-4.228</v>
       </c>
       <c r="AH4">
-        <v>0.002062775268997045</v>
+        <v>0.001144521901987306</v>
       </c>
       <c r="AI4">
-        <v>0.0006091838582741986</v>
+        <v>0.0006582490575070313</v>
       </c>
       <c r="AJ4">
-        <v>-0.536876448870954</v>
+        <v>-0.2823938017632915</v>
       </c>
       <c r="AK4">
-        <v>-0.1148456296949327</v>
+        <v>-0.1449334978746744</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN4">
-        <v>0.03057851239669421</v>
+        <v>0.01264367816091954</v>
+      </c>
+      <c r="AO4">
+        <v>563.3333333333333</v>
       </c>
       <c r="AP4">
-        <v>-5.167768595041323</v>
+        <v>-2.429885057471264</v>
+      </c>
+      <c r="AQ4">
+        <v>563.3333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>UPDC Real Estate Investment Trust (NGSE:UPDCREIT)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NGSE:UPDCREIT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>R.E.I.T.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>554.333333333333</v>
+      </c>
+      <c r="F2">
+        <v>4.04277808624658</v>
+      </c>
+      <c r="G2">
+        <v>0.0126436781609195</v>
+      </c>
+      <c r="H2">
+        <v>4.41885057471264</v>
+      </c>
+      <c r="I2">
+        <v>0.00114452190198731</v>
+      </c>
+      <c r="J2">
+        <v>0.4</v>
+      </c>
+      <c r="K2">
+        <v>19.2</v>
+      </c>
+      <c r="L2">
+        <v>13.5047621383077</v>
+      </c>
+      <c r="M2">
+        <v>14.972</v>
+      </c>
+      <c r="N2">
+        <v>16.9435621383077</v>
+      </c>
+      <c r="O2">
+        <v>0.022</v>
+      </c>
+      <c r="P2">
+        <v>7.6888</v>
+      </c>
+      <c r="Q2">
+        <v>0.116935261543763</v>
+      </c>
+      <c r="R2">
+        <v>0.106986375286453</v>
+      </c>
+      <c r="S2">
+        <v>0.09465155101248041</v>
+      </c>
+      <c r="T2">
+        <v>0.03745</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.11696079496208</v>
+      </c>
+      <c r="X2">
+        <v>0.153343958810755</v>
+      </c>
+      <c r="Y2">
+        <v>0.502101733146576</v>
+      </c>
+      <c r="Z2">
+        <v>0.735825681766062</v>
+      </c>
+      <c r="AA2">
+        <v>0.022</v>
+      </c>
+      <c r="AB2">
+        <v>0.1352165014464005</v>
+      </c>
+      <c r="AC2">
+        <v>554.3333333333334</v>
+      </c>
+      <c r="AD2">
+        <v>0.022</v>
+      </c>
+      <c r="AE2">
+        <v>0.003</v>
+      </c>
+      <c r="AF2">
+        <v>0.077</v>
+      </c>
+      <c r="AG2">
+        <v>1.74</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>19.2</v>
+      </c>
+      <c r="AK2">
+        <v>0.1556672478946873</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>4.163336342344337e-17</v>
+      </c>
+      <c r="AR2">
+        <v>0.003</v>
+      </c>
+      <c r="AS2">
+        <v>0.022</v>
+      </c>
+      <c r="AT2">
+        <v>4.25</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1168981537346056</v>
+      </c>
+      <c r="C2">
+        <v>19.22850077215115</v>
+      </c>
+      <c r="D2">
+        <v>14.97850077215115</v>
+      </c>
+      <c r="E2">
+        <v>-0.022</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.25</v>
+      </c>
+      <c r="H2">
+        <v>19.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.74</v>
+      </c>
+      <c r="K2">
+        <v>0.077</v>
+      </c>
+      <c r="L2">
+        <v>1.663</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.663</v>
+      </c>
+      <c r="O2">
+        <v>0.4989</v>
+      </c>
+      <c r="P2">
+        <v>1.1641</v>
+      </c>
+      <c r="Q2">
+        <v>1.2411</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1168981537346056</v>
+      </c>
+      <c r="T2">
+        <v>0.5016993284768603</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1165887592734018</v>
+      </c>
+      <c r="C3">
+        <v>19.09070293247054</v>
+      </c>
+      <c r="D3">
+        <v>15.03292293247054</v>
+      </c>
+      <c r="E3">
+        <v>0.17022</v>
+      </c>
+      <c r="F3">
+        <v>0.19222</v>
+      </c>
+      <c r="G3">
+        <v>4.25</v>
+      </c>
+      <c r="H3">
+        <v>19.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.74</v>
+      </c>
+      <c r="K3">
+        <v>0.077</v>
+      </c>
+      <c r="L3">
+        <v>1.663</v>
+      </c>
+      <c r="M3">
+        <v>0.008592233999999999</v>
+      </c>
+      <c r="N3">
+        <v>1.654407766</v>
+      </c>
+      <c r="O3">
+        <v>0.4963223298</v>
+      </c>
+      <c r="P3">
+        <v>1.1580854362</v>
+      </c>
+      <c r="Q3">
+        <v>1.2350854362</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.117450362902426</v>
+      </c>
+      <c r="T3">
+        <v>0.5052466974660905</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>193.5468703482703</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1162793648121979</v>
+      </c>
+      <c r="C4">
+        <v>18.95330200460081</v>
+      </c>
+      <c r="D4">
+        <v>15.08774200460081</v>
+      </c>
+      <c r="E4">
+        <v>0.3624399999999999</v>
+      </c>
+      <c r="F4">
+        <v>0.3844399999999999</v>
+      </c>
+      <c r="G4">
+        <v>4.25</v>
+      </c>
+      <c r="H4">
+        <v>19.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.74</v>
+      </c>
+      <c r="K4">
+        <v>0.077</v>
+      </c>
+      <c r="L4">
+        <v>1.663</v>
+      </c>
+      <c r="M4">
+        <v>0.017184468</v>
+      </c>
+      <c r="N4">
+        <v>1.645815532</v>
+      </c>
+      <c r="O4">
+        <v>0.4937446596</v>
+      </c>
+      <c r="P4">
+        <v>1.1520708724</v>
+      </c>
+      <c r="Q4">
+        <v>1.2290708724</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1180138416450999</v>
+      </c>
+      <c r="T4">
+        <v>0.5088664617408154</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>96.77343517413517</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1159699703509941</v>
+      </c>
+      <c r="C5">
+        <v>18.81630234657101</v>
+      </c>
+      <c r="D5">
+        <v>15.14296234657101</v>
+      </c>
+      <c r="E5">
+        <v>0.5546599999999999</v>
+      </c>
+      <c r="F5">
+        <v>0.57666</v>
+      </c>
+      <c r="G5">
+        <v>4.25</v>
+      </c>
+      <c r="H5">
+        <v>19.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.74</v>
+      </c>
+      <c r="K5">
+        <v>0.077</v>
+      </c>
+      <c r="L5">
+        <v>1.663</v>
+      </c>
+      <c r="M5">
+        <v>0.025776702</v>
+      </c>
+      <c r="N5">
+        <v>1.637223298</v>
+      </c>
+      <c r="O5">
+        <v>0.4911669894</v>
+      </c>
+      <c r="P5">
+        <v>1.1460563086</v>
+      </c>
+      <c r="Q5">
+        <v>1.2230563086</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1185889385061795</v>
+      </c>
+      <c r="T5">
+        <v>0.512560860330483</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>64.51562344942344</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1156605758897903</v>
+      </c>
+      <c r="C6">
+        <v>18.67970838044517</v>
+      </c>
+      <c r="D6">
+        <v>15.19858838044517</v>
+      </c>
+      <c r="E6">
+        <v>0.7468799999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.7688799999999999</v>
+      </c>
+      <c r="G6">
+        <v>4.25</v>
+      </c>
+      <c r="H6">
+        <v>19.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.74</v>
+      </c>
+      <c r="K6">
+        <v>0.077</v>
+      </c>
+      <c r="L6">
+        <v>1.663</v>
+      </c>
+      <c r="M6">
+        <v>0.034368936</v>
+      </c>
+      <c r="N6">
+        <v>1.628631064</v>
+      </c>
+      <c r="O6">
+        <v>0.4885893192</v>
+      </c>
+      <c r="P6">
+        <v>1.1400417448</v>
+      </c>
+      <c r="Q6">
+        <v>1.2170417448</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1191760165518649</v>
+      </c>
+      <c r="T6">
+        <v>0.5163322255574353</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>48.38671758706759</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1153511814285865</v>
+      </c>
+      <c r="C7">
+        <v>18.54352459350278</v>
+      </c>
+      <c r="D7">
+        <v>15.25462459350278</v>
+      </c>
+      <c r="E7">
+        <v>0.9390999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.9611</v>
+      </c>
+      <c r="G7">
+        <v>4.25</v>
+      </c>
+      <c r="H7">
+        <v>19.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.74</v>
+      </c>
+      <c r="K7">
+        <v>0.077</v>
+      </c>
+      <c r="L7">
+        <v>1.663</v>
+      </c>
+      <c r="M7">
+        <v>0.04296117</v>
+      </c>
+      <c r="N7">
+        <v>1.62003883</v>
+      </c>
+      <c r="O7">
+        <v>0.4860116489999999</v>
+      </c>
+      <c r="P7">
+        <v>1.134027181</v>
+      </c>
+      <c r="Q7">
+        <v>1.211027181</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1197754541353542</v>
+      </c>
+      <c r="T7">
+        <v>0.5201829879470603</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>38.70937406965406</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1150417869673827</v>
+      </c>
+      <c r="C8">
+        <v>18.40775553944545</v>
+      </c>
+      <c r="D8">
+        <v>15.31107553944545</v>
+      </c>
+      <c r="E8">
+        <v>1.13132</v>
+      </c>
+      <c r="F8">
+        <v>1.15332</v>
+      </c>
+      <c r="G8">
+        <v>4.25</v>
+      </c>
+      <c r="H8">
+        <v>19.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.74</v>
+      </c>
+      <c r="K8">
+        <v>0.077</v>
+      </c>
+      <c r="L8">
+        <v>1.663</v>
+      </c>
+      <c r="M8">
+        <v>0.051553404</v>
+      </c>
+      <c r="N8">
+        <v>1.611446596</v>
+      </c>
+      <c r="O8">
+        <v>0.4834339787999999</v>
+      </c>
+      <c r="P8">
+        <v>1.1280126172</v>
+      </c>
+      <c r="Q8">
+        <v>1.2050126172</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1203876457099816</v>
+      </c>
+      <c r="T8">
+        <v>0.5241156814513582</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>32.25781172471171</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1147323925061789</v>
+      </c>
+      <c r="C9">
+        <v>18.27240583963051</v>
+      </c>
+      <c r="D9">
+        <v>15.36794583963051</v>
+      </c>
+      <c r="E9">
+        <v>1.32354</v>
+      </c>
+      <c r="F9">
+        <v>1.34554</v>
+      </c>
+      <c r="G9">
+        <v>4.25</v>
+      </c>
+      <c r="H9">
+        <v>19.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.74</v>
+      </c>
+      <c r="K9">
+        <v>0.077</v>
+      </c>
+      <c r="L9">
+        <v>1.663</v>
+      </c>
+      <c r="M9">
+        <v>0.060145638</v>
+      </c>
+      <c r="N9">
+        <v>1.602854362</v>
+      </c>
+      <c r="O9">
+        <v>0.4808563085999999</v>
+      </c>
+      <c r="P9">
+        <v>1.1219980534</v>
+      </c>
+      <c r="Q9">
+        <v>1.1989980534</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.121013002694816</v>
+      </c>
+      <c r="T9">
+        <v>0.528132949009512</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>27.64955290689576</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.114422998044975</v>
+      </c>
+      <c r="C10">
+        <v>18.13748018433214</v>
+      </c>
+      <c r="D10">
+        <v>15.42524018433214</v>
+      </c>
+      <c r="E10">
+        <v>1.51576</v>
+      </c>
+      <c r="F10">
+        <v>1.53776</v>
+      </c>
+      <c r="G10">
+        <v>4.25</v>
+      </c>
+      <c r="H10">
+        <v>19.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.74</v>
+      </c>
+      <c r="K10">
+        <v>0.077</v>
+      </c>
+      <c r="L10">
+        <v>1.663</v>
+      </c>
+      <c r="M10">
+        <v>0.06873787199999999</v>
+      </c>
+      <c r="N10">
+        <v>1.594262128</v>
+      </c>
+      <c r="O10">
+        <v>0.4782786384</v>
+      </c>
+      <c r="P10">
+        <v>1.1159834896</v>
+      </c>
+      <c r="Q10">
+        <v>1.1929834896</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.121651954396712</v>
+      </c>
+      <c r="T10">
+        <v>0.5322375484711039</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>24.19335879353379</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1141136035837712</v>
+      </c>
+      <c r="C11">
+        <v>18.00298333403085</v>
+      </c>
+      <c r="D11">
+        <v>15.48296333403085</v>
+      </c>
+      <c r="E11">
+        <v>1.70798</v>
+      </c>
+      <c r="F11">
+        <v>1.72998</v>
+      </c>
+      <c r="G11">
+        <v>4.25</v>
+      </c>
+      <c r="H11">
+        <v>19.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.74</v>
+      </c>
+      <c r="K11">
+        <v>0.077</v>
+      </c>
+      <c r="L11">
+        <v>1.663</v>
+      </c>
+      <c r="M11">
+        <v>0.077330106</v>
+      </c>
+      <c r="N11">
+        <v>1.585669894</v>
+      </c>
+      <c r="O11">
+        <v>0.4757009682</v>
+      </c>
+      <c r="P11">
+        <v>1.1099689258</v>
+      </c>
+      <c r="Q11">
+        <v>1.1869689258</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1223049489931552</v>
+      </c>
+      <c r="T11">
+        <v>0.5364323589098736</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03129</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>21.50520781647448</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1138042091225674</v>
+      </c>
+      <c r="C12">
+        <v>17.86892012073202</v>
+      </c>
+      <c r="D12">
+        <v>15.54112012073202</v>
+      </c>
+      <c r="E12">
+        <v>1.9002</v>
+      </c>
+      <c r="F12">
+        <v>1.9222</v>
+      </c>
+      <c r="G12">
+        <v>4.25</v>
+      </c>
+      <c r="H12">
+        <v>19.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.74</v>
+      </c>
+      <c r="K12">
+        <v>0.077</v>
+      </c>
+      <c r="L12">
+        <v>1.663</v>
+      </c>
+      <c r="M12">
+        <v>0.08592234</v>
+      </c>
+      <c r="N12">
+        <v>1.57707766</v>
+      </c>
+      <c r="O12">
+        <v>0.473123298</v>
+      </c>
+      <c r="P12">
+        <v>1.103954362</v>
+      </c>
+      <c r="Q12">
+        <v>1.180954362</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1229724545806304</v>
+      </c>
+      <c r="T12">
+        <v>0.5407203873583938</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03129</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>19.35468703482703</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1134948146613636</v>
+      </c>
+      <c r="C13">
+        <v>17.7352954493143</v>
+      </c>
+      <c r="D13">
+        <v>15.5997154493143</v>
+      </c>
+      <c r="E13">
+        <v>2.09242</v>
+      </c>
+      <c r="F13">
+        <v>2.11442</v>
+      </c>
+      <c r="G13">
+        <v>4.25</v>
+      </c>
+      <c r="H13">
+        <v>19.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.74</v>
+      </c>
+      <c r="K13">
+        <v>0.077</v>
+      </c>
+      <c r="L13">
+        <v>1.663</v>
+      </c>
+      <c r="M13">
+        <v>0.094514574</v>
+      </c>
+      <c r="N13">
+        <v>1.568485426</v>
+      </c>
+      <c r="O13">
+        <v>0.4705456278</v>
+      </c>
+      <c r="P13">
+        <v>1.0979397982</v>
+      </c>
+      <c r="Q13">
+        <v>1.1749397982</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.123654960293667</v>
+      </c>
+      <c r="T13">
+        <v>0.5451047759967684</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03129</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>17.59517003166094</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1131854202001598</v>
+      </c>
+      <c r="C14">
+        <v>17.60211429890851</v>
+      </c>
+      <c r="D14">
+        <v>15.65875429890851</v>
+      </c>
+      <c r="E14">
+        <v>2.28464</v>
+      </c>
+      <c r="F14">
+        <v>2.30664</v>
+      </c>
+      <c r="G14">
+        <v>4.25</v>
+      </c>
+      <c r="H14">
+        <v>19.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.74</v>
+      </c>
+      <c r="K14">
+        <v>0.077</v>
+      </c>
+      <c r="L14">
+        <v>1.663</v>
+      </c>
+      <c r="M14">
+        <v>0.103106808</v>
+      </c>
+      <c r="N14">
+        <v>1.559893192</v>
+      </c>
+      <c r="O14">
+        <v>0.4679679576</v>
+      </c>
+      <c r="P14">
+        <v>1.0919252344</v>
+      </c>
+      <c r="Q14">
+        <v>1.1689252344</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1243529775001816</v>
+      </c>
+      <c r="T14">
+        <v>0.5495888098314696</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03129</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.12890586235586</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1128760257389559</v>
+      </c>
+      <c r="C15">
+        <v>17.46938172430819</v>
+      </c>
+      <c r="D15">
+        <v>15.71824172430818</v>
+      </c>
+      <c r="E15">
+        <v>2.47686</v>
+      </c>
+      <c r="F15">
+        <v>2.49886</v>
+      </c>
+      <c r="G15">
+        <v>4.25</v>
+      </c>
+      <c r="H15">
+        <v>19.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.74</v>
+      </c>
+      <c r="K15">
+        <v>0.077</v>
+      </c>
+      <c r="L15">
+        <v>1.663</v>
+      </c>
+      <c r="M15">
+        <v>0.111699042</v>
+      </c>
+      <c r="N15">
+        <v>1.551300958</v>
+      </c>
+      <c r="O15">
+        <v>0.4653902874</v>
+      </c>
+      <c r="P15">
+        <v>1.0859106706</v>
+      </c>
+      <c r="Q15">
+        <v>1.1629106706</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1250670410792597</v>
+      </c>
+      <c r="T15">
+        <v>0.5541759249037502</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03129</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>14.88822079602079</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1125666312777521</v>
+      </c>
+      <c r="C16">
+        <v>17.3371028574121</v>
+      </c>
+      <c r="D16">
+        <v>15.7781828574121</v>
+      </c>
+      <c r="E16">
+        <v>2.66908</v>
+      </c>
+      <c r="F16">
+        <v>2.69108</v>
+      </c>
+      <c r="G16">
+        <v>4.25</v>
+      </c>
+      <c r="H16">
+        <v>19.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.74</v>
+      </c>
+      <c r="K16">
+        <v>0.077</v>
+      </c>
+      <c r="L16">
+        <v>1.663</v>
+      </c>
+      <c r="M16">
+        <v>0.120291276</v>
+      </c>
+      <c r="N16">
+        <v>1.542708724</v>
+      </c>
+      <c r="O16">
+        <v>0.4628126172</v>
+      </c>
+      <c r="P16">
+        <v>1.0798961068</v>
+      </c>
+      <c r="Q16">
+        <v>1.1568961068</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1257977107880839</v>
+      </c>
+      <c r="T16">
+        <v>0.558869717070735</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03129</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>13.82477645344788</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1122572368165483</v>
+      </c>
+      <c r="C17">
+        <v>17.20528290870026</v>
+      </c>
+      <c r="D17">
+        <v>15.83858290870026</v>
+      </c>
+      <c r="E17">
+        <v>2.8613</v>
+      </c>
+      <c r="F17">
+        <v>2.8833</v>
+      </c>
+      <c r="G17">
+        <v>4.25</v>
+      </c>
+      <c r="H17">
+        <v>19.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.74</v>
+      </c>
+      <c r="K17">
+        <v>0.077</v>
+      </c>
+      <c r="L17">
+        <v>1.663</v>
+      </c>
+      <c r="M17">
+        <v>0.12888351</v>
+      </c>
+      <c r="N17">
+        <v>1.53411649</v>
+      </c>
+      <c r="O17">
+        <v>0.4602349469999999</v>
+      </c>
+      <c r="P17">
+        <v>1.073881543</v>
+      </c>
+      <c r="Q17">
+        <v>1.150881543</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.126545572725351</v>
+      </c>
+      <c r="T17">
+        <v>0.5636739514063548</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03129</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>12.90312468988469</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1120710423553445</v>
+      </c>
+      <c r="C18">
+        <v>17.04963522996643</v>
+      </c>
+      <c r="D18">
+        <v>15.87515522996643</v>
+      </c>
+      <c r="E18">
+        <v>3.05352</v>
+      </c>
+      <c r="F18">
+        <v>3.07552</v>
+      </c>
+      <c r="G18">
+        <v>4.25</v>
+      </c>
+      <c r="H18">
+        <v>19.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.74</v>
+      </c>
+      <c r="K18">
+        <v>0.077</v>
+      </c>
+      <c r="L18">
+        <v>1.663</v>
+      </c>
+      <c r="M18">
+        <v>0.140858816</v>
+      </c>
+      <c r="N18">
+        <v>1.522141184</v>
+      </c>
+      <c r="O18">
+        <v>0.4566423552</v>
+      </c>
+      <c r="P18">
+        <v>1.0654988288</v>
+      </c>
+      <c r="Q18">
+        <v>1.1424988288</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1273112408992196</v>
+      </c>
+      <c r="T18">
+        <v>0.5685925722737749</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03206</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.80614779553451</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1117693478941407</v>
+      </c>
+      <c r="C19">
+        <v>16.91703395582858</v>
+      </c>
+      <c r="D19">
+        <v>15.93477395582858</v>
+      </c>
+      <c r="E19">
+        <v>3.24574</v>
+      </c>
+      <c r="F19">
+        <v>3.26774</v>
+      </c>
+      <c r="G19">
+        <v>4.25</v>
+      </c>
+      <c r="H19">
+        <v>19.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.74</v>
+      </c>
+      <c r="K19">
+        <v>0.077</v>
+      </c>
+      <c r="L19">
+        <v>1.663</v>
+      </c>
+      <c r="M19">
+        <v>0.149662492</v>
+      </c>
+      <c r="N19">
+        <v>1.513337508</v>
+      </c>
+      <c r="O19">
+        <v>0.4540012524</v>
+      </c>
+      <c r="P19">
+        <v>1.0593362556</v>
+      </c>
+      <c r="Q19">
+        <v>1.1363362556</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1280953589086032</v>
+      </c>
+      <c r="T19">
+        <v>0.5736297141259523</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03206</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.11166851344424</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1114676534329369</v>
+      </c>
+      <c r="C20">
+        <v>16.78488216280349</v>
+      </c>
+      <c r="D20">
+        <v>15.99484216280348</v>
+      </c>
+      <c r="E20">
+        <v>3.437959999999999</v>
+      </c>
+      <c r="F20">
+        <v>3.459959999999999</v>
+      </c>
+      <c r="G20">
+        <v>4.25</v>
+      </c>
+      <c r="H20">
+        <v>19.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.74</v>
+      </c>
+      <c r="K20">
+        <v>0.077</v>
+      </c>
+      <c r="L20">
+        <v>1.663</v>
+      </c>
+      <c r="M20">
+        <v>0.158466168</v>
+      </c>
+      <c r="N20">
+        <v>1.504533832</v>
+      </c>
+      <c r="O20">
+        <v>0.4513601496</v>
+      </c>
+      <c r="P20">
+        <v>1.0531736824</v>
+      </c>
+      <c r="Q20">
+        <v>1.1301736824</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.128898601747484</v>
+      </c>
+      <c r="T20">
+        <v>0.5787897130964753</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03206</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.49435359603067</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.111458558971733</v>
+      </c>
+      <c r="C21">
+        <v>16.5944799276953</v>
+      </c>
+      <c r="D21">
+        <v>15.9966599276953</v>
+      </c>
+      <c r="E21">
+        <v>3.63018</v>
+      </c>
+      <c r="F21">
+        <v>3.65218</v>
+      </c>
+      <c r="G21">
+        <v>4.25</v>
+      </c>
+      <c r="H21">
+        <v>19.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.74</v>
+      </c>
+      <c r="K21">
+        <v>0.077</v>
+      </c>
+      <c r="L21">
+        <v>1.663</v>
+      </c>
+      <c r="M21">
+        <v>0.17530464</v>
+      </c>
+      <c r="N21">
+        <v>1.48769536</v>
+      </c>
+      <c r="O21">
+        <v>0.446308608</v>
+      </c>
+      <c r="P21">
+        <v>1.041386752</v>
+      </c>
+      <c r="Q21">
+        <v>1.118386752</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1297216777428803</v>
+      </c>
+      <c r="T21">
+        <v>0.5840771194489867</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.0336</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>9.486343316411935</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1111722645105293</v>
+      </c>
+      <c r="C22">
+        <v>16.45969531591754</v>
+      </c>
+      <c r="D22">
+        <v>16.05409531591754</v>
+      </c>
+      <c r="E22">
+        <v>3.8224</v>
+      </c>
+      <c r="F22">
+        <v>3.8444</v>
+      </c>
+      <c r="G22">
+        <v>4.25</v>
+      </c>
+      <c r="H22">
+        <v>19.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.74</v>
+      </c>
+      <c r="K22">
+        <v>0.077</v>
+      </c>
+      <c r="L22">
+        <v>1.663</v>
+      </c>
+      <c r="M22">
+        <v>0.1845312</v>
+      </c>
+      <c r="N22">
+        <v>1.4784688</v>
+      </c>
+      <c r="O22">
+        <v>0.44354064</v>
+      </c>
+      <c r="P22">
+        <v>1.03492816</v>
+      </c>
+      <c r="Q22">
+        <v>1.11192816</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1305653306381616</v>
+      </c>
+      <c r="T22">
+        <v>0.5894967109603109</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.0336</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>9.012026150591335</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1108859700493254</v>
+      </c>
+      <c r="C23">
+        <v>16.32532462939847</v>
+      </c>
+      <c r="D23">
+        <v>16.11194462939847</v>
+      </c>
+      <c r="E23">
+        <v>4.014619999999999</v>
+      </c>
+      <c r="F23">
+        <v>4.036619999999999</v>
+      </c>
+      <c r="G23">
+        <v>4.25</v>
+      </c>
+      <c r="H23">
+        <v>19.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.74</v>
+      </c>
+      <c r="K23">
+        <v>0.077</v>
+      </c>
+      <c r="L23">
+        <v>1.663</v>
+      </c>
+      <c r="M23">
+        <v>0.19375776</v>
+      </c>
+      <c r="N23">
+        <v>1.46924224</v>
+      </c>
+      <c r="O23">
+        <v>0.440772672</v>
+      </c>
+      <c r="P23">
+        <v>1.028469568</v>
+      </c>
+      <c r="Q23">
+        <v>1.105469568</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1314303418345891</v>
+      </c>
+      <c r="T23">
+        <v>0.5950535073200228</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.0336</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.582882048182226</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1105996755881216</v>
+      </c>
+      <c r="C24">
+        <v>16.19137235893395</v>
+      </c>
+      <c r="D24">
+        <v>16.17021235893396</v>
+      </c>
+      <c r="E24">
+        <v>4.20684</v>
+      </c>
+      <c r="F24">
+        <v>4.22884</v>
+      </c>
+      <c r="G24">
+        <v>4.25</v>
+      </c>
+      <c r="H24">
+        <v>19.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.74</v>
+      </c>
+      <c r="K24">
+        <v>0.077</v>
+      </c>
+      <c r="L24">
+        <v>1.663</v>
+      </c>
+      <c r="M24">
+        <v>0.20298432</v>
+      </c>
+      <c r="N24">
+        <v>1.46001568</v>
+      </c>
+      <c r="O24">
+        <v>0.438004704</v>
+      </c>
+      <c r="P24">
+        <v>1.022010976</v>
+      </c>
+      <c r="Q24">
+        <v>1.099010976</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1323175328052841</v>
+      </c>
+      <c r="T24">
+        <v>0.6007527856376763</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.0336</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.192751045992125</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1103133811269178</v>
+      </c>
+      <c r="C25">
+        <v>16.05784306051834</v>
+      </c>
+      <c r="D25">
+        <v>16.22890306051834</v>
+      </c>
+      <c r="E25">
+        <v>4.39906</v>
+      </c>
+      <c r="F25">
+        <v>4.42106</v>
+      </c>
+      <c r="G25">
+        <v>4.25</v>
+      </c>
+      <c r="H25">
+        <v>19.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.74</v>
+      </c>
+      <c r="K25">
+        <v>0.077</v>
+      </c>
+      <c r="L25">
+        <v>1.663</v>
+      </c>
+      <c r="M25">
+        <v>0.21221088</v>
+      </c>
+      <c r="N25">
+        <v>1.45078912</v>
+      </c>
+      <c r="O25">
+        <v>0.435236736</v>
+      </c>
+      <c r="P25">
+        <v>1.015552384</v>
+      </c>
+      <c r="Q25">
+        <v>1.092552384</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1332277676972958</v>
+      </c>
+      <c r="T25">
+        <v>0.6066000971583856</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.0336</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.836544478775076</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.110279086665714</v>
+      </c>
+      <c r="C26">
+        <v>15.87268205176409</v>
+      </c>
+      <c r="D26">
+        <v>16.23596205176409</v>
+      </c>
+      <c r="E26">
+        <v>4.591279999999999</v>
+      </c>
+      <c r="F26">
+        <v>4.61328</v>
+      </c>
+      <c r="G26">
+        <v>4.25</v>
+      </c>
+      <c r="H26">
+        <v>19.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.74</v>
+      </c>
+      <c r="K26">
+        <v>0.077</v>
+      </c>
+      <c r="L26">
+        <v>1.663</v>
+      </c>
+      <c r="M26">
+        <v>0.22835736</v>
+      </c>
+      <c r="N26">
+        <v>1.43464264</v>
+      </c>
+      <c r="O26">
+        <v>0.430392792</v>
+      </c>
+      <c r="P26">
+        <v>1.004249848</v>
+      </c>
+      <c r="Q26">
+        <v>1.081249848</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1341619561390973</v>
+      </c>
+      <c r="T26">
+        <v>0.612601285298061</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03465</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.282445374215222</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1100032922045102</v>
+      </c>
+      <c r="C27">
+        <v>15.73745417924334</v>
+      </c>
+      <c r="D27">
+        <v>16.29295417924333</v>
+      </c>
+      <c r="E27">
+        <v>4.783499999999999</v>
+      </c>
+      <c r="F27">
+        <v>4.805499999999999</v>
+      </c>
+      <c r="G27">
+        <v>4.25</v>
+      </c>
+      <c r="H27">
+        <v>19.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.74</v>
+      </c>
+      <c r="K27">
+        <v>0.077</v>
+      </c>
+      <c r="L27">
+        <v>1.663</v>
+      </c>
+      <c r="M27">
+        <v>0.23787225</v>
+      </c>
+      <c r="N27">
+        <v>1.42512775</v>
+      </c>
+      <c r="O27">
+        <v>0.4275383250000001</v>
+      </c>
+      <c r="P27">
+        <v>0.9975894250000001</v>
+      </c>
+      <c r="Q27">
+        <v>1.074589425</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1351210562726802</v>
+      </c>
+      <c r="T27">
+        <v>0.618762505121461</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03465</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.991147559246613</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1097274977433063</v>
+      </c>
+      <c r="C28">
+        <v>15.60262782827925</v>
+      </c>
+      <c r="D28">
+        <v>16.35034782827925</v>
+      </c>
+      <c r="E28">
+        <v>4.975719999999999</v>
+      </c>
+      <c r="F28">
+        <v>4.997719999999999</v>
+      </c>
+      <c r="G28">
+        <v>4.25</v>
+      </c>
+      <c r="H28">
+        <v>19.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.74</v>
+      </c>
+      <c r="K28">
+        <v>0.077</v>
+      </c>
+      <c r="L28">
+        <v>1.663</v>
+      </c>
+      <c r="M28">
+        <v>0.24738714</v>
+      </c>
+      <c r="N28">
+        <v>1.41561286</v>
+      </c>
+      <c r="O28">
+        <v>0.424683858</v>
+      </c>
+      <c r="P28">
+        <v>0.990929002</v>
+      </c>
+      <c r="Q28">
+        <v>1.067929002</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.136106078031495</v>
+      </c>
+      <c r="T28">
+        <v>0.6250902443995475</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03465</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.722257268506358</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1094517032821025</v>
+      </c>
+      <c r="C29">
+        <v>15.46820725707787</v>
+      </c>
+      <c r="D29">
+        <v>16.40814725707787</v>
+      </c>
+      <c r="E29">
+        <v>5.16794</v>
+      </c>
+      <c r="F29">
+        <v>5.18994</v>
+      </c>
+      <c r="G29">
+        <v>4.25</v>
+      </c>
+      <c r="H29">
+        <v>19.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.74</v>
+      </c>
+      <c r="K29">
+        <v>0.077</v>
+      </c>
+      <c r="L29">
+        <v>1.663</v>
+      </c>
+      <c r="M29">
+        <v>0.25690203</v>
+      </c>
+      <c r="N29">
+        <v>1.40609797</v>
+      </c>
+      <c r="O29">
+        <v>0.421829391</v>
+      </c>
+      <c r="P29">
+        <v>0.9842685790000001</v>
+      </c>
+      <c r="Q29">
+        <v>1.061268579</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1371180866878117</v>
+      </c>
+      <c r="T29">
+        <v>0.6315913463975816</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03465</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.473284777080197</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1091759088208987</v>
+      </c>
+      <c r="C30">
+        <v>15.33419678427086</v>
+      </c>
+      <c r="D30">
+        <v>16.46635678427086</v>
+      </c>
+      <c r="E30">
+        <v>5.36016</v>
+      </c>
+      <c r="F30">
+        <v>5.38216</v>
+      </c>
+      <c r="G30">
+        <v>4.25</v>
+      </c>
+      <c r="H30">
+        <v>19.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.74</v>
+      </c>
+      <c r="K30">
+        <v>0.077</v>
+      </c>
+      <c r="L30">
+        <v>1.663</v>
+      </c>
+      <c r="M30">
+        <v>0.26641692</v>
+      </c>
+      <c r="N30">
+        <v>1.39658308</v>
+      </c>
+      <c r="O30">
+        <v>0.418974924</v>
+      </c>
+      <c r="P30">
+        <v>0.9776081560000001</v>
+      </c>
+      <c r="Q30">
+        <v>1.054608156</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1381582066956926</v>
+      </c>
+      <c r="T30">
+        <v>0.6382730345622277</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03465</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.242096035041619</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1091843143596949</v>
+      </c>
+      <c r="C31">
+        <v>15.14019659937991</v>
+      </c>
+      <c r="D31">
+        <v>16.46457659937991</v>
+      </c>
+      <c r="E31">
+        <v>5.552379999999999</v>
+      </c>
+      <c r="F31">
+        <v>5.574379999999999</v>
+      </c>
+      <c r="G31">
+        <v>4.25</v>
+      </c>
+      <c r="H31">
+        <v>19.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.74</v>
+      </c>
+      <c r="K31">
+        <v>0.077</v>
+      </c>
+      <c r="L31">
+        <v>1.663</v>
+      </c>
+      <c r="M31">
+        <v>0.283735942</v>
+      </c>
+      <c r="N31">
+        <v>1.379264058</v>
+      </c>
+      <c r="O31">
+        <v>0.4137792174</v>
+      </c>
+      <c r="P31">
+        <v>0.9654848406000001</v>
+      </c>
+      <c r="Q31">
+        <v>1.0424848406</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1392276258587252</v>
+      </c>
+      <c r="T31">
+        <v>0.6451429392948922</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03563</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.861083330782253</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1089183198984911</v>
+      </c>
+      <c r="C32">
+        <v>15.00449808070165</v>
+      </c>
+      <c r="D32">
+        <v>16.52109808070165</v>
+      </c>
+      <c r="E32">
+        <v>5.744599999999999</v>
+      </c>
+      <c r="F32">
+        <v>5.7666</v>
+      </c>
+      <c r="G32">
+        <v>4.25</v>
+      </c>
+      <c r="H32">
+        <v>19.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.74</v>
+      </c>
+      <c r="K32">
+        <v>0.077</v>
+      </c>
+      <c r="L32">
+        <v>1.663</v>
+      </c>
+      <c r="M32">
+        <v>0.29351994</v>
+      </c>
+      <c r="N32">
+        <v>1.36948006</v>
+      </c>
+      <c r="O32">
+        <v>0.410844018</v>
+      </c>
+      <c r="P32">
+        <v>0.9586360420000001</v>
+      </c>
+      <c r="Q32">
+        <v>1.035636042</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1403275998549873</v>
+      </c>
+      <c r="T32">
+        <v>0.6522091270199184</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03563</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.665713886422845</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1086523254372872</v>
+      </c>
+      <c r="C33">
+        <v>14.86918896562155</v>
+      </c>
+      <c r="D33">
+        <v>16.57800896562155</v>
+      </c>
+      <c r="E33">
+        <v>5.936819999999999</v>
+      </c>
+      <c r="F33">
+        <v>5.958819999999999</v>
+      </c>
+      <c r="G33">
+        <v>4.25</v>
+      </c>
+      <c r="H33">
+        <v>19.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.74</v>
+      </c>
+      <c r="K33">
+        <v>0.077</v>
+      </c>
+      <c r="L33">
+        <v>1.663</v>
+      </c>
+      <c r="M33">
+        <v>0.303303938</v>
+      </c>
+      <c r="N33">
+        <v>1.359696062</v>
+      </c>
+      <c r="O33">
+        <v>0.4079088186</v>
+      </c>
+      <c r="P33">
+        <v>0.9517872434000001</v>
+      </c>
+      <c r="Q33">
+        <v>1.0287872434</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1414594571554888</v>
+      </c>
+      <c r="T33">
+        <v>0.6594801317804525</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.03563</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.482948922344688</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1083863309760834</v>
+      </c>
+      <c r="C34">
+        <v>14.73427329223205</v>
+      </c>
+      <c r="D34">
+        <v>16.63531329223205</v>
+      </c>
+      <c r="E34">
+        <v>6.129039999999999</v>
+      </c>
+      <c r="F34">
+        <v>6.151039999999999</v>
+      </c>
+      <c r="G34">
+        <v>4.25</v>
+      </c>
+      <c r="H34">
+        <v>19.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.74</v>
+      </c>
+      <c r="K34">
+        <v>0.077</v>
+      </c>
+      <c r="L34">
+        <v>1.663</v>
+      </c>
+      <c r="M34">
+        <v>0.313087936</v>
+      </c>
+      <c r="N34">
+        <v>1.349912064</v>
+      </c>
+      <c r="O34">
+        <v>0.4049736192</v>
+      </c>
+      <c r="P34">
+        <v>0.9449384448000002</v>
+      </c>
+      <c r="Q34">
+        <v>1.0219384448</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1426246043765933</v>
+      </c>
+      <c r="T34">
+        <v>0.6669649896221789</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.03563</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.311606768521417</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1081203365148796</v>
+      </c>
+      <c r="C35">
+        <v>14.59975515465231</v>
+      </c>
+      <c r="D35">
+        <v>16.69301515465231</v>
+      </c>
+      <c r="E35">
+        <v>6.32126</v>
+      </c>
+      <c r="F35">
+        <v>6.34326</v>
+      </c>
+      <c r="G35">
+        <v>4.25</v>
+      </c>
+      <c r="H35">
+        <v>19.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.74</v>
+      </c>
+      <c r="K35">
+        <v>0.077</v>
+      </c>
+      <c r="L35">
+        <v>1.663</v>
+      </c>
+      <c r="M35">
+        <v>0.322871934</v>
+      </c>
+      <c r="N35">
+        <v>1.340128066</v>
+      </c>
+      <c r="O35">
+        <v>0.4020384198</v>
+      </c>
+      <c r="P35">
+        <v>0.9380896462000001</v>
+      </c>
+      <c r="Q35">
+        <v>1.0150896462</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1438245321117607</v>
+      </c>
+      <c r="T35">
+        <v>0.6746732760561958</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.03563</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.150648987657131</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1078543420536758</v>
+      </c>
+      <c r="C36">
+        <v>14.46563870400328</v>
+      </c>
+      <c r="D36">
+        <v>16.75111870400328</v>
+      </c>
+      <c r="E36">
+        <v>6.513479999999999</v>
+      </c>
+      <c r="F36">
+        <v>6.53548</v>
+      </c>
+      <c r="G36">
+        <v>4.25</v>
+      </c>
+      <c r="H36">
+        <v>19.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.74</v>
+      </c>
+      <c r="K36">
+        <v>0.077</v>
+      </c>
+      <c r="L36">
+        <v>1.663</v>
+      </c>
+      <c r="M36">
+        <v>0.332655932</v>
+      </c>
+      <c r="N36">
+        <v>1.330344068</v>
+      </c>
+      <c r="O36">
+        <v>0.3991032204</v>
+      </c>
+      <c r="P36">
+        <v>0.9312408476</v>
+      </c>
+      <c r="Q36">
+        <v>1.0082408476</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1450608212934482</v>
+      </c>
+      <c r="T36">
+        <v>0.6826151469276068</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.03563</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.999159311549569</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.107588347592472</v>
+      </c>
+      <c r="C37">
+        <v>14.33192814940314</v>
+      </c>
+      <c r="D37">
+        <v>16.80962814940314</v>
+      </c>
+      <c r="E37">
+        <v>6.705699999999999</v>
+      </c>
+      <c r="F37">
+        <v>6.7277</v>
+      </c>
+      <c r="G37">
+        <v>4.25</v>
+      </c>
+      <c r="H37">
+        <v>19.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.74</v>
+      </c>
+      <c r="K37">
+        <v>0.077</v>
+      </c>
+      <c r="L37">
+        <v>1.663</v>
+      </c>
+      <c r="M37">
+        <v>0.34243993</v>
+      </c>
+      <c r="N37">
+        <v>1.32056007</v>
+      </c>
+      <c r="O37">
+        <v>0.396168021</v>
+      </c>
+      <c r="P37">
+        <v>0.9243920489999999</v>
+      </c>
+      <c r="Q37">
+        <v>1.001392049</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1463351501422646</v>
+      </c>
+      <c r="T37">
+        <v>0.6908013830565999</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.03563</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.856326188362438</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1073223531312682</v>
+      </c>
+      <c r="C38">
+        <v>14.1986277589838</v>
+      </c>
+      <c r="D38">
+        <v>16.8685477589838</v>
+      </c>
+      <c r="E38">
+        <v>6.897919999999998</v>
+      </c>
+      <c r="F38">
+        <v>6.919919999999999</v>
+      </c>
+      <c r="G38">
+        <v>4.25</v>
+      </c>
+      <c r="H38">
+        <v>19.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.74</v>
+      </c>
+      <c r="K38">
+        <v>0.077</v>
+      </c>
+      <c r="L38">
+        <v>1.663</v>
+      </c>
+      <c r="M38">
+        <v>0.3522239279999999</v>
+      </c>
+      <c r="N38">
+        <v>1.310776072</v>
+      </c>
+      <c r="O38">
+        <v>0.3932328216</v>
+      </c>
+      <c r="P38">
+        <v>0.9175432504000001</v>
+      </c>
+      <c r="Q38">
+        <v>0.9945432504</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1476493017676065</v>
+      </c>
+      <c r="T38">
+        <v>0.6992434390646241</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.03563</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.721428238685704</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1070563586700644</v>
+      </c>
+      <c r="C39">
+        <v>14.06574186092876</v>
+      </c>
+      <c r="D39">
+        <v>16.92788186092876</v>
+      </c>
+      <c r="E39">
+        <v>7.090139999999999</v>
+      </c>
+      <c r="F39">
+        <v>7.112139999999999</v>
+      </c>
+      <c r="G39">
+        <v>4.25</v>
+      </c>
+      <c r="H39">
+        <v>19.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.74</v>
+      </c>
+      <c r="K39">
+        <v>0.077</v>
+      </c>
+      <c r="L39">
+        <v>1.663</v>
+      </c>
+      <c r="M39">
+        <v>0.362007926</v>
+      </c>
+      <c r="N39">
+        <v>1.300992074</v>
+      </c>
+      <c r="O39">
+        <v>0.3902976222</v>
+      </c>
+      <c r="P39">
+        <v>0.9106944518</v>
+      </c>
+      <c r="Q39">
+        <v>0.9876944517999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1490051724921656</v>
+      </c>
+      <c r="T39">
+        <v>0.7079534968506805</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.03563</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.593822070072576</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1074819642088605</v>
+      </c>
+      <c r="C40">
+        <v>13.7787833448612</v>
+      </c>
+      <c r="D40">
+        <v>16.8331433448612</v>
+      </c>
+      <c r="E40">
+        <v>7.282359999999999</v>
+      </c>
+      <c r="F40">
+        <v>7.304359999999999</v>
+      </c>
+      <c r="G40">
+        <v>4.25</v>
+      </c>
+      <c r="H40">
+        <v>19.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.74</v>
+      </c>
+      <c r="K40">
+        <v>0.077</v>
+      </c>
+      <c r="L40">
+        <v>1.663</v>
+      </c>
+      <c r="M40">
+        <v>0.39078326</v>
+      </c>
+      <c r="N40">
+        <v>1.27221674</v>
+      </c>
+      <c r="O40">
+        <v>0.381665022</v>
+      </c>
+      <c r="P40">
+        <v>0.8905517180000002</v>
+      </c>
+      <c r="Q40">
+        <v>0.9675517180000002</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1504047809820331</v>
+      </c>
+      <c r="T40">
+        <v>0.716944524242739</v>
+      </c>
+      <c r="U40">
+        <v>0.0535</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.03745</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.25555588025956</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1072341697476567</v>
+      </c>
+      <c r="C41">
+        <v>13.64159225758264</v>
+      </c>
+      <c r="D41">
+        <v>16.88817225758264</v>
+      </c>
+      <c r="E41">
+        <v>7.47458</v>
+      </c>
+      <c r="F41">
+        <v>7.49658</v>
+      </c>
+      <c r="G41">
+        <v>4.25</v>
+      </c>
+      <c r="H41">
+        <v>19.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.74</v>
+      </c>
+      <c r="K41">
+        <v>0.077</v>
+      </c>
+      <c r="L41">
+        <v>1.663</v>
+      </c>
+      <c r="M41">
+        <v>0.40106703</v>
+      </c>
+      <c r="N41">
+        <v>1.26193297</v>
+      </c>
+      <c r="O41">
+        <v>0.3785798910000001</v>
+      </c>
+      <c r="P41">
+        <v>0.8833530790000002</v>
+      </c>
+      <c r="Q41">
+        <v>0.9603530790000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1518502782748471</v>
+      </c>
+      <c r="T41">
+        <v>0.7262303394181436</v>
+      </c>
+      <c r="U41">
+        <v>0.0535</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.03745</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.146439062817006</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1069863752864529</v>
+      </c>
+      <c r="C42">
+        <v>13.50476213830767</v>
+      </c>
+      <c r="D42">
+        <v>16.94356213830767</v>
+      </c>
+      <c r="E42">
+        <v>7.666799999999999</v>
+      </c>
+      <c r="F42">
+        <v>7.6888</v>
+      </c>
+      <c r="G42">
+        <v>4.25</v>
+      </c>
+      <c r="H42">
+        <v>19.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.74</v>
+      </c>
+      <c r="K42">
+        <v>0.077</v>
+      </c>
+      <c r="L42">
+        <v>1.663</v>
+      </c>
+      <c r="M42">
+        <v>0.4113508</v>
+      </c>
+      <c r="N42">
+        <v>1.2516492</v>
+      </c>
+      <c r="O42">
+        <v>0.37549476</v>
+      </c>
+      <c r="P42">
+        <v>0.8761544400000001</v>
+      </c>
+      <c r="Q42">
+        <v>0.95315444</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1533439588107549</v>
+      </c>
+      <c r="T42">
+        <v>0.7358256817660618</v>
+      </c>
+      <c r="U42">
+        <v>0.0535</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.03745</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.042778086246582</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1075134808252491</v>
+      </c>
+      <c r="C43">
+        <v>13.19514999354974</v>
+      </c>
+      <c r="D43">
+        <v>16.82616999354974</v>
+      </c>
+      <c r="E43">
+        <v>7.859019999999999</v>
+      </c>
+      <c r="F43">
+        <v>7.881019999999999</v>
+      </c>
+      <c r="G43">
+        <v>4.25</v>
+      </c>
+      <c r="H43">
+        <v>19.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.74</v>
+      </c>
+      <c r="K43">
+        <v>0.077</v>
+      </c>
+      <c r="L43">
+        <v>1.663</v>
+      </c>
+      <c r="M43">
+        <v>0.442913324</v>
+      </c>
+      <c r="N43">
+        <v>1.220086676</v>
+      </c>
+      <c r="O43">
+        <v>0.3660260028</v>
+      </c>
+      <c r="P43">
+        <v>0.8540606732</v>
+      </c>
+      <c r="Q43">
+        <v>0.9310606732</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.154888272585168</v>
+      </c>
+      <c r="T43">
+        <v>0.7457462899562821</v>
+      </c>
+      <c r="U43">
+        <v>0.0562</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.03934</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.754684968565091</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1072845863640453</v>
+      </c>
+      <c r="C44">
+        <v>13.05370686097631</v>
+      </c>
+      <c r="D44">
+        <v>16.87694686097631</v>
+      </c>
+      <c r="E44">
+        <v>8.051239999999998</v>
+      </c>
+      <c r="F44">
+        <v>8.073239999999998</v>
+      </c>
+      <c r="G44">
+        <v>4.25</v>
+      </c>
+      <c r="H44">
+        <v>19.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.74</v>
+      </c>
+      <c r="K44">
+        <v>0.077</v>
+      </c>
+      <c r="L44">
+        <v>1.663</v>
+      </c>
+      <c r="M44">
+        <v>0.4537160879999999</v>
+      </c>
+      <c r="N44">
+        <v>1.209283912</v>
+      </c>
+      <c r="O44">
+        <v>0.3627851736</v>
+      </c>
+      <c r="P44">
+        <v>0.8464987384</v>
+      </c>
+      <c r="Q44">
+        <v>0.9234987384</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1564858385586987</v>
+      </c>
+      <c r="T44">
+        <v>0.7560089880840962</v>
+      </c>
+      <c r="U44">
+        <v>0.0562</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.03934</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.66528770740878</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1070556919028414</v>
+      </c>
+      <c r="C45">
+        <v>12.91257111795211</v>
+      </c>
+      <c r="D45">
+        <v>16.92803111795211</v>
+      </c>
+      <c r="E45">
+        <v>8.243459999999999</v>
+      </c>
+      <c r="F45">
+        <v>8.265459999999999</v>
+      </c>
+      <c r="G45">
+        <v>4.25</v>
+      </c>
+      <c r="H45">
+        <v>19.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.74</v>
+      </c>
+      <c r="K45">
+        <v>0.077</v>
+      </c>
+      <c r="L45">
+        <v>1.663</v>
+      </c>
+      <c r="M45">
+        <v>0.4645188519999999</v>
+      </c>
+      <c r="N45">
+        <v>1.198481148</v>
+      </c>
+      <c r="O45">
+        <v>0.3595443444</v>
+      </c>
+      <c r="P45">
+        <v>0.8389368036000001</v>
+      </c>
+      <c r="Q45">
+        <v>0.9159368036000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1581394594786692</v>
+      </c>
+      <c r="T45">
+        <v>0.7666317808830618</v>
+      </c>
+      <c r="U45">
+        <v>0.0562</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.03934</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.580048458399274</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1082743974416377</v>
+      </c>
+      <c r="C46">
+        <v>12.45186621704849</v>
+      </c>
+      <c r="D46">
+        <v>16.65954621704849</v>
+      </c>
+      <c r="E46">
+        <v>8.43568</v>
+      </c>
+      <c r="F46">
+        <v>8.45768</v>
+      </c>
+      <c r="G46">
+        <v>4.25</v>
+      </c>
+      <c r="H46">
+        <v>19.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.74</v>
+      </c>
+      <c r="K46">
+        <v>0.077</v>
+      </c>
+      <c r="L46">
+        <v>1.663</v>
+      </c>
+      <c r="M46">
+        <v>0.515072712</v>
+      </c>
+      <c r="N46">
+        <v>1.147927288</v>
+      </c>
+      <c r="O46">
+        <v>0.3443781864</v>
+      </c>
+      <c r="P46">
+        <v>0.8035491016</v>
+      </c>
+      <c r="Q46">
+        <v>0.8805491016</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1598521382886386</v>
+      </c>
+      <c r="T46">
+        <v>0.7776339591391334</v>
+      </c>
+      <c r="U46">
+        <v>0.0609</v>
+      </c>
+      <c r="V46">
+        <v>0.3</v>
+      </c>
+      <c r="W46">
+        <v>0.04263</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.228670362952561</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1080784029804338</v>
+      </c>
+      <c r="C47">
+        <v>12.3022482934509</v>
+      </c>
+      <c r="D47">
+        <v>16.7021482934509</v>
+      </c>
+      <c r="E47">
+        <v>8.627899999999999</v>
+      </c>
+      <c r="F47">
+        <v>8.649899999999999</v>
+      </c>
+      <c r="G47">
+        <v>4.25</v>
+      </c>
+      <c r="H47">
+        <v>19.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.74</v>
+      </c>
+      <c r="K47">
+        <v>0.077</v>
+      </c>
+      <c r="L47">
+        <v>1.663</v>
+      </c>
+      <c r="M47">
+        <v>0.52677891</v>
+      </c>
+      <c r="N47">
+        <v>1.13622109</v>
+      </c>
+      <c r="O47">
+        <v>0.340866327</v>
+      </c>
+      <c r="P47">
+        <v>0.795354763</v>
+      </c>
+      <c r="Q47">
+        <v>0.8723547629999999</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1616270963280615</v>
+      </c>
+      <c r="T47">
+        <v>0.7890362166045166</v>
+      </c>
+      <c r="U47">
+        <v>0.0609</v>
+      </c>
+      <c r="V47">
+        <v>0.3</v>
+      </c>
+      <c r="W47">
+        <v>0.04263</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.156922132664727</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.10788240851923</v>
+      </c>
+      <c r="C48">
+        <v>12.1528488139786</v>
+      </c>
+      <c r="D48">
+        <v>16.74496881397859</v>
+      </c>
+      <c r="E48">
+        <v>8.820119999999999</v>
+      </c>
+      <c r="F48">
+        <v>8.84212</v>
+      </c>
+      <c r="G48">
+        <v>4.25</v>
+      </c>
+      <c r="H48">
+        <v>19.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.74</v>
+      </c>
+      <c r="K48">
+        <v>0.077</v>
+      </c>
+      <c r="L48">
+        <v>1.663</v>
+      </c>
+      <c r="M48">
+        <v>0.538485108</v>
+      </c>
+      <c r="N48">
+        <v>1.124514892</v>
+      </c>
+      <c r="O48">
+        <v>0.3373544676</v>
+      </c>
+      <c r="P48">
+        <v>0.7871604244000001</v>
+      </c>
+      <c r="Q48">
+        <v>0.8641604244000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1634677935541296</v>
+      </c>
+      <c r="T48">
+        <v>0.8008607799019509</v>
+      </c>
+      <c r="U48">
+        <v>0.0609</v>
+      </c>
+      <c r="V48">
+        <v>0.3</v>
+      </c>
+      <c r="W48">
+        <v>0.04263</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.088293390650276</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1076864140580262</v>
+      </c>
+      <c r="C49">
+        <v>12.00366946307368</v>
+      </c>
+      <c r="D49">
+        <v>16.78800946307368</v>
+      </c>
+      <c r="E49">
+        <v>9.01234</v>
+      </c>
+      <c r="F49">
+        <v>9.03434</v>
+      </c>
+      <c r="G49">
+        <v>4.25</v>
+      </c>
+      <c r="H49">
+        <v>19.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.74</v>
+      </c>
+      <c r="K49">
+        <v>0.077</v>
+      </c>
+      <c r="L49">
+        <v>1.663</v>
+      </c>
+      <c r="M49">
+        <v>0.550191306</v>
+      </c>
+      <c r="N49">
+        <v>1.112808694</v>
+      </c>
+      <c r="O49">
+        <v>0.3338426081999999</v>
+      </c>
+      <c r="P49">
+        <v>0.7789660858</v>
+      </c>
+      <c r="Q49">
+        <v>0.8559660858</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1653779510528796</v>
+      </c>
+      <c r="T49">
+        <v>0.8131315531351376</v>
+      </c>
+      <c r="U49">
+        <v>0.0609</v>
+      </c>
+      <c r="V49">
+        <v>0.3</v>
+      </c>
+      <c r="W49">
+        <v>0.04263</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.02258502063644</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1106152195968224</v>
+      </c>
+      <c r="C50">
+        <v>11.19047796604337</v>
+      </c>
+      <c r="D50">
+        <v>16.16703796604337</v>
+      </c>
+      <c r="E50">
+        <v>9.204559999999999</v>
+      </c>
+      <c r="F50">
+        <v>9.226559999999999</v>
+      </c>
+      <c r="G50">
+        <v>4.25</v>
+      </c>
+      <c r="H50">
+        <v>19.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.74</v>
+      </c>
+      <c r="K50">
+        <v>0.077</v>
+      </c>
+      <c r="L50">
+        <v>1.663</v>
+      </c>
+      <c r="M50">
+        <v>0.6477045119999999</v>
+      </c>
+      <c r="N50">
+        <v>1.015295488</v>
+      </c>
+      <c r="O50">
+        <v>0.3045886464</v>
+      </c>
+      <c r="P50">
+        <v>0.7107068416</v>
+      </c>
+      <c r="Q50">
+        <v>0.7877068415999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1673615761477353</v>
+      </c>
+      <c r="T50">
+        <v>0.8258742791849853</v>
+      </c>
+      <c r="U50">
+        <v>0.0702</v>
+      </c>
+      <c r="V50">
+        <v>0.3</v>
+      </c>
+      <c r="W50">
+        <v>0.04914</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.56752881783229</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1104843251356185</v>
+      </c>
+      <c r="C51">
+        <v>11.02502820111028</v>
+      </c>
+      <c r="D51">
+        <v>16.19380820111028</v>
+      </c>
+      <c r="E51">
+        <v>9.396779999999998</v>
+      </c>
+      <c r="F51">
+        <v>9.418779999999998</v>
+      </c>
+      <c r="G51">
+        <v>4.25</v>
+      </c>
+      <c r="H51">
+        <v>19.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.74</v>
+      </c>
+      <c r="K51">
+        <v>0.077</v>
+      </c>
+      <c r="L51">
+        <v>1.663</v>
+      </c>
+      <c r="M51">
+        <v>0.6611983559999999</v>
+      </c>
+      <c r="N51">
+        <v>1.001801644</v>
+      </c>
+      <c r="O51">
+        <v>0.3005404932</v>
+      </c>
+      <c r="P51">
+        <v>0.7012611508000002</v>
+      </c>
+      <c r="Q51">
+        <v>0.7782611508000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1694229904619972</v>
+      </c>
+      <c r="T51">
+        <v>0.8391167199818859</v>
+      </c>
+      <c r="U51">
+        <v>0.0702</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.04914</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.51513027052959</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1119984306744147</v>
+      </c>
+      <c r="C52">
+        <v>10.5284634354547</v>
+      </c>
+      <c r="D52">
+        <v>15.8894634354547</v>
+      </c>
+      <c r="E52">
+        <v>9.588999999999999</v>
+      </c>
+      <c r="F52">
+        <v>9.610999999999999</v>
+      </c>
+      <c r="G52">
+        <v>4.25</v>
+      </c>
+      <c r="H52">
+        <v>19.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.74</v>
+      </c>
+      <c r="K52">
+        <v>0.077</v>
+      </c>
+      <c r="L52">
+        <v>1.663</v>
+      </c>
+      <c r="M52">
+        <v>0.7198638999999999</v>
+      </c>
+      <c r="N52">
+        <v>0.9431361000000001</v>
+      </c>
+      <c r="O52">
+        <v>0.28294083</v>
+      </c>
+      <c r="P52">
+        <v>0.6601952700000001</v>
+      </c>
+      <c r="Q52">
+        <v>0.7371952700000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1715668613488295</v>
+      </c>
+      <c r="T52">
+        <v>0.8528888584106624</v>
+      </c>
+      <c r="U52">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V52">
+        <v>0.3</v>
+      </c>
+      <c r="W52">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.310158906426618</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1119004362132109</v>
+      </c>
+      <c r="C53">
+        <v>10.35559428511799</v>
+      </c>
+      <c r="D53">
+        <v>15.90881428511799</v>
+      </c>
+      <c r="E53">
+        <v>9.781219999999999</v>
+      </c>
+      <c r="F53">
+        <v>9.80322</v>
+      </c>
+      <c r="G53">
+        <v>4.25</v>
+      </c>
+      <c r="H53">
+        <v>19.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.74</v>
+      </c>
+      <c r="K53">
+        <v>0.077</v>
+      </c>
+      <c r="L53">
+        <v>1.663</v>
+      </c>
+      <c r="M53">
+        <v>0.7342611779999999</v>
+      </c>
+      <c r="N53">
+        <v>0.9287388220000001</v>
+      </c>
+      <c r="O53">
+        <v>0.2786216466000001</v>
+      </c>
+      <c r="P53">
+        <v>0.6501171754000001</v>
+      </c>
+      <c r="Q53">
+        <v>0.7271171754000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1737982371698182</v>
+      </c>
+      <c r="T53">
+        <v>0.8672231249385728</v>
+      </c>
+      <c r="U53">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V53">
+        <v>0.3</v>
+      </c>
+      <c r="W53">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.264861672967273</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1118024417520071</v>
+      </c>
+      <c r="C54">
+        <v>10.1827723247909</v>
+      </c>
+      <c r="D54">
+        <v>15.92821232479089</v>
+      </c>
+      <c r="E54">
+        <v>9.973439999999998</v>
+      </c>
+      <c r="F54">
+        <v>9.995439999999999</v>
+      </c>
+      <c r="G54">
+        <v>4.25</v>
+      </c>
+      <c r="H54">
+        <v>19.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.74</v>
+      </c>
+      <c r="K54">
+        <v>0.077</v>
+      </c>
+      <c r="L54">
+        <v>1.663</v>
+      </c>
+      <c r="M54">
+        <v>0.7486584559999998</v>
+      </c>
+      <c r="N54">
+        <v>0.9143415440000002</v>
+      </c>
+      <c r="O54">
+        <v>0.2743024632000001</v>
+      </c>
+      <c r="P54">
+        <v>0.6400390808000002</v>
+      </c>
+      <c r="Q54">
+        <v>0.7170390808000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1761225869833481</v>
+      </c>
+      <c r="T54">
+        <v>0.8821546525718126</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.3</v>
+      </c>
+      <c r="W54">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.221306640794825</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1117044472908033</v>
+      </c>
+      <c r="C55">
+        <v>10.00999772730423</v>
+      </c>
+      <c r="D55">
+        <v>15.94765772730423</v>
+      </c>
+      <c r="E55">
+        <v>10.16566</v>
+      </c>
+      <c r="F55">
+        <v>10.18766</v>
+      </c>
+      <c r="G55">
+        <v>4.25</v>
+      </c>
+      <c r="H55">
+        <v>19.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.74</v>
+      </c>
+      <c r="K55">
+        <v>0.077</v>
+      </c>
+      <c r="L55">
+        <v>1.663</v>
+      </c>
+      <c r="M55">
+        <v>0.7630557339999999</v>
+      </c>
+      <c r="N55">
+        <v>0.8999442660000001</v>
+      </c>
+      <c r="O55">
+        <v>0.2699832798</v>
+      </c>
+      <c r="P55">
+        <v>0.6299609862000001</v>
+      </c>
+      <c r="Q55">
+        <v>0.7069609862</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1785458452995815</v>
+      </c>
+      <c r="T55">
+        <v>0.8977215643596584</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.3</v>
+      </c>
+      <c r="W55">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.179395194742092</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1116064528295995</v>
+      </c>
+      <c r="C56">
+        <v>9.837270666333858</v>
+      </c>
+      <c r="D56">
+        <v>15.96715066633386</v>
+      </c>
+      <c r="E56">
+        <v>10.35788</v>
+      </c>
+      <c r="F56">
+        <v>10.37988</v>
+      </c>
+      <c r="G56">
+        <v>4.25</v>
+      </c>
+      <c r="H56">
+        <v>19.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.74</v>
+      </c>
+      <c r="K56">
+        <v>0.077</v>
+      </c>
+      <c r="L56">
+        <v>1.663</v>
+      </c>
+      <c r="M56">
+        <v>0.7774530119999999</v>
+      </c>
+      <c r="N56">
+        <v>0.8855469880000001</v>
+      </c>
+      <c r="O56">
+        <v>0.2656640964</v>
+      </c>
+      <c r="P56">
+        <v>0.6198828916000001</v>
+      </c>
+      <c r="Q56">
+        <v>0.6968828916000001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1810744626730423</v>
+      </c>
+      <c r="T56">
+        <v>0.9139652983991498</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.3</v>
+      </c>
+      <c r="W56">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.139036024469091</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1115084583683957</v>
+      </c>
+      <c r="C57">
+        <v>9.664591316405783</v>
+      </c>
+      <c r="D57">
+        <v>15.98669131640578</v>
+      </c>
+      <c r="E57">
+        <v>10.5501</v>
+      </c>
+      <c r="F57">
+        <v>10.5721</v>
+      </c>
+      <c r="G57">
+        <v>4.25</v>
+      </c>
+      <c r="H57">
+        <v>19.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.74</v>
+      </c>
+      <c r="K57">
+        <v>0.077</v>
+      </c>
+      <c r="L57">
+        <v>1.663</v>
+      </c>
+      <c r="M57">
+        <v>0.7918502899999998</v>
+      </c>
+      <c r="N57">
+        <v>0.8711497100000002</v>
+      </c>
+      <c r="O57">
+        <v>0.2613449130000001</v>
+      </c>
+      <c r="P57">
+        <v>0.6098047970000001</v>
+      </c>
+      <c r="Q57">
+        <v>0.6868047970000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1837154630408792</v>
+      </c>
+      <c r="T57">
+        <v>0.9309309761737297</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.3</v>
+      </c>
+      <c r="W57">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.100144460387835</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1114104639071918</v>
+      </c>
+      <c r="C58">
+        <v>9.491959852901426</v>
+      </c>
+      <c r="D58">
+        <v>16.00627985290143</v>
+      </c>
+      <c r="E58">
+        <v>10.74232</v>
+      </c>
+      <c r="F58">
+        <v>10.76432</v>
+      </c>
+      <c r="G58">
+        <v>4.25</v>
+      </c>
+      <c r="H58">
+        <v>19.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.74</v>
+      </c>
+      <c r="K58">
+        <v>0.077</v>
+      </c>
+      <c r="L58">
+        <v>1.663</v>
+      </c>
+      <c r="M58">
+        <v>0.8062475679999999</v>
+      </c>
+      <c r="N58">
+        <v>0.8567524320000002</v>
+      </c>
+      <c r="O58">
+        <v>0.2570257296</v>
+      </c>
+      <c r="P58">
+        <v>0.5997267024000001</v>
+      </c>
+      <c r="Q58">
+        <v>0.6767267024000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1864765088799815</v>
+      </c>
+      <c r="T58">
+        <v>0.9486678211198813</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.3</v>
+      </c>
+      <c r="W58">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.062641880738052</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.111312469445988</v>
+      </c>
+      <c r="C59">
+        <v>9.319376452062823</v>
+      </c>
+      <c r="D59">
+        <v>16.02591645206282</v>
+      </c>
+      <c r="E59">
+        <v>10.93454</v>
+      </c>
+      <c r="F59">
+        <v>10.95654</v>
+      </c>
+      <c r="G59">
+        <v>4.25</v>
+      </c>
+      <c r="H59">
+        <v>19.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.74</v>
+      </c>
+      <c r="K59">
+        <v>0.077</v>
+      </c>
+      <c r="L59">
+        <v>1.663</v>
+      </c>
+      <c r="M59">
+        <v>0.820644846</v>
+      </c>
+      <c r="N59">
+        <v>0.8423551540000001</v>
+      </c>
+      <c r="O59">
+        <v>0.2527065462</v>
+      </c>
+      <c r="P59">
+        <v>0.5896486078000001</v>
+      </c>
+      <c r="Q59">
+        <v>0.6666486078</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1893659754557861</v>
+      </c>
+      <c r="T59">
+        <v>0.967229635598412</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.3</v>
+      </c>
+      <c r="W59">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.02645518107598</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1178322749847842</v>
+      </c>
+      <c r="C60">
+        <v>7.91779474677905</v>
+      </c>
+      <c r="D60">
+        <v>14.81655474677905</v>
+      </c>
+      <c r="E60">
+        <v>11.12676</v>
+      </c>
+      <c r="F60">
+        <v>11.14876</v>
+      </c>
+      <c r="G60">
+        <v>4.25</v>
+      </c>
+      <c r="H60">
+        <v>19.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.74</v>
+      </c>
+      <c r="K60">
+        <v>0.077</v>
+      </c>
+      <c r="L60">
+        <v>1.663</v>
+      </c>
+      <c r="M60">
+        <v>1.016766912</v>
+      </c>
+      <c r="N60">
+        <v>0.6462330880000002</v>
+      </c>
+      <c r="O60">
+        <v>0.1938699264000001</v>
+      </c>
+      <c r="P60">
+        <v>0.4523631616000002</v>
+      </c>
+      <c r="Q60">
+        <v>0.5293631616000002</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1923930356780576</v>
+      </c>
+      <c r="T60">
+        <v>0.9866753460044917</v>
+      </c>
+      <c r="U60">
+        <v>0.0912</v>
+      </c>
+      <c r="V60">
+        <v>0.3</v>
+      </c>
+      <c r="W60">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>1.635576433864127</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1178483805235804</v>
+      </c>
+      <c r="C61">
+        <v>7.722813277387541</v>
+      </c>
+      <c r="D61">
+        <v>14.81379327738754</v>
+      </c>
+      <c r="E61">
+        <v>11.31898</v>
+      </c>
+      <c r="F61">
+        <v>11.34098</v>
+      </c>
+      <c r="G61">
+        <v>4.25</v>
+      </c>
+      <c r="H61">
+        <v>19.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.74</v>
+      </c>
+      <c r="K61">
+        <v>0.077</v>
+      </c>
+      <c r="L61">
+        <v>1.663</v>
+      </c>
+      <c r="M61">
+        <v>1.034297376</v>
+      </c>
+      <c r="N61">
+        <v>0.6287026240000002</v>
+      </c>
+      <c r="O61">
+        <v>0.1886107872</v>
+      </c>
+      <c r="P61">
+        <v>0.4400918368000002</v>
+      </c>
+      <c r="Q61">
+        <v>0.5170918368000001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1955677573745863</v>
+      </c>
+      <c r="T61">
+        <v>1.007069627649892</v>
+      </c>
+      <c r="U61">
+        <v>0.0912</v>
+      </c>
+      <c r="V61">
+        <v>0.3</v>
+      </c>
+      <c r="W61">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>1.607854799391853</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1178644860623766</v>
+      </c>
+      <c r="C62">
+        <v>7.5278328371546</v>
+      </c>
+      <c r="D62">
+        <v>14.8110328371546</v>
+      </c>
+      <c r="E62">
+        <v>11.5112</v>
+      </c>
+      <c r="F62">
+        <v>11.5332</v>
+      </c>
+      <c r="G62">
+        <v>4.25</v>
+      </c>
+      <c r="H62">
+        <v>19.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.74</v>
+      </c>
+      <c r="K62">
+        <v>0.077</v>
+      </c>
+      <c r="L62">
+        <v>1.663</v>
+      </c>
+      <c r="M62">
+        <v>1.05182784</v>
+      </c>
+      <c r="N62">
+        <v>0.6111721600000002</v>
+      </c>
+      <c r="O62">
+        <v>0.1833516480000001</v>
+      </c>
+      <c r="P62">
+        <v>0.4278205120000002</v>
+      </c>
+      <c r="Q62">
+        <v>0.5048205120000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1989012151559414</v>
+      </c>
+      <c r="T62">
+        <v>1.028483623377563</v>
+      </c>
+      <c r="U62">
+        <v>0.0912</v>
+      </c>
+      <c r="V62">
+        <v>0.3</v>
+      </c>
+      <c r="W62">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>1.581057219401989</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1178805916011727</v>
+      </c>
+      <c r="C63">
+        <v>7.33285342550503</v>
+      </c>
+      <c r="D63">
+        <v>14.80827342550503</v>
+      </c>
+      <c r="E63">
+        <v>11.70342</v>
+      </c>
+      <c r="F63">
+        <v>11.72542</v>
+      </c>
+      <c r="G63">
+        <v>4.25</v>
+      </c>
+      <c r="H63">
+        <v>19.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.74</v>
+      </c>
+      <c r="K63">
+        <v>0.077</v>
+      </c>
+      <c r="L63">
+        <v>1.663</v>
+      </c>
+      <c r="M63">
+        <v>1.069358304</v>
+      </c>
+      <c r="N63">
+        <v>0.5936416960000002</v>
+      </c>
+      <c r="O63">
+        <v>0.1780925088</v>
+      </c>
+      <c r="P63">
+        <v>0.4155491872000001</v>
+      </c>
+      <c r="Q63">
+        <v>0.4925491872000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2024056194901865</v>
+      </c>
+      <c r="T63">
+        <v>1.050995772732294</v>
+      </c>
+      <c r="U63">
+        <v>0.0912</v>
+      </c>
+      <c r="V63">
+        <v>0.3</v>
+      </c>
+      <c r="W63">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.55513824859212</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1178966971399689</v>
+      </c>
+      <c r="C64">
+        <v>7.137875041864014</v>
+      </c>
+      <c r="D64">
+        <v>14.80551504186401</v>
+      </c>
+      <c r="E64">
+        <v>11.89564</v>
+      </c>
+      <c r="F64">
+        <v>11.91764</v>
+      </c>
+      <c r="G64">
+        <v>4.25</v>
+      </c>
+      <c r="H64">
+        <v>19.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.74</v>
+      </c>
+      <c r="K64">
+        <v>0.077</v>
+      </c>
+      <c r="L64">
+        <v>1.663</v>
+      </c>
+      <c r="M64">
+        <v>1.086888768</v>
+      </c>
+      <c r="N64">
+        <v>0.5761112320000001</v>
+      </c>
+      <c r="O64">
+        <v>0.1728333696</v>
+      </c>
+      <c r="P64">
+        <v>0.4032778624000001</v>
+      </c>
+      <c r="Q64">
+        <v>0.4802778624000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.206094466157813</v>
+      </c>
+      <c r="T64">
+        <v>1.074692772053064</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.3</v>
+      </c>
+      <c r="W64">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.530055373614828</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1179128026787651</v>
+      </c>
+      <c r="C65">
+        <v>6.942897685657199</v>
+      </c>
+      <c r="D65">
+        <v>14.8027576856572</v>
+      </c>
+      <c r="E65">
+        <v>12.08786</v>
+      </c>
+      <c r="F65">
+        <v>12.10986</v>
+      </c>
+      <c r="G65">
+        <v>4.25</v>
+      </c>
+      <c r="H65">
+        <v>19.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.74</v>
+      </c>
+      <c r="K65">
+        <v>0.077</v>
+      </c>
+      <c r="L65">
+        <v>1.663</v>
+      </c>
+      <c r="M65">
+        <v>1.104419232</v>
+      </c>
+      <c r="N65">
+        <v>0.5585807680000001</v>
+      </c>
+      <c r="O65">
+        <v>0.1675742304</v>
+      </c>
+      <c r="P65">
+        <v>0.3910065376000001</v>
+      </c>
+      <c r="Q65">
+        <v>0.4680065376000001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2099827099426084</v>
+      </c>
+      <c r="T65">
+        <v>1.099670690256037</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.3</v>
+      </c>
+      <c r="W65">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.505768780382847</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1533916544435385</v>
+      </c>
+      <c r="C66">
+        <v>2.444362716930605</v>
+      </c>
+      <c r="D66">
+        <v>10.4964427169306</v>
+      </c>
+      <c r="E66">
+        <v>12.28008</v>
+      </c>
+      <c r="F66">
+        <v>12.30208</v>
+      </c>
+      <c r="G66">
+        <v>4.25</v>
+      </c>
+      <c r="H66">
+        <v>19.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.74</v>
+      </c>
+      <c r="K66">
+        <v>0.077</v>
+      </c>
+      <c r="L66">
+        <v>1.663</v>
+      </c>
+      <c r="M66">
+        <v>1.926505728</v>
+      </c>
+      <c r="N66">
+        <v>-0.2635057279999999</v>
+      </c>
+      <c r="O66">
+        <v>-0.07905171839999998</v>
+      </c>
+      <c r="P66">
+        <v>-0.1844540096</v>
+      </c>
+      <c r="Q66">
+        <v>-0.1074540096</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2197841382145599</v>
+      </c>
+      <c r="T66">
+        <v>1.162634662475693</v>
+      </c>
+      <c r="U66">
+        <v>0.1566</v>
+      </c>
+      <c r="V66">
+        <v>0.2589662686951533</v>
+      </c>
+      <c r="W66">
+        <v>0.116045882322339</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8632208956505112</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1545696544435385</v>
+      </c>
+      <c r="C67">
+        <v>2.151725946249261</v>
+      </c>
+      <c r="D67">
+        <v>10.39602594624926</v>
+      </c>
+      <c r="E67">
+        <v>12.4723</v>
+      </c>
+      <c r="F67">
+        <v>12.4943</v>
+      </c>
+      <c r="G67">
+        <v>4.25</v>
+      </c>
+      <c r="H67">
+        <v>19.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.74</v>
+      </c>
+      <c r="K67">
+        <v>0.077</v>
+      </c>
+      <c r="L67">
+        <v>1.663</v>
+      </c>
+      <c r="M67">
+        <v>1.95660738</v>
+      </c>
+      <c r="N67">
+        <v>-0.2936073800000001</v>
+      </c>
+      <c r="O67">
+        <v>-0.08808221400000002</v>
+      </c>
+      <c r="P67">
+        <v>-0.2055251660000001</v>
+      </c>
+      <c r="Q67">
+        <v>-0.1285251660000001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2249551135921188</v>
+      </c>
+      <c r="T67">
+        <v>1.195852795689285</v>
+      </c>
+      <c r="U67">
+        <v>0.1566</v>
+      </c>
+      <c r="V67">
+        <v>0.2549821722536894</v>
+      </c>
+      <c r="W67">
+        <v>0.1166697918250723</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.8499405741789647</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1557476544435386</v>
+      </c>
+      <c r="C68">
+        <v>1.860992291834744</v>
+      </c>
+      <c r="D68">
+        <v>10.29751229183474</v>
+      </c>
+      <c r="E68">
+        <v>12.66452</v>
+      </c>
+      <c r="F68">
+        <v>12.68652</v>
+      </c>
+      <c r="G68">
+        <v>4.25</v>
+      </c>
+      <c r="H68">
+        <v>19.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.74</v>
+      </c>
+      <c r="K68">
+        <v>0.077</v>
+      </c>
+      <c r="L68">
+        <v>1.663</v>
+      </c>
+      <c r="M68">
+        <v>1.986709032</v>
+      </c>
+      <c r="N68">
+        <v>-0.3237090320000002</v>
+      </c>
+      <c r="O68">
+        <v>-0.09711270960000007</v>
+      </c>
+      <c r="P68">
+        <v>-0.2265963224000002</v>
+      </c>
+      <c r="Q68">
+        <v>-0.1495963224000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.230430263991887</v>
+      </c>
+      <c r="T68">
+        <v>1.23102493673897</v>
+      </c>
+      <c r="U68">
+        <v>0.1566</v>
+      </c>
+      <c r="V68">
+        <v>0.2511188060074214</v>
+      </c>
+      <c r="W68">
+        <v>0.1172747949792378</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8370626866914046</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1569256544435385</v>
+      </c>
+      <c r="C69">
+        <v>1.57210815926214</v>
+      </c>
+      <c r="D69">
+        <v>10.20084815926214</v>
+      </c>
+      <c r="E69">
+        <v>12.85674</v>
+      </c>
+      <c r="F69">
+        <v>12.87874</v>
+      </c>
+      <c r="G69">
+        <v>4.25</v>
+      </c>
+      <c r="H69">
+        <v>19.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.74</v>
+      </c>
+      <c r="K69">
+        <v>0.077</v>
+      </c>
+      <c r="L69">
+        <v>1.663</v>
+      </c>
+      <c r="M69">
+        <v>2.016810684</v>
+      </c>
+      <c r="N69">
+        <v>-0.3538106840000002</v>
+      </c>
+      <c r="O69">
+        <v>-0.1061432052</v>
+      </c>
+      <c r="P69">
+        <v>-0.2476674788000001</v>
+      </c>
+      <c r="Q69">
+        <v>-0.1706674788000001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2362372416886108</v>
+      </c>
+      <c r="T69">
+        <v>1.268328722700757</v>
+      </c>
+      <c r="U69">
+        <v>0.1566</v>
+      </c>
+      <c r="V69">
+        <v>0.2473707641267136</v>
+      </c>
+      <c r="W69">
+        <v>0.1178617383377566</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.8245692137557121</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1581036544435385</v>
+      </c>
+      <c r="C70">
+        <v>1.2850219477839</v>
+      </c>
+      <c r="D70">
+        <v>10.1059819477839</v>
+      </c>
+      <c r="E70">
+        <v>13.04896</v>
+      </c>
+      <c r="F70">
+        <v>13.07096</v>
+      </c>
+      <c r="G70">
+        <v>4.25</v>
+      </c>
+      <c r="H70">
+        <v>19.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.74</v>
+      </c>
+      <c r="K70">
+        <v>0.077</v>
+      </c>
+      <c r="L70">
+        <v>1.663</v>
+      </c>
+      <c r="M70">
+        <v>2.046912336</v>
+      </c>
+      <c r="N70">
+        <v>-0.3839123360000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.1151737008</v>
+      </c>
+      <c r="P70">
+        <v>-0.2687386352000001</v>
+      </c>
+      <c r="Q70">
+        <v>-0.1917386352000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2424071554913799</v>
+      </c>
+      <c r="T70">
+        <v>1.307963995285155</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.243732958771909</v>
+      </c>
+      <c r="W70">
+        <v>0.1184314186563191</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8124431959063634</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1592816544435385</v>
+      </c>
+      <c r="C71">
+        <v>0.9996839584796966</v>
+      </c>
+      <c r="D71">
+        <v>10.0128639584797</v>
+      </c>
+      <c r="E71">
+        <v>13.24118</v>
+      </c>
+      <c r="F71">
+        <v>13.26318</v>
+      </c>
+      <c r="G71">
+        <v>4.25</v>
+      </c>
+      <c r="H71">
+        <v>19.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.74</v>
+      </c>
+      <c r="K71">
+        <v>0.077</v>
+      </c>
+      <c r="L71">
+        <v>1.663</v>
+      </c>
+      <c r="M71">
+        <v>2.077013988</v>
+      </c>
+      <c r="N71">
+        <v>-0.414013988</v>
+      </c>
+      <c r="O71">
+        <v>-0.1242041964</v>
+      </c>
+      <c r="P71">
+        <v>-0.2898097916</v>
+      </c>
+      <c r="Q71">
+        <v>-0.2128097916</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2489751282491664</v>
+      </c>
+      <c r="T71">
+        <v>1.350156382229838</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.240200597050577</v>
+      </c>
+      <c r="W71">
+        <v>0.1189845865018797</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8006686568352567</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2002356204378795</v>
+      </c>
+      <c r="C72">
+        <v>-1.621827357320898</v>
+      </c>
+      <c r="D72">
+        <v>7.583572642679101</v>
+      </c>
+      <c r="E72">
+        <v>13.4334</v>
+      </c>
+      <c r="F72">
+        <v>13.4554</v>
+      </c>
+      <c r="G72">
+        <v>4.25</v>
+      </c>
+      <c r="H72">
+        <v>19.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.74</v>
+      </c>
+      <c r="K72">
+        <v>0.077</v>
+      </c>
+      <c r="L72">
+        <v>1.663</v>
+      </c>
+      <c r="M72">
+        <v>2.80948752</v>
+      </c>
+      <c r="N72">
+        <v>-1.14648752</v>
+      </c>
+      <c r="O72">
+        <v>-0.3439462559999999</v>
+      </c>
+      <c r="P72">
+        <v>-0.8025412639999998</v>
+      </c>
+      <c r="Q72">
+        <v>-0.7255412639999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.266767519171942</v>
+      </c>
+      <c r="T72">
+        <v>1.464453969958841</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1775768699623909</v>
+      </c>
+      <c r="W72">
+        <v>0.1717219495518528</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5919228998746362</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2019356204378795</v>
+      </c>
+      <c r="C73">
+        <v>-1.889660305311393</v>
+      </c>
+      <c r="D73">
+        <v>7.507959694688604</v>
+      </c>
+      <c r="E73">
+        <v>13.62562</v>
+      </c>
+      <c r="F73">
+        <v>13.64762</v>
+      </c>
+      <c r="G73">
+        <v>4.25</v>
+      </c>
+      <c r="H73">
+        <v>19.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.74</v>
+      </c>
+      <c r="K73">
+        <v>0.077</v>
+      </c>
+      <c r="L73">
+        <v>1.663</v>
+      </c>
+      <c r="M73">
+        <v>2.849623056</v>
+      </c>
+      <c r="N73">
+        <v>-1.186623056</v>
+      </c>
+      <c r="O73">
+        <v>-0.3559869168</v>
+      </c>
+      <c r="P73">
+        <v>-0.8306361391999999</v>
+      </c>
+      <c r="Q73">
+        <v>-0.7536361391999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2746284681089054</v>
+      </c>
+      <c r="T73">
+        <v>1.514952382716042</v>
+      </c>
+      <c r="U73">
+        <v>0.2088</v>
+      </c>
+      <c r="V73">
+        <v>0.1750757872868642</v>
+      </c>
+      <c r="W73">
+        <v>0.1722441756145028</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5835859576228808</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2036356204378795</v>
+      </c>
+      <c r="C74">
+        <v>-2.156000322275183</v>
+      </c>
+      <c r="D74">
+        <v>7.433839677724814</v>
+      </c>
+      <c r="E74">
+        <v>13.81784</v>
+      </c>
+      <c r="F74">
+        <v>13.83984</v>
+      </c>
+      <c r="G74">
+        <v>4.25</v>
+      </c>
+      <c r="H74">
+        <v>19.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.74</v>
+      </c>
+      <c r="K74">
+        <v>0.077</v>
+      </c>
+      <c r="L74">
+        <v>1.663</v>
+      </c>
+      <c r="M74">
+        <v>2.889758592</v>
+      </c>
+      <c r="N74">
+        <v>-1.226758592</v>
+      </c>
+      <c r="O74">
+        <v>-0.3680275775999999</v>
+      </c>
+      <c r="P74">
+        <v>-0.8587310143999998</v>
+      </c>
+      <c r="Q74">
+        <v>-0.7817310143999998</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2830509133985092</v>
+      </c>
+      <c r="T74">
+        <v>1.569057824955901</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.1726441791301022</v>
+      </c>
+      <c r="W74">
+        <v>0.1727518953976347</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5754805971003408</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2053356204378795</v>
+      </c>
+      <c r="C75">
+        <v>-2.420891191479088</v>
+      </c>
+      <c r="D75">
+        <v>7.36116880852091</v>
+      </c>
+      <c r="E75">
+        <v>14.01006</v>
+      </c>
+      <c r="F75">
+        <v>14.03206</v>
+      </c>
+      <c r="G75">
+        <v>4.25</v>
+      </c>
+      <c r="H75">
+        <v>19.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.74</v>
+      </c>
+      <c r="K75">
+        <v>0.077</v>
+      </c>
+      <c r="L75">
+        <v>1.663</v>
+      </c>
+      <c r="M75">
+        <v>2.929894128</v>
+      </c>
+      <c r="N75">
+        <v>-1.266894128</v>
+      </c>
+      <c r="O75">
+        <v>-0.3800682384</v>
+      </c>
+      <c r="P75">
+        <v>-0.8868258895999999</v>
+      </c>
+      <c r="Q75">
+        <v>-0.8098258895999999</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2920972435243799</v>
+      </c>
+      <c r="T75">
+        <v>1.627171077732045</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.1702791903748953</v>
+      </c>
+      <c r="W75">
+        <v>0.1732457050497219</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5675973012496511</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2070356204378795</v>
+      </c>
+      <c r="C76">
+        <v>-2.684375000718754</v>
+      </c>
+      <c r="D76">
+        <v>7.289904999281243</v>
+      </c>
+      <c r="E76">
+        <v>14.20228</v>
+      </c>
+      <c r="F76">
+        <v>14.22428</v>
+      </c>
+      <c r="G76">
+        <v>4.25</v>
+      </c>
+      <c r="H76">
+        <v>19.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.74</v>
+      </c>
+      <c r="K76">
+        <v>0.077</v>
+      </c>
+      <c r="L76">
+        <v>1.663</v>
+      </c>
+      <c r="M76">
+        <v>2.970029664</v>
+      </c>
+      <c r="N76">
+        <v>-1.307029664</v>
+      </c>
+      <c r="O76">
+        <v>-0.3921088991999999</v>
+      </c>
+      <c r="P76">
+        <v>-0.9149207647999997</v>
+      </c>
+      <c r="Q76">
+        <v>-0.8379207647999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3018394451983945</v>
+      </c>
+      <c r="T76">
+        <v>1.689754580721739</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.1679781202346941</v>
+      </c>
+      <c r="W76">
+        <v>0.1737261684949959</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5599270674489802</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2087356204378795</v>
+      </c>
+      <c r="C77">
+        <v>-2.94649222360143</v>
+      </c>
+      <c r="D77">
+        <v>7.220007776398569</v>
+      </c>
+      <c r="E77">
+        <v>14.3945</v>
+      </c>
+      <c r="F77">
+        <v>14.4165</v>
+      </c>
+      <c r="G77">
+        <v>4.25</v>
+      </c>
+      <c r="H77">
+        <v>19.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.74</v>
+      </c>
+      <c r="K77">
+        <v>0.077</v>
+      </c>
+      <c r="L77">
+        <v>1.663</v>
+      </c>
+      <c r="M77">
+        <v>3.0101652</v>
+      </c>
+      <c r="N77">
+        <v>-1.3471652</v>
+      </c>
+      <c r="O77">
+        <v>-0.40414956</v>
+      </c>
+      <c r="P77">
+        <v>-0.9430156399999998</v>
+      </c>
+      <c r="Q77">
+        <v>-0.8660156399999999</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3123610230063303</v>
+      </c>
+      <c r="T77">
+        <v>1.757344763950609</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1657384119648981</v>
+      </c>
+      <c r="W77">
+        <v>0.1741938195817293</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5524613732163272</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2104356204378795</v>
+      </c>
+      <c r="C78">
+        <v>-3.20728179619698</v>
+      </c>
+      <c r="D78">
+        <v>7.151438203803017</v>
+      </c>
+      <c r="E78">
+        <v>14.58672</v>
+      </c>
+      <c r="F78">
+        <v>14.60872</v>
+      </c>
+      <c r="G78">
+        <v>4.25</v>
+      </c>
+      <c r="H78">
+        <v>19.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.74</v>
+      </c>
+      <c r="K78">
+        <v>0.077</v>
+      </c>
+      <c r="L78">
+        <v>1.663</v>
+      </c>
+      <c r="M78">
+        <v>3.050300736</v>
+      </c>
+      <c r="N78">
+        <v>-1.387300736</v>
+      </c>
+      <c r="O78">
+        <v>-0.4161902207999998</v>
+      </c>
+      <c r="P78">
+        <v>-0.9711105151999997</v>
+      </c>
+      <c r="Q78">
+        <v>-0.8941105151999997</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3237593989649274</v>
+      </c>
+      <c r="T78">
+        <v>1.830567462448551</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1635576433864127</v>
+      </c>
+      <c r="W78">
+        <v>0.174649164060917</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5451921446213756</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2121356204378795</v>
+      </c>
+      <c r="C79">
+        <v>-3.466781189362228</v>
+      </c>
+      <c r="D79">
+        <v>7.084158810637771</v>
+      </c>
+      <c r="E79">
+        <v>14.77894</v>
+      </c>
+      <c r="F79">
+        <v>14.80094</v>
+      </c>
+      <c r="G79">
+        <v>4.25</v>
+      </c>
+      <c r="H79">
+        <v>19.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.74</v>
+      </c>
+      <c r="K79">
+        <v>0.077</v>
+      </c>
+      <c r="L79">
+        <v>1.663</v>
+      </c>
+      <c r="M79">
+        <v>3.090436272</v>
+      </c>
+      <c r="N79">
+        <v>-1.427436272</v>
+      </c>
+      <c r="O79">
+        <v>-0.4282308815999999</v>
+      </c>
+      <c r="P79">
+        <v>-0.9992053903999998</v>
+      </c>
+      <c r="Q79">
+        <v>-0.9222053903999998</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.336148938050359</v>
+      </c>
+      <c r="T79">
+        <v>1.910157352120228</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.161433518147628</v>
+      </c>
+      <c r="W79">
+        <v>0.1750926814107753</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5381117271587602</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2138356204378795</v>
+      </c>
+      <c r="C80">
+        <v>-3.725026477020815</v>
+      </c>
+      <c r="D80">
+        <v>7.018133522979183</v>
+      </c>
+      <c r="E80">
+        <v>14.97116</v>
+      </c>
+      <c r="F80">
+        <v>14.99316</v>
+      </c>
+      <c r="G80">
+        <v>4.25</v>
+      </c>
+      <c r="H80">
+        <v>19.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.74</v>
+      </c>
+      <c r="K80">
+        <v>0.077</v>
+      </c>
+      <c r="L80">
+        <v>1.663</v>
+      </c>
+      <c r="M80">
+        <v>3.130571808</v>
+      </c>
+      <c r="N80">
+        <v>-1.467571808</v>
+      </c>
+      <c r="O80">
+        <v>-0.4402715424</v>
+      </c>
+      <c r="P80">
+        <v>-1.0273002656</v>
+      </c>
+      <c r="Q80">
+        <v>-0.9503002656000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3496647988708299</v>
+      </c>
+      <c r="T80">
+        <v>1.996982686307511</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.1593638576585559</v>
+      </c>
+      <c r="W80">
+        <v>0.1755248265208935</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.531212858861853</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2155356204378795</v>
+      </c>
+      <c r="C81">
+        <v>-3.982052400660105</v>
+      </c>
+      <c r="D81">
+        <v>6.953327599339893</v>
+      </c>
+      <c r="E81">
+        <v>15.16338</v>
+      </c>
+      <c r="F81">
+        <v>15.18538</v>
+      </c>
+      <c r="G81">
+        <v>4.25</v>
+      </c>
+      <c r="H81">
+        <v>19.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.74</v>
+      </c>
+      <c r="K81">
+        <v>0.077</v>
+      </c>
+      <c r="L81">
+        <v>1.663</v>
+      </c>
+      <c r="M81">
+        <v>3.170707344</v>
+      </c>
+      <c r="N81">
+        <v>-1.507707344</v>
+      </c>
+      <c r="O81">
+        <v>-0.4523122031999999</v>
+      </c>
+      <c r="P81">
+        <v>-1.0553951408</v>
+      </c>
+      <c r="Q81">
+        <v>-0.9783951408</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3644678845313456</v>
+      </c>
+      <c r="T81">
+        <v>2.092077099941202</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.1573465936375615</v>
+      </c>
+      <c r="W81">
+        <v>0.1759460312484772</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5244886454585385</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2172356204378796</v>
+      </c>
+      <c r="C82">
+        <v>-4.237892430287348</v>
+      </c>
+      <c r="D82">
+        <v>6.889707569712653</v>
+      </c>
+      <c r="E82">
+        <v>15.3556</v>
+      </c>
+      <c r="F82">
+        <v>15.3776</v>
+      </c>
+      <c r="G82">
+        <v>4.25</v>
+      </c>
+      <c r="H82">
+        <v>19.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.74</v>
+      </c>
+      <c r="K82">
+        <v>0.077</v>
+      </c>
+      <c r="L82">
+        <v>1.663</v>
+      </c>
+      <c r="M82">
+        <v>3.21084288</v>
+      </c>
+      <c r="N82">
+        <v>-1.54784288</v>
+      </c>
+      <c r="O82">
+        <v>-0.464352864</v>
+      </c>
+      <c r="P82">
+        <v>-1.083490016</v>
+      </c>
+      <c r="Q82">
+        <v>-1.006490016</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3807512787579129</v>
+      </c>
+      <c r="T82">
+        <v>2.196680954938262</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.155379761217092</v>
+      </c>
+      <c r="W82">
+        <v>0.1763567058578712</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5179325373903068</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2189356204378795</v>
+      </c>
+      <c r="C83">
+        <v>-4.492578822069813</v>
+      </c>
+      <c r="D83">
+        <v>6.827241177930187</v>
+      </c>
+      <c r="E83">
+        <v>15.54782</v>
+      </c>
+      <c r="F83">
+        <v>15.56982</v>
+      </c>
+      <c r="G83">
+        <v>4.25</v>
+      </c>
+      <c r="H83">
+        <v>19.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.74</v>
+      </c>
+      <c r="K83">
+        <v>0.077</v>
+      </c>
+      <c r="L83">
+        <v>1.663</v>
+      </c>
+      <c r="M83">
+        <v>3.250978416</v>
+      </c>
+      <c r="N83">
+        <v>-1.587978416</v>
+      </c>
+      <c r="O83">
+        <v>-0.4763935248</v>
+      </c>
+      <c r="P83">
+        <v>-1.1115848912</v>
+      </c>
+      <c r="Q83">
+        <v>-1.0345848912</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3987487144820136</v>
+      </c>
+      <c r="T83">
+        <v>2.312295742040276</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.1534614925600909</v>
+      </c>
+      <c r="W83">
+        <v>0.176757240353453</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5115383085336362</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2206356204378795</v>
+      </c>
+      <c r="C84">
+        <v>-4.746142672867569</v>
+      </c>
+      <c r="D84">
+        <v>6.76589732713243</v>
+      </c>
+      <c r="E84">
+        <v>15.74004</v>
+      </c>
+      <c r="F84">
+        <v>15.76204</v>
+      </c>
+      <c r="G84">
+        <v>4.25</v>
+      </c>
+      <c r="H84">
+        <v>19.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.74</v>
+      </c>
+      <c r="K84">
+        <v>0.077</v>
+      </c>
+      <c r="L84">
+        <v>1.663</v>
+      </c>
+      <c r="M84">
+        <v>3.291113952</v>
+      </c>
+      <c r="N84">
+        <v>-1.628113952</v>
+      </c>
+      <c r="O84">
+        <v>-0.4884341856</v>
+      </c>
+      <c r="P84">
+        <v>-1.1396797664</v>
+      </c>
+      <c r="Q84">
+        <v>-1.0626797664</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4187458652865699</v>
+      </c>
+      <c r="T84">
+        <v>2.440756616598069</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1515900109435044</v>
+      </c>
+      <c r="W84">
+        <v>0.1771480057149963</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.505300036478348</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2484552056116262</v>
+      </c>
+      <c r="C85">
+        <v>-5.80567472387265</v>
+      </c>
+      <c r="D85">
+        <v>5.898585276127349</v>
+      </c>
+      <c r="E85">
+        <v>15.93226</v>
+      </c>
+      <c r="F85">
+        <v>15.95426</v>
+      </c>
+      <c r="G85">
+        <v>4.25</v>
+      </c>
+      <c r="H85">
+        <v>19.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.74</v>
+      </c>
+      <c r="K85">
+        <v>0.077</v>
+      </c>
+      <c r="L85">
+        <v>1.663</v>
+      </c>
+      <c r="M85">
+        <v>3.809877288</v>
+      </c>
+      <c r="N85">
+        <v>-2.146877288</v>
+      </c>
+      <c r="O85">
+        <v>-0.6440631863999999</v>
+      </c>
+      <c r="P85">
+        <v>-1.5028141016</v>
+      </c>
+      <c r="Q85">
+        <v>-1.4258141016</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4482696525019365</v>
+      </c>
+      <c r="T85">
+        <v>2.630416211757997</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.1309490994818624</v>
+      </c>
+      <c r="W85">
+        <v>0.2075293550437313</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4364969982728746</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2504552056116262</v>
+      </c>
+      <c r="C86">
+        <v>-6.051758051332673</v>
+      </c>
+      <c r="D86">
+        <v>5.844721948667323</v>
+      </c>
+      <c r="E86">
+        <v>16.12448</v>
+      </c>
+      <c r="F86">
+        <v>16.14648</v>
+      </c>
+      <c r="G86">
+        <v>4.25</v>
+      </c>
+      <c r="H86">
+        <v>19.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.74</v>
+      </c>
+      <c r="K86">
+        <v>0.077</v>
+      </c>
+      <c r="L86">
+        <v>1.663</v>
+      </c>
+      <c r="M86">
+        <v>3.855779424</v>
+      </c>
+      <c r="N86">
+        <v>-2.192779423999999</v>
+      </c>
+      <c r="O86">
+        <v>-0.6578338271999998</v>
+      </c>
+      <c r="P86">
+        <v>-1.5349455968</v>
+      </c>
+      <c r="Q86">
+        <v>-1.4579455968</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4738615057833073</v>
+      </c>
+      <c r="T86">
+        <v>2.794817224992871</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.1293901816308878</v>
+      </c>
+      <c r="W86">
+        <v>0.207901624626544</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4313006054362928</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2524552056116262</v>
+      </c>
+      <c r="C87">
+        <v>-6.296866567168689</v>
+      </c>
+      <c r="D87">
+        <v>5.791833432831312</v>
+      </c>
+      <c r="E87">
+        <v>16.3167</v>
+      </c>
+      <c r="F87">
+        <v>16.3387</v>
+      </c>
+      <c r="G87">
+        <v>4.25</v>
+      </c>
+      <c r="H87">
+        <v>19.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.74</v>
+      </c>
+      <c r="K87">
+        <v>0.077</v>
+      </c>
+      <c r="L87">
+        <v>1.663</v>
+      </c>
+      <c r="M87">
+        <v>3.90168156</v>
+      </c>
+      <c r="N87">
+        <v>-2.23868156</v>
+      </c>
+      <c r="O87">
+        <v>-0.671604468</v>
+      </c>
+      <c r="P87">
+        <v>-1.567077092</v>
+      </c>
+      <c r="Q87">
+        <v>-1.490077092</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5028656061688612</v>
+      </c>
+      <c r="T87">
+        <v>2.981138373325729</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.1278679441999362</v>
+      </c>
+      <c r="W87">
+        <v>0.2082651349250552</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4262264806664541</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2544552056116262</v>
+      </c>
+      <c r="C88">
+        <v>-6.541026497090394</v>
+      </c>
+      <c r="D88">
+        <v>5.739893502909604</v>
+      </c>
+      <c r="E88">
+        <v>16.50892</v>
+      </c>
+      <c r="F88">
+        <v>16.53092</v>
+      </c>
+      <c r="G88">
+        <v>4.25</v>
+      </c>
+      <c r="H88">
+        <v>19.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.74</v>
+      </c>
+      <c r="K88">
+        <v>0.077</v>
+      </c>
+      <c r="L88">
+        <v>1.663</v>
+      </c>
+      <c r="M88">
+        <v>3.947583696</v>
+      </c>
+      <c r="N88">
+        <v>-2.284583695999999</v>
+      </c>
+      <c r="O88">
+        <v>-0.6853751087999999</v>
+      </c>
+      <c r="P88">
+        <v>-1.5992085872</v>
+      </c>
+      <c r="Q88">
+        <v>-1.5222085872</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5360131494666369</v>
+      </c>
+      <c r="T88">
+        <v>3.194076828563281</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.1263811076394718</v>
+      </c>
+      <c r="W88">
+        <v>0.2086201914956941</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4212703587982395</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2564552056116261</v>
+      </c>
+      <c r="C89">
+        <v>-6.784263134422602</v>
+      </c>
+      <c r="D89">
+        <v>5.688876865577396</v>
+      </c>
+      <c r="E89">
+        <v>16.70114</v>
+      </c>
+      <c r="F89">
+        <v>16.72314</v>
+      </c>
+      <c r="G89">
+        <v>4.25</v>
+      </c>
+      <c r="H89">
+        <v>19.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.74</v>
+      </c>
+      <c r="K89">
+        <v>0.077</v>
+      </c>
+      <c r="L89">
+        <v>1.663</v>
+      </c>
+      <c r="M89">
+        <v>3.993485832</v>
+      </c>
+      <c r="N89">
+        <v>-2.330485832</v>
+      </c>
+      <c r="O89">
+        <v>-0.6991457496</v>
+      </c>
+      <c r="P89">
+        <v>-1.6313400824</v>
+      </c>
+      <c r="Q89">
+        <v>-1.5543400824</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5742603148102243</v>
+      </c>
+      <c r="T89">
+        <v>3.439775046145071</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.1249284512298227</v>
+      </c>
+      <c r="W89">
+        <v>0.2089670858463183</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4164281707660757</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2584552056116262</v>
+      </c>
+      <c r="C90">
+        <v>-7.026600881175732</v>
+      </c>
+      <c r="D90">
+        <v>5.638759118824267</v>
+      </c>
+      <c r="E90">
+        <v>16.89336</v>
+      </c>
+      <c r="F90">
+        <v>16.91536</v>
+      </c>
+      <c r="G90">
+        <v>4.25</v>
+      </c>
+      <c r="H90">
+        <v>19.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.74</v>
+      </c>
+      <c r="K90">
+        <v>0.077</v>
+      </c>
+      <c r="L90">
+        <v>1.663</v>
+      </c>
+      <c r="M90">
+        <v>4.039387968</v>
+      </c>
+      <c r="N90">
+        <v>-2.376387968</v>
+      </c>
+      <c r="O90">
+        <v>-0.7129163903999999</v>
+      </c>
+      <c r="P90">
+        <v>-1.6634715776</v>
+      </c>
+      <c r="Q90">
+        <v>-1.5864715776</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6188820077110766</v>
+      </c>
+      <c r="T90">
+        <v>3.726422966657162</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.1235088097385747</v>
+      </c>
+      <c r="W90">
+        <v>0.2093060962344284</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4116960324619159</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2604552056116262</v>
+      </c>
+      <c r="C91">
+        <v>-7.268063286964358</v>
+      </c>
+      <c r="D91">
+        <v>5.589516713035641</v>
+      </c>
+      <c r="E91">
+        <v>17.08558</v>
+      </c>
+      <c r="F91">
+        <v>17.10758</v>
+      </c>
+      <c r="G91">
+        <v>4.25</v>
+      </c>
+      <c r="H91">
+        <v>19.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.74</v>
+      </c>
+      <c r="K91">
+        <v>0.077</v>
+      </c>
+      <c r="L91">
+        <v>1.663</v>
+      </c>
+      <c r="M91">
+        <v>4.085290104</v>
+      </c>
+      <c r="N91">
+        <v>-2.422290104</v>
+      </c>
+      <c r="O91">
+        <v>-0.7266870312</v>
+      </c>
+      <c r="P91">
+        <v>-1.6956030728</v>
+      </c>
+      <c r="Q91">
+        <v>-1.6186030728</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6716167356848108</v>
+      </c>
+      <c r="T91">
+        <v>4.065188690898721</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.1221210703033098</v>
+      </c>
+      <c r="W91">
+        <v>0.2096374884115696</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4070702343443662</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2624552056116262</v>
+      </c>
+      <c r="C92">
+        <v>-7.508673085904213</v>
+      </c>
+      <c r="D92">
+        <v>5.541126914095785</v>
+      </c>
+      <c r="E92">
+        <v>17.2778</v>
+      </c>
+      <c r="F92">
+        <v>17.2998</v>
+      </c>
+      <c r="G92">
+        <v>4.25</v>
+      </c>
+      <c r="H92">
+        <v>19.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.74</v>
+      </c>
+      <c r="K92">
+        <v>0.077</v>
+      </c>
+      <c r="L92">
+        <v>1.663</v>
+      </c>
+      <c r="M92">
+        <v>4.13119224</v>
+      </c>
+      <c r="N92">
+        <v>-2.46819224</v>
+      </c>
+      <c r="O92">
+        <v>-0.7404576719999999</v>
+      </c>
+      <c r="P92">
+        <v>-1.727734568</v>
+      </c>
+      <c r="Q92">
+        <v>-1.650734568</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7348984092532918</v>
+      </c>
+      <c r="T92">
+        <v>4.471707559988594</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.120764169522162</v>
+      </c>
+      <c r="W92">
+        <v>0.2099615163181077</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.40254723174054</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2644552056116262</v>
+      </c>
+      <c r="C93">
+        <v>-7.748452231609058</v>
+      </c>
+      <c r="D93">
+        <v>5.493567768390943</v>
+      </c>
+      <c r="E93">
+        <v>17.47002</v>
+      </c>
+      <c r="F93">
+        <v>17.49202</v>
+      </c>
+      <c r="G93">
+        <v>4.25</v>
+      </c>
+      <c r="H93">
+        <v>19.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.74</v>
+      </c>
+      <c r="K93">
+        <v>0.077</v>
+      </c>
+      <c r="L93">
+        <v>1.663</v>
+      </c>
+      <c r="M93">
+        <v>4.177094376</v>
+      </c>
+      <c r="N93">
+        <v>-2.514094376</v>
+      </c>
+      <c r="O93">
+        <v>-0.7542283128</v>
+      </c>
+      <c r="P93">
+        <v>-1.7598660632</v>
+      </c>
+      <c r="Q93">
+        <v>-1.6828660632</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8122426769481024</v>
+      </c>
+      <c r="T93">
+        <v>4.968563955542884</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.1194370907362041</v>
+      </c>
+      <c r="W93">
+        <v>0.2102784227321945</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3981236357873471</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2664552056116262</v>
+      </c>
+      <c r="C94">
+        <v>-7.987421930400625</v>
+      </c>
+      <c r="D94">
+        <v>5.446818069599373</v>
+      </c>
+      <c r="E94">
+        <v>17.66224</v>
+      </c>
+      <c r="F94">
+        <v>17.68424</v>
+      </c>
+      <c r="G94">
+        <v>4.25</v>
+      </c>
+      <c r="H94">
+        <v>19.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.74</v>
+      </c>
+      <c r="K94">
+        <v>0.077</v>
+      </c>
+      <c r="L94">
+        <v>1.663</v>
+      </c>
+      <c r="M94">
+        <v>4.222996512</v>
+      </c>
+      <c r="N94">
+        <v>-2.559996512</v>
+      </c>
+      <c r="O94">
+        <v>-0.7679989535999999</v>
+      </c>
+      <c r="P94">
+        <v>-1.7919975584</v>
+      </c>
+      <c r="Q94">
+        <v>-1.7149975584</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9089230115666151</v>
+      </c>
+      <c r="T94">
+        <v>5.589634449985745</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.1181388614890715</v>
+      </c>
+      <c r="W94">
+        <v>0.2105884398764097</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3937962049635717</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2684552056116261</v>
+      </c>
+      <c r="C95">
+        <v>-8.225602672837239</v>
+      </c>
+      <c r="D95">
+        <v>5.400857327162759</v>
+      </c>
+      <c r="E95">
+        <v>17.85446</v>
+      </c>
+      <c r="F95">
+        <v>17.87646</v>
+      </c>
+      <c r="G95">
+        <v>4.25</v>
+      </c>
+      <c r="H95">
+        <v>19.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.74</v>
+      </c>
+      <c r="K95">
+        <v>0.077</v>
+      </c>
+      <c r="L95">
+        <v>1.663</v>
+      </c>
+      <c r="M95">
+        <v>4.268898648</v>
+      </c>
+      <c r="N95">
+        <v>-2.605898647999999</v>
+      </c>
+      <c r="O95">
+        <v>-0.7817695943999997</v>
+      </c>
+      <c r="P95">
+        <v>-1.8241290536</v>
+      </c>
+      <c r="Q95">
+        <v>-1.7471290536</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.033226298933275</v>
+      </c>
+      <c r="T95">
+        <v>6.388153657126566</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.1168685511504793</v>
+      </c>
+      <c r="W95">
+        <v>0.2108917899852655</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3895618371682645</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2704552056116262</v>
+      </c>
+      <c r="C96">
+        <v>-8.463014263659488</v>
+      </c>
+      <c r="D96">
+        <v>5.355665736340512</v>
+      </c>
+      <c r="E96">
+        <v>18.04668</v>
+      </c>
+      <c r="F96">
+        <v>18.06868</v>
+      </c>
+      <c r="G96">
+        <v>4.25</v>
+      </c>
+      <c r="H96">
+        <v>19.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.74</v>
+      </c>
+      <c r="K96">
+        <v>0.077</v>
+      </c>
+      <c r="L96">
+        <v>1.663</v>
+      </c>
+      <c r="M96">
+        <v>4.314800784</v>
+      </c>
+      <c r="N96">
+        <v>-2.651800784</v>
+      </c>
+      <c r="O96">
+        <v>-0.7955402351999999</v>
+      </c>
+      <c r="P96">
+        <v>-1.8562605488</v>
+      </c>
+      <c r="Q96">
+        <v>-1.7792605488</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.198964015422154</v>
+      </c>
+      <c r="T96">
+        <v>7.45284593331433</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.1156252686914317</v>
+      </c>
+      <c r="W96">
+        <v>0.2111886858364861</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3854175623047723</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2724552056116262</v>
+      </c>
+      <c r="C97">
+        <v>-8.699675850244972</v>
+      </c>
+      <c r="D97">
+        <v>5.311224149755027</v>
+      </c>
+      <c r="E97">
+        <v>18.2389</v>
+      </c>
+      <c r="F97">
+        <v>18.2609</v>
+      </c>
+      <c r="G97">
+        <v>4.25</v>
+      </c>
+      <c r="H97">
+        <v>19.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.74</v>
+      </c>
+      <c r="K97">
+        <v>0.077</v>
+      </c>
+      <c r="L97">
+        <v>1.663</v>
+      </c>
+      <c r="M97">
+        <v>4.36070292</v>
+      </c>
+      <c r="N97">
+        <v>-2.69770292</v>
+      </c>
+      <c r="O97">
+        <v>-0.8093108760000001</v>
+      </c>
+      <c r="P97">
+        <v>-1.888392044</v>
+      </c>
+      <c r="Q97">
+        <v>-1.811392044</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.430996818506586</v>
+      </c>
+      <c r="T97">
+        <v>8.9434151199772</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.1144081605999429</v>
+      </c>
+      <c r="W97">
+        <v>0.2114793312487337</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3813605353331431</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2744552056116261</v>
+      </c>
+      <c r="C98">
+        <v>-8.935605949658026</v>
+      </c>
+      <c r="D98">
+        <v>5.267514050341974</v>
+      </c>
+      <c r="E98">
+        <v>18.43112</v>
+      </c>
+      <c r="F98">
+        <v>18.45312</v>
+      </c>
+      <c r="G98">
+        <v>4.25</v>
+      </c>
+      <c r="H98">
+        <v>19.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.74</v>
+      </c>
+      <c r="K98">
+        <v>0.077</v>
+      </c>
+      <c r="L98">
+        <v>1.663</v>
+      </c>
+      <c r="M98">
+        <v>4.406605056</v>
+      </c>
+      <c r="N98">
+        <v>-2.743605056</v>
+      </c>
+      <c r="O98">
+        <v>-0.8230815168</v>
+      </c>
+      <c r="P98">
+        <v>-1.9205235392</v>
+      </c>
+      <c r="Q98">
+        <v>-1.8435235392</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.779046023133228</v>
+      </c>
+      <c r="T98">
+        <v>11.17926889997147</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.1132164089270268</v>
+      </c>
+      <c r="W98">
+        <v>0.211763921548226</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3773880297567562</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2764552056116262</v>
+      </c>
+      <c r="C99">
+        <v>-9.170822474374624</v>
+      </c>
+      <c r="D99">
+        <v>5.224517525625373</v>
+      </c>
+      <c r="E99">
+        <v>18.62334</v>
+      </c>
+      <c r="F99">
+        <v>18.64534</v>
+      </c>
+      <c r="G99">
+        <v>4.25</v>
+      </c>
+      <c r="H99">
+        <v>19.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.74</v>
+      </c>
+      <c r="K99">
+        <v>0.077</v>
+      </c>
+      <c r="L99">
+        <v>1.663</v>
+      </c>
+      <c r="M99">
+        <v>4.452507192</v>
+      </c>
+      <c r="N99">
+        <v>-2.789507191999999</v>
+      </c>
+      <c r="O99">
+        <v>-0.8368521575999998</v>
+      </c>
+      <c r="P99">
+        <v>-1.9526550344</v>
+      </c>
+      <c r="Q99">
+        <v>-1.8756550344</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.359128030844304</v>
+      </c>
+      <c r="T99">
+        <v>14.90569186662863</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.1120492294535523</v>
+      </c>
+      <c r="W99">
+        <v>0.2120426440064917</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3734974315118412</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2784552056116262</v>
+      </c>
+      <c r="C100">
+        <v>-9.405342756757616</v>
+      </c>
+      <c r="D100">
+        <v>5.182217243242381</v>
+      </c>
+      <c r="E100">
+        <v>18.81556</v>
+      </c>
+      <c r="F100">
+        <v>18.83756</v>
+      </c>
+      <c r="G100">
+        <v>4.25</v>
+      </c>
+      <c r="H100">
+        <v>19.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.74</v>
+      </c>
+      <c r="K100">
+        <v>0.077</v>
+      </c>
+      <c r="L100">
+        <v>1.663</v>
+      </c>
+      <c r="M100">
+        <v>4.498409327999999</v>
+      </c>
+      <c r="N100">
+        <v>-2.835409327999999</v>
+      </c>
+      <c r="O100">
+        <v>-0.8506227983999997</v>
+      </c>
+      <c r="P100">
+        <v>-1.984786529599999</v>
+      </c>
+      <c r="Q100">
+        <v>-1.907786529599999</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.519292046266456</v>
+      </c>
+      <c r="T100">
+        <v>22.35853779994295</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.1109058699693324</v>
+      </c>
+      <c r="W100">
+        <v>0.2123156782513234</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3696862332311082</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2804552056116262</v>
+      </c>
+      <c r="C101">
+        <v>-9.63918357235254</v>
+      </c>
+      <c r="D101">
+        <v>5.140596427647458</v>
+      </c>
+      <c r="E101">
+        <v>19.00778</v>
+      </c>
+      <c r="F101">
+        <v>19.02978</v>
+      </c>
+      <c r="G101">
+        <v>4.25</v>
+      </c>
+      <c r="H101">
+        <v>19.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.74</v>
+      </c>
+      <c r="K101">
+        <v>0.077</v>
+      </c>
+      <c r="L101">
+        <v>1.663</v>
+      </c>
+      <c r="M101">
+        <v>4.544311464</v>
+      </c>
+      <c r="N101">
+        <v>-2.881311463999999</v>
+      </c>
+      <c r="O101">
+        <v>-0.8643934391999998</v>
+      </c>
+      <c r="P101">
+        <v>-2.0169180248</v>
+      </c>
+      <c r="Q101">
+        <v>-1.9399180248</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.999784092532912</v>
+      </c>
+      <c r="T101">
+        <v>44.7170755998859</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.1097856086565109</v>
+      </c>
+      <c r="W101">
+        <v>0.2125831966528252</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3659520288550363</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/nigeria/nigeria_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_r_e_i_t.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1177546019247098</v>
+        <v>0.1174328381189357</v>
       </c>
       <c r="C2">
-        <v>8.687860274735524</v>
+        <v>8.609597517665597</v>
       </c>
       <c r="D2">
-        <v>4.847860274735525</v>
+        <v>4.856457517665596</v>
       </c>
       <c r="E2">
-        <v>-0.026</v>
+        <v>0.06086000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.08686000000000001</v>
       </c>
       <c r="G2">
         <v>3.84</v>
@@ -1576,28 +1576,28 @@
         <v>1.262</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.004369058</v>
       </c>
       <c r="N2">
-        <v>1.262</v>
+        <v>1.257630942</v>
       </c>
       <c r="O2">
-        <v>0.3786</v>
+        <v>0.3772892826</v>
       </c>
       <c r="P2">
-        <v>0.8834</v>
+        <v>0.8803416594</v>
       </c>
       <c r="Q2">
-        <v>0.9414</v>
+        <v>0.9383416594</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1177546019247098</v>
+        <v>0.1182633718373088</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768603</v>
+        <v>0.5052466974660905</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>288.8494499271926</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1174328381189357</v>
+        <v>0.1171110743131615</v>
       </c>
       <c r="C3">
-        <v>8.609597517665597</v>
+        <v>8.531365307637856</v>
       </c>
       <c r="D3">
-        <v>4.856457517665596</v>
+        <v>4.865085307637855</v>
       </c>
       <c r="E3">
-        <v>0.06086000000000001</v>
+        <v>0.14772</v>
       </c>
       <c r="F3">
-        <v>0.08686000000000001</v>
+        <v>0.17372</v>
       </c>
       <c r="G3">
         <v>3.84</v>
@@ -1658,28 +1658,28 @@
         <v>1.262</v>
       </c>
       <c r="M3">
-        <v>0.004369058</v>
+        <v>0.008738116000000001</v>
       </c>
       <c r="N3">
-        <v>1.257630942</v>
+        <v>1.253261884</v>
       </c>
       <c r="O3">
-        <v>0.3772892826</v>
+        <v>0.3759785652</v>
       </c>
       <c r="P3">
-        <v>0.8803416594</v>
+        <v>0.8772833188</v>
       </c>
       <c r="Q3">
-        <v>0.9383416594</v>
+        <v>0.9352833188</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1182633718373088</v>
+        <v>0.1187825248093485</v>
       </c>
       <c r="T3">
-        <v>0.5052466974660905</v>
+        <v>0.5088664617408154</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>288.8494499271926</v>
+        <v>144.4247249635963</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1171110743131615</v>
+        <v>0.1167893105073874</v>
       </c>
       <c r="C4">
-        <v>8.531365307637856</v>
+        <v>8.453163807748048</v>
       </c>
       <c r="D4">
-        <v>4.865085307637855</v>
+        <v>4.873743807748047</v>
       </c>
       <c r="E4">
-        <v>0.14772</v>
+        <v>0.23458</v>
       </c>
       <c r="F4">
-        <v>0.17372</v>
+        <v>0.26058</v>
       </c>
       <c r="G4">
         <v>3.84</v>
@@ -1740,28 +1740,28 @@
         <v>1.262</v>
       </c>
       <c r="M4">
-        <v>0.008738116000000001</v>
+        <v>0.013107174</v>
       </c>
       <c r="N4">
-        <v>1.253261884</v>
+        <v>1.248892826</v>
       </c>
       <c r="O4">
-        <v>0.3759785652</v>
+        <v>0.3746678478</v>
       </c>
       <c r="P4">
-        <v>0.8772833188</v>
+        <v>0.8742249782</v>
       </c>
       <c r="Q4">
-        <v>0.9352833188</v>
+        <v>0.9322249782000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1187825248093485</v>
+        <v>0.1193123819663788</v>
       </c>
       <c r="T4">
-        <v>0.5088664617408154</v>
+        <v>0.512560860330483</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>144.4247249635963</v>
+        <v>96.28314997573086</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1167893105073874</v>
+        <v>0.1164675467016133</v>
       </c>
       <c r="C5">
-        <v>8.453163807748048</v>
+        <v>8.374993182255045</v>
       </c>
       <c r="D5">
-        <v>4.873743807748047</v>
+        <v>4.882433182255046</v>
       </c>
       <c r="E5">
-        <v>0.23458</v>
+        <v>0.32144</v>
       </c>
       <c r="F5">
-        <v>0.26058</v>
+        <v>0.34744</v>
       </c>
       <c r="G5">
         <v>3.84</v>
@@ -1822,28 +1822,28 @@
         <v>1.262</v>
       </c>
       <c r="M5">
-        <v>0.013107174</v>
+        <v>0.017476232</v>
       </c>
       <c r="N5">
-        <v>1.248892826</v>
+        <v>1.244523768</v>
       </c>
       <c r="O5">
-        <v>0.3746678478</v>
+        <v>0.3733571304</v>
       </c>
       <c r="P5">
-        <v>0.8742249782</v>
+        <v>0.8711666376</v>
       </c>
       <c r="Q5">
-        <v>0.9322249782000001</v>
+        <v>0.9291666376000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1193123819663788</v>
+        <v>0.1198532778141805</v>
       </c>
       <c r="T5">
-        <v>0.512560860330483</v>
+        <v>0.5163322255574353</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.28314997573086</v>
+        <v>72.21236248179814</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1164675467016133</v>
+        <v>0.1161457828958391</v>
       </c>
       <c r="C6">
-        <v>8.374993182255045</v>
+        <v>8.296853596591241</v>
       </c>
       <c r="D6">
-        <v>4.882433182255046</v>
+        <v>4.891153596591242</v>
       </c>
       <c r="E6">
-        <v>0.32144</v>
+        <v>0.4083</v>
       </c>
       <c r="F6">
-        <v>0.34744</v>
+        <v>0.4343</v>
       </c>
       <c r="G6">
         <v>3.84</v>
@@ -1904,28 +1904,28 @@
         <v>1.262</v>
       </c>
       <c r="M6">
-        <v>0.017476232</v>
+        <v>0.02184529</v>
       </c>
       <c r="N6">
-        <v>1.244523768</v>
+        <v>1.24015471</v>
       </c>
       <c r="O6">
-        <v>0.3733571304</v>
+        <v>0.372046413</v>
       </c>
       <c r="P6">
-        <v>0.8711666376</v>
+        <v>0.868108297</v>
       </c>
       <c r="Q6">
-        <v>0.9291666376000001</v>
+        <v>0.9261082970000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1198532778141805</v>
+        <v>0.1204055609429886</v>
       </c>
       <c r="T6">
-        <v>0.5163322255574353</v>
+        <v>0.5201829879470603</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.21236248179814</v>
+        <v>57.76988998543851</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1161457828958391</v>
+        <v>0.115824019090065</v>
       </c>
       <c r="C7">
-        <v>8.296853596591241</v>
+        <v>8.218745217373042</v>
       </c>
       <c r="D7">
-        <v>4.891153596591242</v>
+        <v>4.899905217373044</v>
       </c>
       <c r="E7">
-        <v>0.4083</v>
+        <v>0.49516</v>
       </c>
       <c r="F7">
-        <v>0.4343</v>
+        <v>0.5211600000000001</v>
       </c>
       <c r="G7">
         <v>3.84</v>
@@ -1986,28 +1986,28 @@
         <v>1.262</v>
       </c>
       <c r="M7">
-        <v>0.02184529</v>
+        <v>0.026214348</v>
       </c>
       <c r="N7">
-        <v>1.24015471</v>
+        <v>1.235785652</v>
       </c>
       <c r="O7">
-        <v>0.372046413</v>
+        <v>0.3707356956</v>
       </c>
       <c r="P7">
-        <v>0.868108297</v>
+        <v>0.8650499563999999</v>
       </c>
       <c r="Q7">
-        <v>0.9261082970000001</v>
+        <v>0.9230499564</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1204055609429886</v>
+        <v>0.1209695947766649</v>
       </c>
       <c r="T7">
-        <v>0.5201829879470603</v>
+        <v>0.5241156814513582</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>57.76988998543851</v>
+        <v>48.14157498786542</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.115824019090065</v>
+        <v>0.1155022552842909</v>
       </c>
       <c r="C8">
-        <v>8.218745217373042</v>
+        <v>8.140668212411487</v>
       </c>
       <c r="D8">
-        <v>4.899905217373044</v>
+        <v>4.908688212411487</v>
       </c>
       <c r="E8">
-        <v>0.4951599999999999</v>
+        <v>0.5820199999999999</v>
       </c>
       <c r="F8">
-        <v>0.52116</v>
+        <v>0.6080199999999999</v>
       </c>
       <c r="G8">
         <v>3.84</v>
@@ -2068,28 +2068,28 @@
         <v>1.262</v>
       </c>
       <c r="M8">
-        <v>0.02621434799999999</v>
+        <v>0.03058340599999999</v>
       </c>
       <c r="N8">
-        <v>1.235785652</v>
+        <v>1.231416594</v>
       </c>
       <c r="O8">
-        <v>0.3707356956</v>
+        <v>0.3694249782</v>
       </c>
       <c r="P8">
-        <v>0.8650499564</v>
+        <v>0.8619916157999999</v>
       </c>
       <c r="Q8">
-        <v>0.9230499564000001</v>
+        <v>0.9199916158</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1209695947766649</v>
+        <v>0.1215457583702053</v>
       </c>
       <c r="T8">
-        <v>0.5241156814513582</v>
+        <v>0.528132949009512</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.14157498786544</v>
+        <v>41.26420713245609</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1155022552842909</v>
+        <v>0.1151804914785167</v>
       </c>
       <c r="C9">
-        <v>8.140668212411487</v>
+        <v>8.062622750722964</v>
       </c>
       <c r="D9">
-        <v>4.908688212411487</v>
+        <v>4.917502750722963</v>
       </c>
       <c r="E9">
-        <v>0.58202</v>
+        <v>0.66888</v>
       </c>
       <c r="F9">
-        <v>0.60802</v>
+        <v>0.6948800000000001</v>
       </c>
       <c r="G9">
         <v>3.84</v>
@@ -2150,28 +2150,28 @@
         <v>1.262</v>
       </c>
       <c r="M9">
-        <v>0.030583406</v>
+        <v>0.034952464</v>
       </c>
       <c r="N9">
-        <v>1.231416594</v>
+        <v>1.227047536</v>
       </c>
       <c r="O9">
-        <v>0.3694249782</v>
+        <v>0.3681142608</v>
       </c>
       <c r="P9">
-        <v>0.8619916157999999</v>
+        <v>0.8589332752</v>
       </c>
       <c r="Q9">
-        <v>0.9199916158</v>
+        <v>0.9169332752</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1215457583702053</v>
+        <v>0.1221344472592573</v>
       </c>
       <c r="T9">
-        <v>0.528132949009512</v>
+        <v>0.5322375484711039</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.26420713245608</v>
+        <v>36.10618124089906</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1151804914785167</v>
+        <v>0.1148587276727426</v>
       </c>
       <c r="C10">
-        <v>8.062622750722964</v>
+        <v>7.984609002540053</v>
       </c>
       <c r="D10">
-        <v>4.917502750722963</v>
+        <v>4.926349002540054</v>
       </c>
       <c r="E10">
-        <v>0.66888</v>
+        <v>0.75574</v>
       </c>
       <c r="F10">
-        <v>0.6948800000000001</v>
+        <v>0.78174</v>
       </c>
       <c r="G10">
         <v>3.84</v>
@@ -2232,28 +2232,28 @@
         <v>1.262</v>
       </c>
       <c r="M10">
-        <v>0.034952464</v>
+        <v>0.039321522</v>
       </c>
       <c r="N10">
-        <v>1.227047536</v>
+        <v>1.222678478</v>
       </c>
       <c r="O10">
-        <v>0.3681142608</v>
+        <v>0.3668035434</v>
       </c>
       <c r="P10">
-        <v>0.8589332752</v>
+        <v>0.8558749346</v>
       </c>
       <c r="Q10">
-        <v>0.9169332752</v>
+        <v>0.9138749346</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1221344472592573</v>
+        <v>0.1227360743656512</v>
       </c>
       <c r="T10">
-        <v>0.5322375484711039</v>
+        <v>0.5364323589098736</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.10618124089906</v>
+        <v>32.09438332524361</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1148587276727426</v>
+        <v>0.1145369638669685</v>
       </c>
       <c r="C11">
-        <v>7.984609002540053</v>
+        <v>7.906627139322507</v>
       </c>
       <c r="D11">
-        <v>4.926349002540054</v>
+        <v>4.935227139322506</v>
       </c>
       <c r="E11">
-        <v>0.75574</v>
+        <v>0.8425999999999999</v>
       </c>
       <c r="F11">
-        <v>0.78174</v>
+        <v>0.8685999999999999</v>
       </c>
       <c r="G11">
         <v>3.84</v>
@@ -2314,28 +2314,28 @@
         <v>1.262</v>
       </c>
       <c r="M11">
-        <v>0.039321522</v>
+        <v>0.04369057999999999</v>
       </c>
       <c r="N11">
-        <v>1.222678478</v>
+        <v>1.21830942</v>
       </c>
       <c r="O11">
-        <v>0.3668035434</v>
+        <v>0.365492826</v>
       </c>
       <c r="P11">
-        <v>0.8558749346</v>
+        <v>0.852816594</v>
       </c>
       <c r="Q11">
-        <v>0.9138749346</v>
+        <v>0.910816594</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1227360743656512</v>
+        <v>0.1233510709632983</v>
       </c>
       <c r="T11">
-        <v>0.5364323589098736</v>
+        <v>0.5407203873583938</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.09438332524361</v>
+        <v>28.88494499271926</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1145369638669685</v>
+        <v>0.1142152000611944</v>
       </c>
       <c r="C12">
-        <v>7.906627139322507</v>
+        <v>7.828677333768288</v>
       </c>
       <c r="D12">
-        <v>4.935227139322506</v>
+        <v>4.944137333768288</v>
       </c>
       <c r="E12">
-        <v>0.8426</v>
+        <v>0.92946</v>
       </c>
       <c r="F12">
-        <v>0.8686</v>
+        <v>0.95546</v>
       </c>
       <c r="G12">
         <v>3.84</v>
@@ -2396,28 +2396,28 @@
         <v>1.262</v>
       </c>
       <c r="M12">
-        <v>0.04369058</v>
+        <v>0.04805963799999999</v>
       </c>
       <c r="N12">
-        <v>1.21830942</v>
+        <v>1.213940362</v>
       </c>
       <c r="O12">
-        <v>0.365492826</v>
+        <v>0.3641821086</v>
       </c>
       <c r="P12">
-        <v>0.852816594</v>
+        <v>0.8497582534</v>
       </c>
       <c r="Q12">
-        <v>0.910816594</v>
+        <v>0.9077582534</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1233510709632983</v>
+        <v>0.1239798877092072</v>
       </c>
       <c r="T12">
-        <v>0.5407203873583938</v>
+        <v>0.5451047759967684</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>28.88494499271926</v>
+        <v>26.25904090247205</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1142152000611944</v>
+        <v>0.1138934362554203</v>
       </c>
       <c r="C13">
-        <v>7.828677333768288</v>
+        <v>7.750759759824806</v>
       </c>
       <c r="D13">
-        <v>4.944137333768288</v>
+        <v>4.953079759824806</v>
       </c>
       <c r="E13">
-        <v>0.92946</v>
+        <v>1.01632</v>
       </c>
       <c r="F13">
-        <v>0.95546</v>
+        <v>1.04232</v>
       </c>
       <c r="G13">
         <v>3.84</v>
@@ -2478,28 +2478,28 @@
         <v>1.262</v>
       </c>
       <c r="M13">
-        <v>0.04805963799999999</v>
+        <v>0.05242869599999999</v>
       </c>
       <c r="N13">
-        <v>1.213940362</v>
+        <v>1.209571304</v>
       </c>
       <c r="O13">
-        <v>0.3641821086</v>
+        <v>0.3628713912</v>
       </c>
       <c r="P13">
-        <v>0.8497582534</v>
+        <v>0.8466999128</v>
       </c>
       <c r="Q13">
-        <v>0.9077582534</v>
+        <v>0.9046999128000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1239798877092072</v>
+        <v>0.1246229957447957</v>
       </c>
       <c r="T13">
-        <v>0.5451047759967684</v>
+        <v>0.5495888098314696</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.25904090247205</v>
+        <v>24.07078749393272</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1138934362554203</v>
+        <v>0.1135716724496461</v>
       </c>
       <c r="C14">
-        <v>7.750759759824806</v>
+        <v>7.672874592700209</v>
       </c>
       <c r="D14">
-        <v>4.953079759824806</v>
+        <v>4.96205459270021</v>
       </c>
       <c r="E14">
-        <v>1.01632</v>
+        <v>1.10318</v>
       </c>
       <c r="F14">
-        <v>1.04232</v>
+        <v>1.12918</v>
       </c>
       <c r="G14">
         <v>3.84</v>
@@ -2560,28 +2560,28 @@
         <v>1.262</v>
       </c>
       <c r="M14">
-        <v>0.05242869599999999</v>
+        <v>0.056797754</v>
       </c>
       <c r="N14">
-        <v>1.209571304</v>
+        <v>1.205202246</v>
       </c>
       <c r="O14">
-        <v>0.3628713912</v>
+        <v>0.3615606738</v>
       </c>
       <c r="P14">
-        <v>0.8466999128</v>
+        <v>0.8436415722</v>
       </c>
       <c r="Q14">
-        <v>0.9046999128000001</v>
+        <v>0.9016415722000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1246229957447957</v>
+        <v>0.1252808878731564</v>
       </c>
       <c r="T14">
-        <v>0.5495888098314696</v>
+        <v>0.5541759249037502</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.07078749393272</v>
+        <v>22.21918845593789</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1135716724496461</v>
+        <v>0.113249908643872</v>
       </c>
       <c r="C15">
-        <v>7.672874592700209</v>
+        <v>7.595022008874851</v>
       </c>
       <c r="D15">
-        <v>4.96205459270021</v>
+        <v>4.971062008874851</v>
       </c>
       <c r="E15">
-        <v>1.10318</v>
+        <v>1.19004</v>
       </c>
       <c r="F15">
-        <v>1.12918</v>
+        <v>1.21604</v>
       </c>
       <c r="G15">
         <v>3.84</v>
@@ -2642,28 +2642,28 @@
         <v>1.262</v>
       </c>
       <c r="M15">
-        <v>0.056797754</v>
+        <v>0.06116681199999999</v>
       </c>
       <c r="N15">
-        <v>1.205202246</v>
+        <v>1.200833188</v>
       </c>
       <c r="O15">
-        <v>0.3615606738</v>
+        <v>0.3602499564</v>
       </c>
       <c r="P15">
-        <v>0.8436415722</v>
+        <v>0.8405832316</v>
       </c>
       <c r="Q15">
-        <v>0.9016415722000001</v>
+        <v>0.8985832316000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1252808878731564</v>
+        <v>0.1259540798184558</v>
       </c>
       <c r="T15">
-        <v>0.5541759249037502</v>
+        <v>0.558869717070735</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.21918845593789</v>
+        <v>20.63210356622804</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.113249908643872</v>
+        <v>0.1129281448380978</v>
       </c>
       <c r="C16">
-        <v>7.595022008874851</v>
+        <v>7.517202186112834</v>
       </c>
       <c r="D16">
-        <v>4.971062008874851</v>
+        <v>4.980102186112833</v>
       </c>
       <c r="E16">
-        <v>1.19004</v>
+        <v>1.2769</v>
       </c>
       <c r="F16">
-        <v>1.21604</v>
+        <v>1.3029</v>
       </c>
       <c r="G16">
         <v>3.84</v>
@@ -2724,28 +2724,28 @@
         <v>1.262</v>
       </c>
       <c r="M16">
-        <v>0.06116681199999999</v>
+        <v>0.06553587000000001</v>
       </c>
       <c r="N16">
-        <v>1.200833188</v>
+        <v>1.19646413</v>
       </c>
       <c r="O16">
-        <v>0.3602499564</v>
+        <v>0.358939239</v>
       </c>
       <c r="P16">
-        <v>0.8405832316</v>
+        <v>0.837524891</v>
       </c>
       <c r="Q16">
-        <v>0.8985832316000001</v>
+        <v>0.8955248910000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1259540798184558</v>
+        <v>0.1266431115742328</v>
       </c>
       <c r="T16">
-        <v>0.558869717070735</v>
+        <v>0.5636739514063548</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.63210356622804</v>
+        <v>19.25662999514617</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1129281448380978</v>
+        <v>0.1126063810323237</v>
       </c>
       <c r="C17">
-        <v>7.517202186112834</v>
+        <v>7.43941530347372</v>
       </c>
       <c r="D17">
-        <v>4.980102186112833</v>
+        <v>4.98917530347372</v>
       </c>
       <c r="E17">
-        <v>1.2769</v>
+        <v>1.36376</v>
       </c>
       <c r="F17">
-        <v>1.3029</v>
+        <v>1.38976</v>
       </c>
       <c r="G17">
         <v>3.84</v>
@@ -2806,28 +2806,28 @@
         <v>1.262</v>
       </c>
       <c r="M17">
-        <v>0.06553587</v>
+        <v>0.06990492800000001</v>
       </c>
       <c r="N17">
-        <v>1.19646413</v>
+        <v>1.192095072</v>
       </c>
       <c r="O17">
-        <v>0.358939239</v>
+        <v>0.3576285216</v>
       </c>
       <c r="P17">
-        <v>0.837524891</v>
+        <v>0.8344665504000001</v>
       </c>
       <c r="Q17">
-        <v>0.8955248910000001</v>
+        <v>0.8924665504000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1266431115742328</v>
+        <v>0.1273485488480044</v>
       </c>
       <c r="T17">
-        <v>0.5636739514063548</v>
+        <v>0.5685925722737749</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.25662999514617</v>
+        <v>18.05309062044953</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1126063810323237</v>
+        <v>0.1122846172265496</v>
       </c>
       <c r="C18">
-        <v>7.43941530347372</v>
+        <v>7.361661541324349</v>
       </c>
       <c r="D18">
-        <v>4.98917530347372</v>
+        <v>4.99828154132435</v>
       </c>
       <c r="E18">
-        <v>1.36376</v>
+        <v>1.45062</v>
       </c>
       <c r="F18">
-        <v>1.38976</v>
+        <v>1.47662</v>
       </c>
       <c r="G18">
         <v>3.84</v>
@@ -2888,28 +2888,28 @@
         <v>1.262</v>
       </c>
       <c r="M18">
-        <v>0.06990492800000001</v>
+        <v>0.074273986</v>
       </c>
       <c r="N18">
-        <v>1.192095072</v>
+        <v>1.187726014</v>
       </c>
       <c r="O18">
-        <v>0.3576285216</v>
+        <v>0.3563178042</v>
       </c>
       <c r="P18">
-        <v>0.8344665504000001</v>
+        <v>0.8314082098000001</v>
       </c>
       <c r="Q18">
-        <v>0.8924665504000001</v>
+        <v>0.8894082098000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1273485488480044</v>
+        <v>0.1280709846103007</v>
       </c>
       <c r="T18">
-        <v>0.5685925722737749</v>
+        <v>0.5736297141259523</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.05309062044953</v>
+        <v>16.99114411336427</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1122846172265496</v>
+        <v>0.1119628534207755</v>
       </c>
       <c r="C19">
-        <v>7.361661541324349</v>
+        <v>7.283941081350795</v>
       </c>
       <c r="D19">
-        <v>4.99828154132435</v>
+        <v>5.007421081350794</v>
       </c>
       <c r="E19">
-        <v>1.45062</v>
+        <v>1.53748</v>
       </c>
       <c r="F19">
-        <v>1.47662</v>
+        <v>1.56348</v>
       </c>
       <c r="G19">
         <v>3.84</v>
@@ -2970,28 +2970,28 @@
         <v>1.262</v>
       </c>
       <c r="M19">
-        <v>0.074273986</v>
+        <v>0.07864304400000001</v>
       </c>
       <c r="N19">
-        <v>1.187726014</v>
+        <v>1.183356956</v>
       </c>
       <c r="O19">
-        <v>0.3563178042</v>
+        <v>0.3550070868</v>
       </c>
       <c r="P19">
-        <v>0.8314082098000001</v>
+        <v>0.8283498692</v>
       </c>
       <c r="Q19">
-        <v>0.8894082098000001</v>
+        <v>0.8863498692</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1280709846103007</v>
+        <v>0.1288110407570432</v>
       </c>
       <c r="T19">
-        <v>0.5736297141259523</v>
+        <v>0.5787897130964753</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.99114411336427</v>
+        <v>16.04719166262181</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1119628534207755</v>
+        <v>0.1116410896150013</v>
       </c>
       <c r="C20">
-        <v>7.283941081350793</v>
+        <v>7.206254106570432</v>
       </c>
       <c r="D20">
-        <v>5.007421081350794</v>
+        <v>5.016594106570432</v>
       </c>
       <c r="E20">
-        <v>1.53748</v>
+        <v>1.62434</v>
       </c>
       <c r="F20">
-        <v>1.56348</v>
+        <v>1.65034</v>
       </c>
       <c r="G20">
         <v>3.84</v>
@@ -3052,28 +3052,28 @@
         <v>1.262</v>
       </c>
       <c r="M20">
-        <v>0.078643044</v>
+        <v>0.08301210199999999</v>
       </c>
       <c r="N20">
-        <v>1.183356956</v>
+        <v>1.178987898</v>
       </c>
       <c r="O20">
-        <v>0.3550070868</v>
+        <v>0.3536963694</v>
       </c>
       <c r="P20">
-        <v>0.8283498692</v>
+        <v>0.8252915286</v>
       </c>
       <c r="Q20">
-        <v>0.8863498692</v>
+        <v>0.8832915286</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1288110407570432</v>
+        <v>0.1295693698950634</v>
       </c>
       <c r="T20">
-        <v>0.5787897130964753</v>
+        <v>0.5840771194489867</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.04719166262181</v>
+        <v>15.20260262774698</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1116410896150013</v>
+        <v>0.1113193258092272</v>
       </c>
       <c r="C21">
-        <v>7.206254106570432</v>
+        <v>7.128600801344177</v>
       </c>
       <c r="D21">
-        <v>5.016594106570432</v>
+        <v>5.025800801344177</v>
       </c>
       <c r="E21">
-        <v>1.62434</v>
+        <v>1.7112</v>
       </c>
       <c r="F21">
-        <v>1.65034</v>
+        <v>1.7372</v>
       </c>
       <c r="G21">
         <v>3.84</v>
@@ -3134,28 +3134,28 @@
         <v>1.262</v>
       </c>
       <c r="M21">
-        <v>0.08301210199999999</v>
+        <v>0.08738116</v>
       </c>
       <c r="N21">
-        <v>1.178987898</v>
+        <v>1.17461884</v>
       </c>
       <c r="O21">
-        <v>0.3536963694</v>
+        <v>0.352385652</v>
       </c>
       <c r="P21">
-        <v>0.8252915286</v>
+        <v>0.822233188</v>
       </c>
       <c r="Q21">
-        <v>0.8832915286</v>
+        <v>0.8802331880000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1295693698950634</v>
+        <v>0.130346657261534</v>
       </c>
       <c r="T21">
-        <v>0.5840771194489867</v>
+        <v>0.5894967109603109</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.20260262774698</v>
+        <v>14.44247249635963</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1113193258092272</v>
+        <v>0.1109975620034531</v>
       </c>
       <c r="C22">
-        <v>7.128600801344177</v>
+        <v>7.050981351388818</v>
       </c>
       <c r="D22">
-        <v>5.025800801344177</v>
+        <v>5.035041351388818</v>
       </c>
       <c r="E22">
-        <v>1.7112</v>
+        <v>1.79806</v>
       </c>
       <c r="F22">
-        <v>1.7372</v>
+        <v>1.82406</v>
       </c>
       <c r="G22">
         <v>3.84</v>
@@ -3216,28 +3216,28 @@
         <v>1.262</v>
       </c>
       <c r="M22">
-        <v>0.08738116</v>
+        <v>0.09175021800000001</v>
       </c>
       <c r="N22">
-        <v>1.17461884</v>
+        <v>1.170249782</v>
       </c>
       <c r="O22">
-        <v>0.352385652</v>
+        <v>0.3510749346</v>
       </c>
       <c r="P22">
-        <v>0.822233188</v>
+        <v>0.8191748474</v>
       </c>
       <c r="Q22">
-        <v>0.8802331880000001</v>
+        <v>0.8771748474000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.130346657261534</v>
+        <v>0.1311436227891811</v>
       </c>
       <c r="T22">
-        <v>0.5894967109603109</v>
+        <v>0.5950535073200229</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.44247249635963</v>
+        <v>13.75473571081869</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1109975620034531</v>
+        <v>0.110675798197679</v>
       </c>
       <c r="C23">
-        <v>7.05098135138882</v>
+        <v>6.973395943789517</v>
       </c>
       <c r="D23">
-        <v>5.035041351388819</v>
+        <v>5.044315943789516</v>
       </c>
       <c r="E23">
-        <v>1.79806</v>
+        <v>1.88492</v>
       </c>
       <c r="F23">
-        <v>1.82406</v>
+        <v>1.91092</v>
       </c>
       <c r="G23">
         <v>3.84</v>
@@ -3298,28 +3298,28 @@
         <v>1.262</v>
       </c>
       <c r="M23">
-        <v>0.09175021799999999</v>
+        <v>0.09611927599999999</v>
       </c>
       <c r="N23">
-        <v>1.170249782</v>
+        <v>1.165880724</v>
       </c>
       <c r="O23">
-        <v>0.3510749346</v>
+        <v>0.3497642172</v>
       </c>
       <c r="P23">
-        <v>0.8191748474</v>
+        <v>0.8161165068</v>
       </c>
       <c r="Q23">
-        <v>0.8771748474000001</v>
+        <v>0.8741165068000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1311436227891811</v>
+        <v>0.1319610233303576</v>
       </c>
       <c r="T23">
-        <v>0.5950535073200228</v>
+        <v>0.6007527856376763</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.75473571081869</v>
+        <v>13.12952045123603</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.110675798197679</v>
+        <v>0.1105955343919048</v>
       </c>
       <c r="C24">
-        <v>6.973395943789517</v>
+        <v>6.888854812861595</v>
       </c>
       <c r="D24">
-        <v>5.044315943789516</v>
+        <v>5.046634812861596</v>
       </c>
       <c r="E24">
-        <v>1.88492</v>
+        <v>1.97178</v>
       </c>
       <c r="F24">
-        <v>1.91092</v>
+        <v>1.99778</v>
       </c>
       <c r="G24">
         <v>3.84</v>
@@ -3380,45 +3380,45 @@
         <v>1.262</v>
       </c>
       <c r="M24">
-        <v>0.09611927599999999</v>
+        <v>0.103485004</v>
       </c>
       <c r="N24">
-        <v>1.165880724</v>
+        <v>1.158514996</v>
       </c>
       <c r="O24">
-        <v>0.3497642172</v>
+        <v>0.3475544988</v>
       </c>
       <c r="P24">
-        <v>0.8161165068</v>
+        <v>0.8109604972000001</v>
       </c>
       <c r="Q24">
-        <v>0.8741165068000001</v>
+        <v>0.8689604972000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1319610233303576</v>
+        <v>0.1327996550544218</v>
       </c>
       <c r="T24">
-        <v>0.6007527856376763</v>
+        <v>0.6066000971583856</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.12952045123603</v>
+        <v>12.19500363550259</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1105955343919048</v>
+        <v>0.1102842705861307</v>
       </c>
       <c r="C25">
-        <v>6.888854812861595</v>
+        <v>6.811007610455885</v>
       </c>
       <c r="D25">
-        <v>5.046634812861596</v>
+        <v>5.055647610455885</v>
       </c>
       <c r="E25">
-        <v>1.97178</v>
+        <v>2.05864</v>
       </c>
       <c r="F25">
-        <v>1.99778</v>
+        <v>2.08464</v>
       </c>
       <c r="G25">
         <v>3.84</v>
@@ -3462,28 +3462,28 @@
         <v>1.262</v>
       </c>
       <c r="M25">
-        <v>0.103485004</v>
+        <v>0.107984352</v>
       </c>
       <c r="N25">
-        <v>1.158514996</v>
+        <v>1.154015648</v>
       </c>
       <c r="O25">
-        <v>0.3475544988</v>
+        <v>0.3462046944</v>
       </c>
       <c r="P25">
-        <v>0.8109604972000001</v>
+        <v>0.8078109536000001</v>
       </c>
       <c r="Q25">
-        <v>0.8689604972000001</v>
+        <v>0.8658109536000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1327996550544218</v>
+        <v>0.1336603560343825</v>
       </c>
       <c r="T25">
-        <v>0.6066000971583856</v>
+        <v>0.612601285298061</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.19500363550259</v>
+        <v>11.68687848402332</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1102842705861307</v>
+        <v>0.1099730067803566</v>
       </c>
       <c r="C26">
-        <v>6.811007610455885</v>
+        <v>6.733192657599757</v>
       </c>
       <c r="D26">
-        <v>5.055647610455885</v>
+        <v>5.064692657599756</v>
       </c>
       <c r="E26">
-        <v>2.05864</v>
+        <v>2.1455</v>
       </c>
       <c r="F26">
-        <v>2.08464</v>
+        <v>2.1715</v>
       </c>
       <c r="G26">
         <v>3.84</v>
@@ -3544,28 +3544,28 @@
         <v>1.262</v>
       </c>
       <c r="M26">
-        <v>0.107984352</v>
+        <v>0.1124837</v>
       </c>
       <c r="N26">
-        <v>1.154015648</v>
+        <v>1.1495163</v>
       </c>
       <c r="O26">
-        <v>0.3462046944</v>
+        <v>0.34485489</v>
       </c>
       <c r="P26">
-        <v>0.8078109536000001</v>
+        <v>0.80466141</v>
       </c>
       <c r="Q26">
-        <v>0.8658109536000002</v>
+        <v>0.8626614100000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1336603560343825</v>
+        <v>0.1345440090404754</v>
       </c>
       <c r="T26">
-        <v>0.612601285298061</v>
+        <v>0.618762505121461</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.68687848402332</v>
+        <v>11.21940334466238</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1099730067803566</v>
+        <v>0.1096617429745824</v>
       </c>
       <c r="C27">
-        <v>6.733192657599757</v>
+        <v>6.655410127696221</v>
       </c>
       <c r="D27">
-        <v>5.064692657599756</v>
+        <v>5.07377012769622</v>
       </c>
       <c r="E27">
-        <v>2.1455</v>
+        <v>2.23236</v>
       </c>
       <c r="F27">
-        <v>2.1715</v>
+        <v>2.25836</v>
       </c>
       <c r="G27">
         <v>3.84</v>
@@ -3626,28 +3626,28 @@
         <v>1.262</v>
       </c>
       <c r="M27">
-        <v>0.1124837</v>
+        <v>0.116983048</v>
       </c>
       <c r="N27">
-        <v>1.1495163</v>
+        <v>1.145016952</v>
       </c>
       <c r="O27">
-        <v>0.34485489</v>
+        <v>0.3435050856</v>
       </c>
       <c r="P27">
-        <v>0.80466141</v>
+        <v>0.8015118664000001</v>
       </c>
       <c r="Q27">
-        <v>0.8626614100000001</v>
+        <v>0.8595118664000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1345440090404754</v>
+        <v>0.1354515445602465</v>
       </c>
       <c r="T27">
-        <v>0.618762505121461</v>
+        <v>0.6250902443995475</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.21940334466238</v>
+        <v>10.78788783140614</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1096617429745824</v>
+        <v>0.1093504791688083</v>
       </c>
       <c r="C28">
-        <v>6.655410127696221</v>
+        <v>6.577660195393688</v>
       </c>
       <c r="D28">
-        <v>5.07377012769622</v>
+        <v>5.082880195393687</v>
       </c>
       <c r="E28">
-        <v>2.23236</v>
+        <v>2.319220000000001</v>
       </c>
       <c r="F28">
-        <v>2.25836</v>
+        <v>2.34522</v>
       </c>
       <c r="G28">
         <v>3.84</v>
@@ -3708,28 +3708,28 @@
         <v>1.262</v>
       </c>
       <c r="M28">
-        <v>0.116983048</v>
+        <v>0.121482396</v>
       </c>
       <c r="N28">
-        <v>1.145016952</v>
+        <v>1.140517604</v>
       </c>
       <c r="O28">
-        <v>0.3435050856</v>
+        <v>0.3421552812</v>
       </c>
       <c r="P28">
-        <v>0.8015118664000001</v>
+        <v>0.7983623228000001</v>
       </c>
       <c r="Q28">
-        <v>0.8595118664000001</v>
+        <v>0.8563623228000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1354515445602465</v>
+        <v>0.1363839440668607</v>
       </c>
       <c r="T28">
-        <v>0.6250902443995475</v>
+        <v>0.6315913463975816</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.78788783140614</v>
+        <v>10.38833643024295</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1093504791688083</v>
+        <v>0.1090392153630342</v>
       </c>
       <c r="C29">
-        <v>6.577660195393688</v>
+        <v>6.499943036597162</v>
       </c>
       <c r="D29">
-        <v>5.082880195393687</v>
+        <v>5.092023036597162</v>
       </c>
       <c r="E29">
-        <v>2.319220000000001</v>
+        <v>2.40608</v>
       </c>
       <c r="F29">
-        <v>2.34522</v>
+        <v>2.43208</v>
       </c>
       <c r="G29">
         <v>3.84</v>
@@ -3790,28 +3790,28 @@
         <v>1.262</v>
       </c>
       <c r="M29">
-        <v>0.121482396</v>
+        <v>0.125981744</v>
       </c>
       <c r="N29">
-        <v>1.140517604</v>
+        <v>1.136018256</v>
       </c>
       <c r="O29">
-        <v>0.3421552812</v>
+        <v>0.3408054768</v>
       </c>
       <c r="P29">
-        <v>0.7983623228000001</v>
+        <v>0.7952127792000001</v>
       </c>
       <c r="Q29">
-        <v>0.8563623228000001</v>
+        <v>0.8532127792000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1363839440668607</v>
+        <v>0.1373422435597697</v>
       </c>
       <c r="T29">
-        <v>0.6315913463975816</v>
+        <v>0.6382730345622277</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.38833643024295</v>
+        <v>10.01732441487713</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1090392153630342</v>
+        <v>0.10907305155726</v>
       </c>
       <c r="C30">
-        <v>6.499943036597162</v>
+        <v>6.412087563247486</v>
       </c>
       <c r="D30">
-        <v>5.092023036597162</v>
+        <v>5.091027563247486</v>
       </c>
       <c r="E30">
-        <v>2.40608</v>
+        <v>2.49294</v>
       </c>
       <c r="F30">
-        <v>2.43208</v>
+        <v>2.51894</v>
       </c>
       <c r="G30">
         <v>3.84</v>
@@ -3872,45 +3872,45 @@
         <v>1.262</v>
       </c>
       <c r="M30">
-        <v>0.125981744</v>
+        <v>0.13476329</v>
       </c>
       <c r="N30">
-        <v>1.136018256</v>
+        <v>1.12723671</v>
       </c>
       <c r="O30">
-        <v>0.3408054768</v>
+        <v>0.338171013</v>
       </c>
       <c r="P30">
-        <v>0.7952127792000001</v>
+        <v>0.7890656970000001</v>
       </c>
       <c r="Q30">
-        <v>0.8532127792000002</v>
+        <v>0.8470656970000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1373422435597697</v>
+        <v>0.1383275374045916</v>
       </c>
       <c r="T30">
-        <v>0.6382730345622277</v>
+        <v>0.6451429392948922</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.3</v>
       </c>
       <c r="W30">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.01732441487713</v>
+        <v>9.36456805113618</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.10907305155726</v>
+        <v>0.1087736877514859</v>
       </c>
       <c r="C31">
-        <v>6.412087563247487</v>
+        <v>6.334048492407137</v>
       </c>
       <c r="D31">
-        <v>5.091027563247486</v>
+        <v>5.099848492407136</v>
       </c>
       <c r="E31">
-        <v>2.49294</v>
+        <v>2.5798</v>
       </c>
       <c r="F31">
-        <v>2.51894</v>
+        <v>2.6058</v>
       </c>
       <c r="G31">
         <v>3.84</v>
@@ -3954,28 +3954,28 @@
         <v>1.262</v>
       </c>
       <c r="M31">
-        <v>0.13476329</v>
+        <v>0.1394103</v>
       </c>
       <c r="N31">
-        <v>1.12723671</v>
+        <v>1.1225897</v>
       </c>
       <c r="O31">
-        <v>0.338171013</v>
+        <v>0.33677691</v>
       </c>
       <c r="P31">
-        <v>0.7890656970000001</v>
+        <v>0.78581279</v>
       </c>
       <c r="Q31">
-        <v>0.8470656970000001</v>
+        <v>0.8438127900000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1383275374045916</v>
+        <v>0.1393409825021227</v>
       </c>
       <c r="T31">
-        <v>0.6451429392948922</v>
+        <v>0.6522091270199184</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.364568051136182</v>
+        <v>9.052415782764976</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1087736877514859</v>
+        <v>0.1084743239457118</v>
       </c>
       <c r="C32">
-        <v>6.334048492407137</v>
+        <v>6.256040041648511</v>
       </c>
       <c r="D32">
-        <v>5.099848492407136</v>
+        <v>5.108700041648511</v>
       </c>
       <c r="E32">
-        <v>2.5798</v>
+        <v>2.66666</v>
       </c>
       <c r="F32">
-        <v>2.6058</v>
+        <v>2.69266</v>
       </c>
       <c r="G32">
         <v>3.84</v>
@@ -4036,28 +4036,28 @@
         <v>1.262</v>
       </c>
       <c r="M32">
-        <v>0.1394103</v>
+        <v>0.14405731</v>
       </c>
       <c r="N32">
-        <v>1.1225897</v>
+        <v>1.11794269</v>
       </c>
       <c r="O32">
-        <v>0.33677691</v>
+        <v>0.335382807</v>
       </c>
       <c r="P32">
-        <v>0.78581279</v>
+        <v>0.782559883</v>
       </c>
       <c r="Q32">
-        <v>0.8438127900000001</v>
+        <v>0.8405598830000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1393409825021227</v>
+        <v>0.1403838028198721</v>
       </c>
       <c r="T32">
-        <v>0.6522091270199184</v>
+        <v>0.6594801317804525</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.052415782764976</v>
+        <v>8.760402370417719</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1084743239457118</v>
+        <v>0.1081749601399376</v>
       </c>
       <c r="C33">
-        <v>6.256040041648511</v>
+        <v>6.178062370686005</v>
       </c>
       <c r="D33">
-        <v>5.108700041648511</v>
+        <v>5.117582370686004</v>
       </c>
       <c r="E33">
-        <v>2.66666</v>
+        <v>2.75352</v>
       </c>
       <c r="F33">
-        <v>2.69266</v>
+        <v>2.77952</v>
       </c>
       <c r="G33">
         <v>3.84</v>
@@ -4118,28 +4118,28 @@
         <v>1.262</v>
       </c>
       <c r="M33">
-        <v>0.14405731</v>
+        <v>0.14870432</v>
       </c>
       <c r="N33">
-        <v>1.11794269</v>
+        <v>1.11329568</v>
       </c>
       <c r="O33">
-        <v>0.335382807</v>
+        <v>0.333988704</v>
       </c>
       <c r="P33">
-        <v>0.782559883</v>
+        <v>0.779306976</v>
       </c>
       <c r="Q33">
-        <v>0.8405598830000001</v>
+        <v>0.837306976</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1403838028198721</v>
+        <v>0.1414572943234377</v>
       </c>
       <c r="T33">
-        <v>0.6594801317804525</v>
+        <v>0.6669649896221789</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.760402370417719</v>
+        <v>8.486639796342164</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1081749601399376</v>
+        <v>0.1078755963341635</v>
       </c>
       <c r="C34">
-        <v>6.178062370686005</v>
+        <v>6.100115640346703</v>
       </c>
       <c r="D34">
-        <v>5.117582370686004</v>
+        <v>5.126495640346702</v>
       </c>
       <c r="E34">
-        <v>2.75352</v>
+        <v>2.84038</v>
       </c>
       <c r="F34">
-        <v>2.77952</v>
+        <v>2.86638</v>
       </c>
       <c r="G34">
         <v>3.84</v>
@@ -4200,28 +4200,28 @@
         <v>1.262</v>
       </c>
       <c r="M34">
-        <v>0.14870432</v>
+        <v>0.15335133</v>
       </c>
       <c r="N34">
-        <v>1.11329568</v>
+        <v>1.10864867</v>
       </c>
       <c r="O34">
-        <v>0.333988704</v>
+        <v>0.332594601</v>
       </c>
       <c r="P34">
-        <v>0.779306976</v>
+        <v>0.776054069</v>
       </c>
       <c r="Q34">
-        <v>0.837306976</v>
+        <v>0.834054069</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1414572943234377</v>
+        <v>0.1425628303494978</v>
       </c>
       <c r="T34">
-        <v>0.6669649896221789</v>
+        <v>0.6746732760561958</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.486639796342164</v>
+        <v>8.229468893422705</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1078755963341635</v>
+        <v>0.1075762325283894</v>
       </c>
       <c r="C35">
-        <v>6.100115640346703</v>
+        <v>6.022200012580094</v>
       </c>
       <c r="D35">
-        <v>5.126495640346702</v>
+        <v>5.135440012580095</v>
       </c>
       <c r="E35">
-        <v>2.84038</v>
+        <v>2.92724</v>
       </c>
       <c r="F35">
-        <v>2.86638</v>
+        <v>2.95324</v>
       </c>
       <c r="G35">
         <v>3.84</v>
@@ -4282,28 +4282,28 @@
         <v>1.262</v>
       </c>
       <c r="M35">
-        <v>0.15335133</v>
+        <v>0.15799834</v>
       </c>
       <c r="N35">
-        <v>1.10864867</v>
+        <v>1.10400166</v>
       </c>
       <c r="O35">
-        <v>0.332594601</v>
+        <v>0.331200498</v>
       </c>
       <c r="P35">
-        <v>0.776054069</v>
+        <v>0.7728011619999999</v>
       </c>
       <c r="Q35">
-        <v>0.834054069</v>
+        <v>0.830801162</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1425628303494978</v>
+        <v>0.1437018674672567</v>
       </c>
       <c r="T35">
-        <v>0.6746732760561958</v>
+        <v>0.6826151469276068</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.229468893422705</v>
+        <v>7.987425690674978</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1075762325283894</v>
+        <v>0.1072768687226153</v>
       </c>
       <c r="C36">
-        <v>6.022200012580094</v>
+        <v>5.944315650467882</v>
       </c>
       <c r="D36">
-        <v>5.135440012580095</v>
+        <v>5.144415650467883</v>
       </c>
       <c r="E36">
-        <v>2.92724</v>
+        <v>3.0141</v>
       </c>
       <c r="F36">
-        <v>2.95324</v>
+        <v>3.0401</v>
       </c>
       <c r="G36">
         <v>3.84</v>
@@ -4364,28 +4364,28 @@
         <v>1.262</v>
       </c>
       <c r="M36">
-        <v>0.15799834</v>
+        <v>0.16264535</v>
       </c>
       <c r="N36">
-        <v>1.10400166</v>
+        <v>1.09935465</v>
       </c>
       <c r="O36">
-        <v>0.331200498</v>
+        <v>0.329806395</v>
       </c>
       <c r="P36">
-        <v>0.7728011619999999</v>
+        <v>0.769548255</v>
       </c>
       <c r="Q36">
-        <v>0.830801162</v>
+        <v>0.8275482550000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1437018674672567</v>
+        <v>0.1448759518809466</v>
       </c>
       <c r="T36">
-        <v>0.6826151469276068</v>
+        <v>0.6908013830565999</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.987425690674978</v>
+        <v>7.759213528084263</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1072768687226153</v>
+        <v>0.1071791049168411</v>
       </c>
       <c r="C37">
-        <v>5.944315650467882</v>
+        <v>5.860393641580083</v>
       </c>
       <c r="D37">
-        <v>5.144415650467883</v>
+        <v>5.147353641580084</v>
       </c>
       <c r="E37">
-        <v>3.0141</v>
+        <v>3.100960000000001</v>
       </c>
       <c r="F37">
-        <v>3.0401</v>
+        <v>3.12696</v>
       </c>
       <c r="G37">
         <v>3.84</v>
@@ -4446,45 +4446,45 @@
         <v>1.262</v>
       </c>
       <c r="M37">
-        <v>0.16264535</v>
+        <v>0.169793928</v>
       </c>
       <c r="N37">
-        <v>1.09935465</v>
+        <v>1.092206072</v>
       </c>
       <c r="O37">
-        <v>0.329806395</v>
+        <v>0.3276618216</v>
       </c>
       <c r="P37">
-        <v>0.769548255</v>
+        <v>0.7645442504</v>
       </c>
       <c r="Q37">
-        <v>0.8275482550000001</v>
+        <v>0.8225442504</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1448759518809466</v>
+        <v>0.1460867264325643</v>
       </c>
       <c r="T37">
-        <v>0.6908013830565999</v>
+        <v>0.6992434390646241</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.3</v>
       </c>
       <c r="W37">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.759213528084263</v>
+        <v>7.432539048157245</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1071791049168412</v>
+        <v>0.106885341111067</v>
       </c>
       <c r="C38">
-        <v>5.860393641580083</v>
+        <v>5.782382037348649</v>
       </c>
       <c r="D38">
-        <v>5.147353641580084</v>
+        <v>5.156202037348649</v>
       </c>
       <c r="E38">
-        <v>3.10096</v>
+        <v>3.18782</v>
       </c>
       <c r="F38">
-        <v>3.12696</v>
+        <v>3.21382</v>
       </c>
       <c r="G38">
         <v>3.84</v>
@@ -4528,28 +4528,28 @@
         <v>1.262</v>
       </c>
       <c r="M38">
-        <v>0.169793928</v>
+        <v>0.174510426</v>
       </c>
       <c r="N38">
-        <v>1.092206072</v>
+        <v>1.087489574</v>
       </c>
       <c r="O38">
-        <v>0.3276618216</v>
+        <v>0.3262468722</v>
       </c>
       <c r="P38">
-        <v>0.7645442504</v>
+        <v>0.7612427018000001</v>
       </c>
       <c r="Q38">
-        <v>0.8225442504</v>
+        <v>0.8192427018000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1460867264325643</v>
+        <v>0.1473359382715349</v>
       </c>
       <c r="T38">
-        <v>0.6992434390646241</v>
+        <v>0.7079534968506805</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.432539048157246</v>
+        <v>7.231659614423267</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.106885341111067</v>
+        <v>0.1065915773052929</v>
       </c>
       <c r="C39">
-        <v>5.782382037348649</v>
+        <v>5.704400906612495</v>
       </c>
       <c r="D39">
-        <v>5.156202037348649</v>
+        <v>5.165080906612494</v>
       </c>
       <c r="E39">
-        <v>3.18782</v>
+        <v>3.27468</v>
       </c>
       <c r="F39">
-        <v>3.21382</v>
+        <v>3.30068</v>
       </c>
       <c r="G39">
         <v>3.84</v>
@@ -4610,28 +4610,28 @@
         <v>1.262</v>
       </c>
       <c r="M39">
-        <v>0.174510426</v>
+        <v>0.179226924</v>
       </c>
       <c r="N39">
-        <v>1.087489574</v>
+        <v>1.082773076</v>
       </c>
       <c r="O39">
-        <v>0.3262468722</v>
+        <v>0.3248319228</v>
       </c>
       <c r="P39">
-        <v>0.7612427018000001</v>
+        <v>0.7579411532</v>
       </c>
       <c r="Q39">
-        <v>0.8192427018000001</v>
+        <v>0.8159411532</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1473359382715349</v>
+        <v>0.1486254472666014</v>
       </c>
       <c r="T39">
-        <v>0.7079534968506805</v>
+        <v>0.716944524242739</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.231659614423267</v>
+        <v>7.04135278246476</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1065915773052929</v>
+        <v>0.1062978134995188</v>
       </c>
       <c r="C40">
-        <v>5.704400906612495</v>
+        <v>5.626450407067283</v>
       </c>
       <c r="D40">
-        <v>5.165080906612494</v>
+        <v>5.173990407067283</v>
       </c>
       <c r="E40">
-        <v>3.27468</v>
+        <v>3.36154</v>
       </c>
       <c r="F40">
-        <v>3.30068</v>
+        <v>3.38754</v>
       </c>
       <c r="G40">
         <v>3.84</v>
@@ -4692,28 +4692,28 @@
         <v>1.262</v>
       </c>
       <c r="M40">
-        <v>0.179226924</v>
+        <v>0.183943422</v>
       </c>
       <c r="N40">
-        <v>1.082773076</v>
+        <v>1.078056578</v>
       </c>
       <c r="O40">
-        <v>0.3248319228</v>
+        <v>0.3234169734</v>
       </c>
       <c r="P40">
-        <v>0.7579411532</v>
+        <v>0.7546396046</v>
       </c>
       <c r="Q40">
-        <v>0.8159411532</v>
+        <v>0.8126396046000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1486254472666014</v>
+        <v>0.1499572352451127</v>
       </c>
       <c r="T40">
-        <v>0.716944524242739</v>
+        <v>0.7262303394181436</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.04135278246476</v>
+        <v>6.860805275222074</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1062978134995188</v>
+        <v>0.1060040496937446</v>
       </c>
       <c r="C41">
-        <v>5.626450407067283</v>
+        <v>5.548530697498626</v>
       </c>
       <c r="D41">
-        <v>5.173990407067283</v>
+        <v>5.182930697498627</v>
       </c>
       <c r="E41">
-        <v>3.36154</v>
+        <v>3.4484</v>
       </c>
       <c r="F41">
-        <v>3.38754</v>
+        <v>3.4744</v>
       </c>
       <c r="G41">
         <v>3.84</v>
@@ -4774,28 +4774,28 @@
         <v>1.262</v>
       </c>
       <c r="M41">
-        <v>0.183943422</v>
+        <v>0.18865992</v>
       </c>
       <c r="N41">
-        <v>1.078056578</v>
+        <v>1.07334008</v>
       </c>
       <c r="O41">
-        <v>0.3234169734</v>
+        <v>0.3220020239999999</v>
       </c>
       <c r="P41">
-        <v>0.7546396046</v>
+        <v>0.751338056</v>
       </c>
       <c r="Q41">
-        <v>0.8126396046000001</v>
+        <v>0.8093380560000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1499572352451127</v>
+        <v>0.151333416156241</v>
       </c>
       <c r="T41">
-        <v>0.7262303394181436</v>
+        <v>0.7358256817660618</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.860805275222074</v>
+        <v>6.689285143341521</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1060040496937446</v>
+        <v>0.1057102858879705</v>
       </c>
       <c r="C42">
-        <v>5.548530697498626</v>
+        <v>5.470641937791516</v>
       </c>
       <c r="D42">
-        <v>5.182930697498627</v>
+        <v>5.191901937791516</v>
       </c>
       <c r="E42">
-        <v>3.4484</v>
+        <v>3.535260000000001</v>
       </c>
       <c r="F42">
-        <v>3.4744</v>
+        <v>3.56126</v>
       </c>
       <c r="G42">
         <v>3.84</v>
@@ -4856,28 +4856,28 @@
         <v>1.262</v>
       </c>
       <c r="M42">
-        <v>0.18865992</v>
+        <v>0.193376418</v>
       </c>
       <c r="N42">
-        <v>1.07334008</v>
+        <v>1.068623582</v>
       </c>
       <c r="O42">
-        <v>0.3220020239999999</v>
+        <v>0.3205870746</v>
       </c>
       <c r="P42">
-        <v>0.751338056</v>
+        <v>0.7480365074000001</v>
       </c>
       <c r="Q42">
-        <v>0.8093380560000001</v>
+        <v>0.8060365074000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.151333416156241</v>
+        <v>0.1527562472677466</v>
       </c>
       <c r="T42">
-        <v>0.7358256817660618</v>
+        <v>0.7457462899562821</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.689285143341521</v>
+        <v>6.52613184716246</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1057102858879705</v>
+        <v>0.1054165220821963</v>
       </c>
       <c r="C43">
-        <v>5.470641937791516</v>
+        <v>5.392784288939859</v>
       </c>
       <c r="D43">
-        <v>5.191901937791516</v>
+        <v>5.200904288939859</v>
       </c>
       <c r="E43">
-        <v>3.535260000000001</v>
+        <v>3.622120000000001</v>
       </c>
       <c r="F43">
-        <v>3.56126</v>
+        <v>3.64812</v>
       </c>
       <c r="G43">
         <v>3.84</v>
@@ -4938,28 +4938,28 @@
         <v>1.262</v>
       </c>
       <c r="M43">
-        <v>0.193376418</v>
+        <v>0.198092916</v>
       </c>
       <c r="N43">
-        <v>1.068623582</v>
+        <v>1.063907084</v>
       </c>
       <c r="O43">
-        <v>0.3205870746</v>
+        <v>0.3191721252</v>
       </c>
       <c r="P43">
-        <v>0.7480365074000001</v>
+        <v>0.7447349588000001</v>
       </c>
       <c r="Q43">
-        <v>0.8060365074000001</v>
+        <v>0.8027349588000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1527562472677466</v>
+        <v>0.1542281415210282</v>
       </c>
       <c r="T43">
-        <v>0.7457462899562821</v>
+        <v>0.7560089880840963</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.52613184716246</v>
+        <v>6.370747755563353</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1054165220821964</v>
+        <v>0.1051227582764222</v>
       </c>
       <c r="C44">
-        <v>5.392784288939858</v>
+        <v>5.314957913056098</v>
       </c>
       <c r="D44">
-        <v>5.200904288939858</v>
+        <v>5.209937913056098</v>
       </c>
       <c r="E44">
-        <v>3.62212</v>
+        <v>3.70898</v>
       </c>
       <c r="F44">
-        <v>3.64812</v>
+        <v>3.73498</v>
       </c>
       <c r="G44">
         <v>3.84</v>
@@ -5020,28 +5020,28 @@
         <v>1.262</v>
       </c>
       <c r="M44">
-        <v>0.198092916</v>
+        <v>0.202809414</v>
       </c>
       <c r="N44">
-        <v>1.063907084</v>
+        <v>1.059190586</v>
       </c>
       <c r="O44">
-        <v>0.3191721252</v>
+        <v>0.3177571758</v>
       </c>
       <c r="P44">
-        <v>0.7447349588000001</v>
+        <v>0.7414334102</v>
       </c>
       <c r="Q44">
-        <v>0.8027349588000001</v>
+        <v>0.7994334102</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1542281415210282</v>
+        <v>0.1557516811867057</v>
       </c>
       <c r="T44">
-        <v>0.7560089880840962</v>
+        <v>0.7666317808830618</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.370747755563354</v>
+        <v>6.222590831015369</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1051227582764222</v>
+        <v>0.1051369944706481</v>
       </c>
       <c r="C45">
-        <v>5.314957913056098</v>
+        <v>5.227659407837924</v>
       </c>
       <c r="D45">
-        <v>5.209937913056098</v>
+        <v>5.209499407837924</v>
       </c>
       <c r="E45">
-        <v>3.70898</v>
+        <v>3.79584</v>
       </c>
       <c r="F45">
-        <v>3.73498</v>
+        <v>3.82184</v>
       </c>
       <c r="G45">
         <v>3.84</v>
@@ -5102,45 +5102,45 @@
         <v>1.262</v>
       </c>
       <c r="M45">
-        <v>0.202809414</v>
+        <v>0.211347752</v>
       </c>
       <c r="N45">
-        <v>1.059190586</v>
+        <v>1.050652248</v>
       </c>
       <c r="O45">
-        <v>0.3177571758</v>
+        <v>0.3151956744</v>
       </c>
       <c r="P45">
-        <v>0.7414334102</v>
+        <v>0.7354565736000001</v>
       </c>
       <c r="Q45">
-        <v>0.7994334102</v>
+        <v>0.7934565736000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1557516811867057</v>
+        <v>0.1573296329833002</v>
       </c>
       <c r="T45">
-        <v>0.7666317808830618</v>
+        <v>0.7776339591391334</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.222590831015369</v>
+        <v>5.971201434874973</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1051369944706481</v>
+        <v>0.104850230664874</v>
       </c>
       <c r="C46">
-        <v>5.227659407837924</v>
+        <v>5.149646602244395</v>
       </c>
       <c r="D46">
-        <v>5.209499407837924</v>
+        <v>5.218346602244395</v>
       </c>
       <c r="E46">
-        <v>3.79584</v>
+        <v>3.8827</v>
       </c>
       <c r="F46">
-        <v>3.82184</v>
+        <v>3.9087</v>
       </c>
       <c r="G46">
         <v>3.84</v>
@@ -5184,28 +5184,28 @@
         <v>1.262</v>
       </c>
       <c r="M46">
-        <v>0.211347752</v>
+        <v>0.21615111</v>
       </c>
       <c r="N46">
-        <v>1.050652248</v>
+        <v>1.04584889</v>
       </c>
       <c r="O46">
-        <v>0.3151956744</v>
+        <v>0.313754667</v>
       </c>
       <c r="P46">
-        <v>0.7354565736000001</v>
+        <v>0.732094223</v>
       </c>
       <c r="Q46">
-        <v>0.7934565736000001</v>
+        <v>0.7900942230000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1573296329833002</v>
+        <v>0.1589649648452254</v>
       </c>
       <c r="T46">
-        <v>0.7776339591391334</v>
+        <v>0.7890362166045166</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.971201434874973</v>
+        <v>5.838508069655529</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.104850230664874</v>
+        <v>0.1045634668590999</v>
       </c>
       <c r="C47">
-        <v>5.149646602244395</v>
+        <v>5.071663897817278</v>
       </c>
       <c r="D47">
-        <v>5.218346602244395</v>
+        <v>5.227223897817278</v>
       </c>
       <c r="E47">
-        <v>3.8827</v>
+        <v>3.96956</v>
       </c>
       <c r="F47">
-        <v>3.9087</v>
+        <v>3.99556</v>
       </c>
       <c r="G47">
         <v>3.84</v>
@@ -5266,28 +5266,28 @@
         <v>1.262</v>
       </c>
       <c r="M47">
-        <v>0.21615111</v>
+        <v>0.220954468</v>
       </c>
       <c r="N47">
-        <v>1.04584889</v>
+        <v>1.041045532</v>
       </c>
       <c r="O47">
-        <v>0.313754667</v>
+        <v>0.3123136596</v>
       </c>
       <c r="P47">
-        <v>0.732094223</v>
+        <v>0.7287318724</v>
       </c>
       <c r="Q47">
-        <v>0.7900942230000001</v>
+        <v>0.7867318724000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1589649648452254</v>
+        <v>0.1606608645538886</v>
       </c>
       <c r="T47">
-        <v>0.7890362166045166</v>
+        <v>0.8008607799019509</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.838508069655529</v>
+        <v>5.711583981184757</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1045634668590999</v>
+        <v>0.1042767030533257</v>
       </c>
       <c r="C48">
-        <v>5.071663897817278</v>
+        <v>4.993711448439975</v>
       </c>
       <c r="D48">
-        <v>5.227223897817278</v>
+        <v>5.236131448439975</v>
       </c>
       <c r="E48">
-        <v>3.96956</v>
+        <v>4.05642</v>
       </c>
       <c r="F48">
-        <v>3.99556</v>
+        <v>4.08242</v>
       </c>
       <c r="G48">
         <v>3.84</v>
@@ -5348,28 +5348,28 @@
         <v>1.262</v>
       </c>
       <c r="M48">
-        <v>0.220954468</v>
+        <v>0.225757826</v>
       </c>
       <c r="N48">
-        <v>1.041045532</v>
+        <v>1.036242174</v>
       </c>
       <c r="O48">
-        <v>0.3123136596</v>
+        <v>0.3108726522</v>
       </c>
       <c r="P48">
-        <v>0.7287318724</v>
+        <v>0.7253695218</v>
       </c>
       <c r="Q48">
-        <v>0.7867318724000001</v>
+        <v>0.7833695218000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1606608645538886</v>
+        <v>0.162420760477973</v>
       </c>
       <c r="T48">
-        <v>0.8008607799019509</v>
+        <v>0.8131315531351376</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.711583981184757</v>
+        <v>5.590060917755294</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1042767030533257</v>
+        <v>0.1039899392475516</v>
       </c>
       <c r="C49">
-        <v>4.993711448439975</v>
+        <v>4.915789409046589</v>
       </c>
       <c r="D49">
-        <v>5.236131448439975</v>
+        <v>5.245069409046589</v>
       </c>
       <c r="E49">
-        <v>4.05642</v>
+        <v>4.143280000000001</v>
       </c>
       <c r="F49">
-        <v>4.08242</v>
+        <v>4.169280000000001</v>
       </c>
       <c r="G49">
         <v>3.84</v>
@@ -5430,28 +5430,28 @@
         <v>1.262</v>
       </c>
       <c r="M49">
-        <v>0.225757826</v>
+        <v>0.230561184</v>
       </c>
       <c r="N49">
-        <v>1.036242174</v>
+        <v>1.031438816</v>
       </c>
       <c r="O49">
-        <v>0.3108726522</v>
+        <v>0.3094316448</v>
       </c>
       <c r="P49">
-        <v>0.7253695218</v>
+        <v>0.7220071712</v>
       </c>
       <c r="Q49">
-        <v>0.7833695218000001</v>
+        <v>0.7800071712000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.162420760477973</v>
+        <v>0.16424834470683</v>
       </c>
       <c r="T49">
-        <v>0.8131315531351376</v>
+        <v>0.8258742791849853</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.590060917755294</v>
+        <v>5.473601315302059</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1039899392475516</v>
+        <v>0.1037031754417775</v>
       </c>
       <c r="C50">
-        <v>4.91578940904659</v>
+        <v>4.837897935630908</v>
       </c>
       <c r="D50">
-        <v>5.245069409046589</v>
+        <v>5.254037935630909</v>
       </c>
       <c r="E50">
-        <v>4.14328</v>
+        <v>4.23014</v>
       </c>
       <c r="F50">
-        <v>4.16928</v>
+        <v>4.25614</v>
       </c>
       <c r="G50">
         <v>3.84</v>
@@ -5512,28 +5512,28 @@
         <v>1.262</v>
       </c>
       <c r="M50">
-        <v>0.230561184</v>
+        <v>0.235364542</v>
       </c>
       <c r="N50">
-        <v>1.031438816</v>
+        <v>1.026635458</v>
       </c>
       <c r="O50">
-        <v>0.3094316448</v>
+        <v>0.3079906373999999</v>
       </c>
       <c r="P50">
-        <v>0.7220071712</v>
+        <v>0.7186448206</v>
       </c>
       <c r="Q50">
-        <v>0.7800071712000001</v>
+        <v>0.7766448206000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.16424834470683</v>
+        <v>0.166147598905446</v>
       </c>
       <c r="T50">
-        <v>0.8258742791849853</v>
+        <v>0.8391167199818859</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.47360131530206</v>
+        <v>5.361895166010179</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1037031754417775</v>
+        <v>0.1034164116360033</v>
       </c>
       <c r="C51">
-        <v>4.837897935630908</v>
+        <v>4.760037185255481</v>
       </c>
       <c r="D51">
-        <v>5.254037935630909</v>
+        <v>5.263037185255482</v>
       </c>
       <c r="E51">
-        <v>4.23014</v>
+        <v>4.317</v>
       </c>
       <c r="F51">
-        <v>4.25614</v>
+        <v>4.343</v>
       </c>
       <c r="G51">
         <v>3.84</v>
@@ -5594,28 +5594,28 @@
         <v>1.262</v>
       </c>
       <c r="M51">
-        <v>0.235364542</v>
+        <v>0.2401679</v>
       </c>
       <c r="N51">
-        <v>1.026635458</v>
+        <v>1.0218321</v>
       </c>
       <c r="O51">
-        <v>0.3079906373999999</v>
+        <v>0.30654963</v>
       </c>
       <c r="P51">
-        <v>0.7186448206</v>
+        <v>0.71528247</v>
       </c>
       <c r="Q51">
-        <v>0.7766448206000001</v>
+        <v>0.7732824700000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.166147598905446</v>
+        <v>0.1681228232720066</v>
       </c>
       <c r="T51">
-        <v>0.8391167199818859</v>
+        <v>0.8528888584106624</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.361895166010179</v>
+        <v>5.254657262689975</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1034164116360033</v>
+        <v>0.1031296478302292</v>
       </c>
       <c r="C52">
-        <v>4.760037185255481</v>
+        <v>4.682207316060788</v>
       </c>
       <c r="D52">
-        <v>5.263037185255482</v>
+        <v>5.272067316060787</v>
       </c>
       <c r="E52">
-        <v>4.317</v>
+        <v>4.40386</v>
       </c>
       <c r="F52">
-        <v>4.343</v>
+        <v>4.42986</v>
       </c>
       <c r="G52">
         <v>3.84</v>
@@ -5676,28 +5676,28 @@
         <v>1.262</v>
       </c>
       <c r="M52">
-        <v>0.2401679</v>
+        <v>0.244971258</v>
       </c>
       <c r="N52">
-        <v>1.0218321</v>
+        <v>1.017028742</v>
       </c>
       <c r="O52">
-        <v>0.30654963</v>
+        <v>0.3051086226</v>
       </c>
       <c r="P52">
-        <v>0.71528247</v>
+        <v>0.7119201194</v>
       </c>
       <c r="Q52">
-        <v>0.7732824700000001</v>
+        <v>0.7699201194</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1681228232720066</v>
+        <v>0.1701786690412841</v>
       </c>
       <c r="T52">
-        <v>0.8528888584106624</v>
+        <v>0.8672231249385728</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.254657262689975</v>
+        <v>5.151624767343114</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1031296478302292</v>
+        <v>0.1028428840244551</v>
       </c>
       <c r="C53">
-        <v>4.682207316060788</v>
+        <v>4.604408487274495</v>
       </c>
       <c r="D53">
-        <v>5.272067316060787</v>
+        <v>5.281128487274495</v>
       </c>
       <c r="E53">
-        <v>4.40386</v>
+        <v>4.49072</v>
       </c>
       <c r="F53">
-        <v>4.42986</v>
+        <v>4.51672</v>
       </c>
       <c r="G53">
         <v>3.84</v>
@@ -5758,28 +5758,28 @@
         <v>1.262</v>
       </c>
       <c r="M53">
-        <v>0.244971258</v>
+        <v>0.249774616</v>
       </c>
       <c r="N53">
-        <v>1.017028742</v>
+        <v>1.012225384</v>
       </c>
       <c r="O53">
-        <v>0.3051086226</v>
+        <v>0.3036676152</v>
       </c>
       <c r="P53">
-        <v>0.7119201194</v>
+        <v>0.7085577688</v>
       </c>
       <c r="Q53">
-        <v>0.7699201194</v>
+        <v>0.7665577688</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1701786690412841</v>
+        <v>0.1723201750509481</v>
       </c>
       <c r="T53">
-        <v>0.8672231249385728</v>
+        <v>0.8821546525718126</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.151624767343114</v>
+        <v>5.052555060278823</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1028428840244551</v>
+        <v>0.1025561202186809</v>
       </c>
       <c r="C54">
-        <v>4.604408487274495</v>
+        <v>4.526640859220827</v>
       </c>
       <c r="D54">
-        <v>5.281128487274495</v>
+        <v>5.290220859220828</v>
       </c>
       <c r="E54">
-        <v>4.49072</v>
+        <v>4.57758</v>
       </c>
       <c r="F54">
-        <v>4.51672</v>
+        <v>4.60358</v>
       </c>
       <c r="G54">
         <v>3.84</v>
@@ -5840,28 +5840,28 @@
         <v>1.262</v>
       </c>
       <c r="M54">
-        <v>0.249774616</v>
+        <v>0.254577974</v>
       </c>
       <c r="N54">
-        <v>1.012225384</v>
+        <v>1.007422026</v>
       </c>
       <c r="O54">
-        <v>0.3036676152</v>
+        <v>0.3022266078</v>
       </c>
       <c r="P54">
-        <v>0.7085577688</v>
+        <v>0.7051954182</v>
       </c>
       <c r="Q54">
-        <v>0.7665577688</v>
+        <v>0.7631954182</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1723201750509481</v>
+        <v>0.1745528089759169</v>
       </c>
       <c r="T54">
-        <v>0.8821546525718126</v>
+        <v>0.8977215643596584</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.052555060278823</v>
+        <v>4.957223832726394</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1025561202186809</v>
+        <v>0.1022693564129068</v>
       </c>
       <c r="C55">
-        <v>4.526640859220827</v>
+        <v>4.448904593330015</v>
       </c>
       <c r="D55">
-        <v>5.290220859220828</v>
+        <v>5.299344593330017</v>
       </c>
       <c r="E55">
-        <v>4.57758</v>
+        <v>4.664440000000001</v>
       </c>
       <c r="F55">
-        <v>4.60358</v>
+        <v>4.690440000000001</v>
       </c>
       <c r="G55">
         <v>3.84</v>
@@ -5922,28 +5922,28 @@
         <v>1.262</v>
       </c>
       <c r="M55">
-        <v>0.254577974</v>
+        <v>0.259381332</v>
       </c>
       <c r="N55">
-        <v>1.007422026</v>
+        <v>1.002618668</v>
       </c>
       <c r="O55">
-        <v>0.3022266078</v>
+        <v>0.3007856004</v>
       </c>
       <c r="P55">
-        <v>0.7051954182</v>
+        <v>0.7018330676</v>
       </c>
       <c r="Q55">
-        <v>0.7631954182</v>
+        <v>0.7598330676</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1745528089759169</v>
+        <v>0.1768825139411018</v>
       </c>
       <c r="T55">
-        <v>0.8977215643596584</v>
+        <v>0.9139652983991498</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.957223832726394</v>
+        <v>4.865423391379608</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1022693564129068</v>
+        <v>0.1019825926071327</v>
       </c>
       <c r="C56">
-        <v>4.448904593330015</v>
+        <v>4.371199852147846</v>
       </c>
       <c r="D56">
-        <v>5.299344593330017</v>
+        <v>5.308499852147848</v>
       </c>
       <c r="E56">
-        <v>4.664440000000001</v>
+        <v>4.751300000000001</v>
       </c>
       <c r="F56">
-        <v>4.690440000000001</v>
+        <v>4.7773</v>
       </c>
       <c r="G56">
         <v>3.84</v>
@@ -6004,28 +6004,28 @@
         <v>1.262</v>
       </c>
       <c r="M56">
-        <v>0.259381332</v>
+        <v>0.26418469</v>
       </c>
       <c r="N56">
-        <v>1.002618668</v>
+        <v>0.99781531</v>
       </c>
       <c r="O56">
-        <v>0.3007856004</v>
+        <v>0.299344593</v>
       </c>
       <c r="P56">
-        <v>0.7018330676</v>
+        <v>0.698470717</v>
       </c>
       <c r="Q56">
-        <v>0.7598330676</v>
+        <v>0.756470717</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1768825139411018</v>
+        <v>0.1793157613491838</v>
       </c>
       <c r="T56">
-        <v>0.9139652983991498</v>
+        <v>0.9309309761737297</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.865423391379608</v>
+        <v>4.776961147899978</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1019825926071327</v>
+        <v>0.1016958288013586</v>
       </c>
       <c r="C57">
-        <v>4.371199852147846</v>
+        <v>4.293526799345328</v>
       </c>
       <c r="D57">
-        <v>5.308499852147848</v>
+        <v>5.317686799345328</v>
       </c>
       <c r="E57">
-        <v>4.751300000000001</v>
+        <v>4.83816</v>
       </c>
       <c r="F57">
-        <v>4.7773</v>
+        <v>4.86416</v>
       </c>
       <c r="G57">
         <v>3.84</v>
@@ -6086,28 +6086,28 @@
         <v>1.262</v>
       </c>
       <c r="M57">
-        <v>0.26418469</v>
+        <v>0.268988048</v>
       </c>
       <c r="N57">
-        <v>0.99781531</v>
+        <v>0.993011952</v>
       </c>
       <c r="O57">
-        <v>0.299344593</v>
+        <v>0.2979035856</v>
       </c>
       <c r="P57">
-        <v>0.698470717</v>
+        <v>0.6951083664</v>
       </c>
       <c r="Q57">
-        <v>0.756470717</v>
+        <v>0.7531083664</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1793157613491838</v>
+        <v>0.1818596109121786</v>
       </c>
       <c r="T57">
-        <v>0.9309309761737297</v>
+        <v>0.9486678211198813</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.776961147899978</v>
+        <v>4.691658270258907</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1016958288013586</v>
+        <v>0.1014090649955844</v>
       </c>
       <c r="C58">
-        <v>4.293526799345328</v>
+        <v>4.215885599728426</v>
       </c>
       <c r="D58">
-        <v>5.317686799345328</v>
+        <v>5.326905599728428</v>
       </c>
       <c r="E58">
-        <v>4.83816</v>
+        <v>4.925020000000001</v>
       </c>
       <c r="F58">
-        <v>4.86416</v>
+        <v>4.951020000000001</v>
       </c>
       <c r="G58">
         <v>3.84</v>
@@ -6168,28 +6168,28 @@
         <v>1.262</v>
       </c>
       <c r="M58">
-        <v>0.268988048</v>
+        <v>0.2737914060000001</v>
       </c>
       <c r="N58">
-        <v>0.993011952</v>
+        <v>0.9882085939999999</v>
       </c>
       <c r="O58">
-        <v>0.2979035856</v>
+        <v>0.2964625782</v>
       </c>
       <c r="P58">
-        <v>0.6951083664</v>
+        <v>0.6917460157999999</v>
       </c>
       <c r="Q58">
-        <v>0.7531083664</v>
+        <v>0.7497460158</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1818596109121786</v>
+        <v>0.1845217790594987</v>
       </c>
       <c r="T58">
-        <v>0.9486678211198813</v>
+        <v>0.967229635598412</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.691658270258907</v>
+        <v>4.609348476043838</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1014090649955844</v>
+        <v>0.1011223011898103</v>
       </c>
       <c r="C59">
-        <v>4.215885599728426</v>
+        <v>4.138276419247942</v>
       </c>
       <c r="D59">
-        <v>5.326905599728428</v>
+        <v>5.336156419247941</v>
       </c>
       <c r="E59">
-        <v>4.925020000000001</v>
+        <v>5.011880000000001</v>
       </c>
       <c r="F59">
-        <v>4.951020000000001</v>
+        <v>5.03788</v>
       </c>
       <c r="G59">
         <v>3.84</v>
@@ -6250,28 +6250,28 @@
         <v>1.262</v>
       </c>
       <c r="M59">
-        <v>0.2737914060000001</v>
+        <v>0.2785947640000001</v>
       </c>
       <c r="N59">
-        <v>0.9882085939999999</v>
+        <v>0.983405236</v>
       </c>
       <c r="O59">
-        <v>0.2964625782</v>
+        <v>0.2950215708</v>
       </c>
       <c r="P59">
-        <v>0.6917460157999999</v>
+        <v>0.6883836651999999</v>
       </c>
       <c r="Q59">
-        <v>0.7497460158</v>
+        <v>0.7463836652</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1845217790594987</v>
+        <v>0.187310717118596</v>
       </c>
       <c r="T59">
-        <v>0.967229635598412</v>
+        <v>0.9866753460044919</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.609348476043838</v>
+        <v>4.529876950594806</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1011223011898103</v>
+        <v>0.1018680373840362</v>
       </c>
       <c r="C60">
-        <v>4.138276419247941</v>
+        <v>4.02742600580943</v>
       </c>
       <c r="D60">
-        <v>5.33615641924794</v>
+        <v>5.312166005809432</v>
       </c>
       <c r="E60">
-        <v>5.01188</v>
+        <v>5.09874</v>
       </c>
       <c r="F60">
-        <v>5.037879999999999</v>
+        <v>5.12474</v>
       </c>
       <c r="G60">
         <v>3.84</v>
@@ -6332,45 +6332,45 @@
         <v>1.262</v>
       </c>
       <c r="M60">
-        <v>0.278594764</v>
+        <v>0.296209972</v>
       </c>
       <c r="N60">
-        <v>0.9834052360000001</v>
+        <v>0.965790028</v>
       </c>
       <c r="O60">
-        <v>0.2950215708</v>
+        <v>0.2897370084</v>
       </c>
       <c r="P60">
-        <v>0.6883836652</v>
+        <v>0.6760530196000001</v>
       </c>
       <c r="Q60">
-        <v>0.7463836652000001</v>
+        <v>0.7340530196000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1873107171185959</v>
+        <v>0.1902357009366736</v>
       </c>
       <c r="T60">
-        <v>0.9866753460044917</v>
+        <v>1.007069627649892</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.3</v>
       </c>
       <c r="W60">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.529876950594808</v>
+        <v>4.260491270699015</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1018680373840362</v>
+        <v>0.101598773578262</v>
       </c>
       <c r="C61">
-        <v>4.02742600580943</v>
+        <v>3.949203328499267</v>
       </c>
       <c r="D61">
-        <v>5.312166005809432</v>
+        <v>5.320803328499268</v>
       </c>
       <c r="E61">
-        <v>5.09874</v>
+        <v>5.1856</v>
       </c>
       <c r="F61">
-        <v>5.12474</v>
+        <v>5.2116</v>
       </c>
       <c r="G61">
         <v>3.84</v>
@@ -6414,28 +6414,28 @@
         <v>1.262</v>
       </c>
       <c r="M61">
-        <v>0.296209972</v>
+        <v>0.30123048</v>
       </c>
       <c r="N61">
-        <v>0.965790028</v>
+        <v>0.9607695199999999</v>
       </c>
       <c r="O61">
-        <v>0.2897370084</v>
+        <v>0.288230856</v>
       </c>
       <c r="P61">
-        <v>0.6760530196000001</v>
+        <v>0.672538664</v>
       </c>
       <c r="Q61">
-        <v>0.7340530196000001</v>
+        <v>0.730538664</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1902357009366736</v>
+        <v>0.1933069339456551</v>
       </c>
       <c r="T61">
-        <v>1.007069627649892</v>
+        <v>1.028483623377563</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.260491270699015</v>
+        <v>4.189483082854032</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.101598773578262</v>
+        <v>0.1013295097724879</v>
       </c>
       <c r="C62">
-        <v>3.949203328499267</v>
+        <v>3.871008784663135</v>
       </c>
       <c r="D62">
-        <v>5.320803328499268</v>
+        <v>5.329468784663136</v>
       </c>
       <c r="E62">
-        <v>5.1856</v>
+        <v>5.27246</v>
       </c>
       <c r="F62">
-        <v>5.2116</v>
+        <v>5.29846</v>
       </c>
       <c r="G62">
         <v>3.84</v>
@@ -6496,28 +6496,28 @@
         <v>1.262</v>
       </c>
       <c r="M62">
-        <v>0.30123048</v>
+        <v>0.306250988</v>
       </c>
       <c r="N62">
-        <v>0.9607695199999999</v>
+        <v>0.9557490120000001</v>
       </c>
       <c r="O62">
-        <v>0.288230856</v>
+        <v>0.2867247036</v>
       </c>
       <c r="P62">
-        <v>0.672538664</v>
+        <v>0.6690243084</v>
       </c>
       <c r="Q62">
-        <v>0.730538664</v>
+        <v>0.7270243084000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1933069339456551</v>
+        <v>0.1965356660833023</v>
       </c>
       <c r="T62">
-        <v>1.028483623377563</v>
+        <v>1.050995772732294</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.189483082854032</v>
+        <v>4.120803032315441</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1013295097724879</v>
+        <v>0.1010602459667138</v>
       </c>
       <c r="C63">
-        <v>3.871008784663135</v>
+        <v>3.792842511979725</v>
       </c>
       <c r="D63">
-        <v>5.329468784663136</v>
+        <v>5.338162511979725</v>
       </c>
       <c r="E63">
-        <v>5.27246</v>
+        <v>5.35932</v>
       </c>
       <c r="F63">
-        <v>5.29846</v>
+        <v>5.38532</v>
       </c>
       <c r="G63">
         <v>3.84</v>
@@ -6578,28 +6578,28 @@
         <v>1.262</v>
       </c>
       <c r="M63">
-        <v>0.306250988</v>
+        <v>0.311271496</v>
       </c>
       <c r="N63">
-        <v>0.9557490120000001</v>
+        <v>0.950728504</v>
       </c>
       <c r="O63">
-        <v>0.2867247036</v>
+        <v>0.2852185512</v>
       </c>
       <c r="P63">
-        <v>0.6690243084</v>
+        <v>0.6655099527999999</v>
       </c>
       <c r="Q63">
-        <v>0.7270243084000001</v>
+        <v>0.7235099528</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1965356660833023</v>
+        <v>0.199934331491352</v>
       </c>
       <c r="T63">
-        <v>1.050995772732294</v>
+        <v>1.074692772053064</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.120803032315441</v>
+        <v>4.054338467278096</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1010602459667138</v>
+        <v>0.1023344821609396</v>
       </c>
       <c r="C64">
-        <v>3.792842511979725</v>
+        <v>3.66508977872215</v>
       </c>
       <c r="D64">
-        <v>5.338162511979725</v>
+        <v>5.297269778722149</v>
       </c>
       <c r="E64">
-        <v>5.35932</v>
+        <v>5.44618</v>
       </c>
       <c r="F64">
-        <v>5.38532</v>
+        <v>5.47218</v>
       </c>
       <c r="G64">
         <v>3.84</v>
@@ -6660,45 +6660,45 @@
         <v>1.262</v>
       </c>
       <c r="M64">
-        <v>0.311271496</v>
+        <v>0.335444634</v>
       </c>
       <c r="N64">
-        <v>0.950728504</v>
+        <v>0.9265553660000001</v>
       </c>
       <c r="O64">
-        <v>0.2852185512</v>
+        <v>0.2779666098</v>
       </c>
       <c r="P64">
-        <v>0.6655099527999999</v>
+        <v>0.6485887562000001</v>
       </c>
       <c r="Q64">
-        <v>0.7235099528</v>
+        <v>0.7065887562000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.199934331491352</v>
+        <v>0.2035167085430801</v>
       </c>
       <c r="T64">
-        <v>1.074692772053064</v>
+        <v>1.099670690256037</v>
       </c>
       <c r="U64">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>4.054338467278096</v>
+        <v>3.762170778978686</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1023344821609396</v>
+        <v>0.1020897183551655</v>
       </c>
       <c r="C65">
-        <v>3.66508977872215</v>
+        <v>3.58603604250301</v>
       </c>
       <c r="D65">
-        <v>5.297269778722149</v>
+        <v>5.305076042503011</v>
       </c>
       <c r="E65">
-        <v>5.44618</v>
+        <v>5.533040000000001</v>
       </c>
       <c r="F65">
-        <v>5.47218</v>
+        <v>5.55904</v>
       </c>
       <c r="G65">
         <v>3.84</v>
@@ -6742,28 +6742,28 @@
         <v>1.262</v>
       </c>
       <c r="M65">
-        <v>0.335444634</v>
+        <v>0.340769152</v>
       </c>
       <c r="N65">
-        <v>0.9265553660000001</v>
+        <v>0.921230848</v>
       </c>
       <c r="O65">
-        <v>0.2779666098</v>
+        <v>0.2763692544</v>
       </c>
       <c r="P65">
-        <v>0.6485887562000001</v>
+        <v>0.6448615935999999</v>
       </c>
       <c r="Q65">
-        <v>0.7065887562000002</v>
+        <v>0.7028615936</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2035167085430801</v>
+        <v>0.2072981065421265</v>
       </c>
       <c r="T65">
-        <v>1.099670690256037</v>
+        <v>1.126036270581398</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.762170778978686</v>
+        <v>3.703386860557143</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1020897183551655</v>
+        <v>0.1018449545493914</v>
       </c>
       <c r="C66">
-        <v>3.58603604250301</v>
+        <v>3.507005347469067</v>
       </c>
       <c r="D66">
-        <v>5.305076042503011</v>
+        <v>5.312905347469068</v>
       </c>
       <c r="E66">
-        <v>5.533040000000001</v>
+        <v>5.6199</v>
       </c>
       <c r="F66">
-        <v>5.55904</v>
+        <v>5.6459</v>
       </c>
       <c r="G66">
         <v>3.84</v>
@@ -6824,28 +6824,28 @@
         <v>1.262</v>
       </c>
       <c r="M66">
-        <v>0.340769152</v>
+        <v>0.34609367</v>
       </c>
       <c r="N66">
-        <v>0.921230848</v>
+        <v>0.91590633</v>
       </c>
       <c r="O66">
-        <v>0.2763692544</v>
+        <v>0.274771899</v>
       </c>
       <c r="P66">
-        <v>0.6448615935999999</v>
+        <v>0.641134431</v>
       </c>
       <c r="Q66">
-        <v>0.7028615936</v>
+        <v>0.6991344310000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2072981065421265</v>
+        <v>0.2112955844268325</v>
       </c>
       <c r="T66">
-        <v>1.126036270581398</v>
+        <v>1.153908455496778</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.703386860557143</v>
+        <v>3.646411678087033</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1018449545493914</v>
+        <v>0.1016001907436173</v>
       </c>
       <c r="C67">
-        <v>3.507005347469067</v>
+        <v>3.427997795784598</v>
       </c>
       <c r="D67">
-        <v>5.312905347469068</v>
+        <v>5.320757795784599</v>
       </c>
       <c r="E67">
-        <v>5.6199</v>
+        <v>5.70676</v>
       </c>
       <c r="F67">
-        <v>5.6459</v>
+        <v>5.73276</v>
       </c>
       <c r="G67">
         <v>3.84</v>
@@ -6906,28 +6906,28 @@
         <v>1.262</v>
       </c>
       <c r="M67">
-        <v>0.34609367</v>
+        <v>0.351418188</v>
       </c>
       <c r="N67">
-        <v>0.91590633</v>
+        <v>0.910581812</v>
       </c>
       <c r="O67">
-        <v>0.274771899</v>
+        <v>0.2731745436</v>
       </c>
       <c r="P67">
-        <v>0.641134431</v>
+        <v>0.6374072684000001</v>
       </c>
       <c r="Q67">
-        <v>0.6991344310000001</v>
+        <v>0.6954072684000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2112955844268325</v>
+        <v>0.2155282080694625</v>
       </c>
       <c r="T67">
-        <v>1.153908455496778</v>
+        <v>1.1834201807013</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.646411678087033</v>
+        <v>3.591163016297836</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1016001907436173</v>
+        <v>0.1013554269378431</v>
       </c>
       <c r="C68">
-        <v>3.427997795784598</v>
+        <v>3.349013490218772</v>
       </c>
       <c r="D68">
-        <v>5.320757795784599</v>
+        <v>5.328633490218772</v>
       </c>
       <c r="E68">
-        <v>5.70676</v>
+        <v>5.793620000000001</v>
       </c>
       <c r="F68">
-        <v>5.73276</v>
+        <v>5.81962</v>
       </c>
       <c r="G68">
         <v>3.84</v>
@@ -6988,28 +6988,28 @@
         <v>1.262</v>
       </c>
       <c r="M68">
-        <v>0.351418188</v>
+        <v>0.356742706</v>
       </c>
       <c r="N68">
-        <v>0.910581812</v>
+        <v>0.905257294</v>
       </c>
       <c r="O68">
-        <v>0.2731745436</v>
+        <v>0.2715771882</v>
       </c>
       <c r="P68">
-        <v>0.6374072684000001</v>
+        <v>0.6336801058</v>
       </c>
       <c r="Q68">
-        <v>0.6954072684000001</v>
+        <v>0.6916801058000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2155282080694625</v>
+        <v>0.2200173543571004</v>
       </c>
       <c r="T68">
-        <v>1.1834201807013</v>
+        <v>1.214720495312156</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.591163016297836</v>
+        <v>3.537563568293391</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1013554269378431</v>
+        <v>0.102443463132069</v>
       </c>
       <c r="C69">
-        <v>3.349013490218772</v>
+        <v>3.227321430196275</v>
       </c>
       <c r="D69">
-        <v>5.328633490218772</v>
+        <v>5.293801430196276</v>
       </c>
       <c r="E69">
-        <v>5.793620000000001</v>
+        <v>5.88048</v>
       </c>
       <c r="F69">
-        <v>5.81962</v>
+        <v>5.90648</v>
       </c>
       <c r="G69">
         <v>3.84</v>
@@ -7070,45 +7070,45 @@
         <v>1.262</v>
       </c>
       <c r="M69">
-        <v>0.356742706</v>
+        <v>0.3786053680000001</v>
       </c>
       <c r="N69">
-        <v>0.905257294</v>
+        <v>0.8833946319999999</v>
       </c>
       <c r="O69">
-        <v>0.2715771882</v>
+        <v>0.2650183896</v>
       </c>
       <c r="P69">
-        <v>0.6336801058</v>
+        <v>0.6183762423999999</v>
       </c>
       <c r="Q69">
-        <v>0.6916801058000001</v>
+        <v>0.6763762423999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2200173543571004</v>
+        <v>0.2247870722877156</v>
       </c>
       <c r="T69">
-        <v>1.214720495312156</v>
+        <v>1.24797707958619</v>
       </c>
       <c r="U69">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V69">
         <v>0.3</v>
       </c>
       <c r="W69">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.537563568293391</v>
+        <v>3.333286072161554</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.102443463132069</v>
+        <v>0.1022182993262949</v>
       </c>
       <c r="C70">
-        <v>3.227321430196275</v>
+        <v>3.14763233712621</v>
       </c>
       <c r="D70">
-        <v>5.293801430196276</v>
+        <v>5.300972337126212</v>
       </c>
       <c r="E70">
-        <v>5.88048</v>
+        <v>5.967340000000001</v>
       </c>
       <c r="F70">
-        <v>5.90648</v>
+        <v>5.993340000000001</v>
       </c>
       <c r="G70">
         <v>3.84</v>
@@ -7152,28 +7152,28 @@
         <v>1.262</v>
       </c>
       <c r="M70">
-        <v>0.3786053680000001</v>
+        <v>0.384173094</v>
       </c>
       <c r="N70">
-        <v>0.8833946319999999</v>
+        <v>0.8778269059999999</v>
       </c>
       <c r="O70">
-        <v>0.2650183896</v>
+        <v>0.2633480718</v>
       </c>
       <c r="P70">
-        <v>0.6183762423999999</v>
+        <v>0.6144788341999999</v>
       </c>
       <c r="Q70">
-        <v>0.6763762423999999</v>
+        <v>0.6724788342</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2247870722877156</v>
+        <v>0.2298645139557899</v>
       </c>
       <c r="T70">
-        <v>1.24797707958619</v>
+        <v>1.28337924994242</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.333286072161554</v>
+        <v>3.284977578362112</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1022182993262949</v>
+        <v>0.1019931355205207</v>
       </c>
       <c r="C71">
-        <v>3.14763233712621</v>
+        <v>3.067962697621504</v>
       </c>
       <c r="D71">
-        <v>5.300972337126212</v>
+        <v>5.308162697621505</v>
       </c>
       <c r="E71">
-        <v>5.967340000000001</v>
+        <v>6.054200000000001</v>
       </c>
       <c r="F71">
-        <v>5.993340000000001</v>
+        <v>6.0802</v>
       </c>
       <c r="G71">
         <v>3.84</v>
@@ -7234,28 +7234,28 @@
         <v>1.262</v>
       </c>
       <c r="M71">
-        <v>0.384173094</v>
+        <v>0.38974082</v>
       </c>
       <c r="N71">
-        <v>0.8778269059999999</v>
+        <v>0.8722591799999999</v>
       </c>
       <c r="O71">
-        <v>0.2633480718</v>
+        <v>0.261677754</v>
       </c>
       <c r="P71">
-        <v>0.6144788341999999</v>
+        <v>0.610581426</v>
       </c>
       <c r="Q71">
-        <v>0.6724788342</v>
+        <v>0.668581426</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2298645139557899</v>
+        <v>0.2352804517350692</v>
       </c>
       <c r="T71">
-        <v>1.28337924994242</v>
+        <v>1.321141564989066</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.284977578362112</v>
+        <v>3.238049327242653</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1019931355205207</v>
+        <v>0.1017679717147466</v>
       </c>
       <c r="C72">
-        <v>3.067962697621504</v>
+        <v>2.988312590951462</v>
       </c>
       <c r="D72">
-        <v>5.308162697621505</v>
+        <v>5.315372590951462</v>
       </c>
       <c r="E72">
-        <v>6.054200000000001</v>
+        <v>6.14106</v>
       </c>
       <c r="F72">
-        <v>6.0802</v>
+        <v>6.16706</v>
       </c>
       <c r="G72">
         <v>3.84</v>
@@ -7316,28 +7316,28 @@
         <v>1.262</v>
       </c>
       <c r="M72">
-        <v>0.38974082</v>
+        <v>0.395308546</v>
       </c>
       <c r="N72">
-        <v>0.8722591799999999</v>
+        <v>0.8666914539999999</v>
       </c>
       <c r="O72">
-        <v>0.261677754</v>
+        <v>0.2600074361999999</v>
       </c>
       <c r="P72">
-        <v>0.610581426</v>
+        <v>0.6066840177999999</v>
       </c>
       <c r="Q72">
-        <v>0.668581426</v>
+        <v>0.6646840178</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2352804517350692</v>
+        <v>0.2410699024646435</v>
       </c>
       <c r="T72">
-        <v>1.321141564989066</v>
+        <v>1.361508177625135</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.238049327242653</v>
+        <v>3.192442998689939</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1017679717147466</v>
+        <v>0.1015428079089725</v>
       </c>
       <c r="C73">
-        <v>2.988312590951463</v>
+        <v>2.908682096816656</v>
       </c>
       <c r="D73">
-        <v>5.315372590951462</v>
+        <v>5.322602096816656</v>
       </c>
       <c r="E73">
-        <v>6.14106</v>
+        <v>6.22792</v>
       </c>
       <c r="F73">
-        <v>6.167059999999999</v>
+        <v>6.25392</v>
       </c>
       <c r="G73">
         <v>3.84</v>
@@ -7398,28 +7398,28 @@
         <v>1.262</v>
       </c>
       <c r="M73">
-        <v>0.395308546</v>
+        <v>0.400876272</v>
       </c>
       <c r="N73">
-        <v>0.866691454</v>
+        <v>0.8611237279999999</v>
       </c>
       <c r="O73">
-        <v>0.2600074362</v>
+        <v>0.2583371184</v>
       </c>
       <c r="P73">
-        <v>0.6066840178</v>
+        <v>0.6027866096</v>
       </c>
       <c r="Q73">
-        <v>0.6646840178000001</v>
+        <v>0.6607866096</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2410699024646435</v>
+        <v>0.2472728853891874</v>
       </c>
       <c r="T73">
-        <v>1.361508177625135</v>
+        <v>1.404758119735209</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.19244299868994</v>
+        <v>3.148103512597023</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1015428079089725</v>
+        <v>0.1013176441031984</v>
       </c>
       <c r="C74">
-        <v>2.908682096816656</v>
+        <v>2.829071295351855</v>
       </c>
       <c r="D74">
-        <v>5.322602096816656</v>
+        <v>5.329851295351854</v>
       </c>
       <c r="E74">
-        <v>6.22792</v>
+        <v>6.31478</v>
       </c>
       <c r="F74">
-        <v>6.25392</v>
+        <v>6.34078</v>
       </c>
       <c r="G74">
         <v>3.84</v>
@@ -7480,28 +7480,28 @@
         <v>1.262</v>
       </c>
       <c r="M74">
-        <v>0.400876272</v>
+        <v>0.406443998</v>
       </c>
       <c r="N74">
-        <v>0.8611237279999999</v>
+        <v>0.8555560019999999</v>
       </c>
       <c r="O74">
-        <v>0.2583371184</v>
+        <v>0.2566668006</v>
       </c>
       <c r="P74">
-        <v>0.6027866096</v>
+        <v>0.5988892014</v>
       </c>
       <c r="Q74">
-        <v>0.6607866096</v>
+        <v>0.6568892014000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2472728853891874</v>
+        <v>0.2539353485303643</v>
       </c>
       <c r="T74">
-        <v>1.404758119735209</v>
+        <v>1.451211761260844</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.148103512597023</v>
+        <v>3.104978806945009</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1013176441031984</v>
+        <v>0.1010924802974242</v>
       </c>
       <c r="C75">
-        <v>2.829071295351855</v>
+        <v>2.749480267128982</v>
       </c>
       <c r="D75">
-        <v>5.329851295351854</v>
+        <v>5.337120267128983</v>
       </c>
       <c r="E75">
-        <v>6.31478</v>
+        <v>6.40164</v>
       </c>
       <c r="F75">
-        <v>6.34078</v>
+        <v>6.42764</v>
       </c>
       <c r="G75">
         <v>3.84</v>
@@ -7562,28 +7562,28 @@
         <v>1.262</v>
       </c>
       <c r="M75">
-        <v>0.406443998</v>
+        <v>0.412011724</v>
       </c>
       <c r="N75">
-        <v>0.8555560019999999</v>
+        <v>0.8499882759999999</v>
       </c>
       <c r="O75">
-        <v>0.2566668006</v>
+        <v>0.2549964828</v>
       </c>
       <c r="P75">
-        <v>0.5988892014</v>
+        <v>0.5949917932</v>
       </c>
       <c r="Q75">
-        <v>0.6568892014000001</v>
+        <v>0.6529917932</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2539353485303643</v>
+        <v>0.261110308836247</v>
       </c>
       <c r="T75">
-        <v>1.451211761260844</v>
+        <v>1.501238759826912</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.104978806945009</v>
+        <v>3.063019633878185</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1010924802974242</v>
+        <v>0.1008673164916501</v>
       </c>
       <c r="C76">
-        <v>2.749480267128982</v>
+        <v>2.669909093160111</v>
       </c>
       <c r="D76">
-        <v>5.337120267128983</v>
+        <v>5.344409093160111</v>
       </c>
       <c r="E76">
-        <v>6.40164</v>
+        <v>6.4885</v>
       </c>
       <c r="F76">
-        <v>6.42764</v>
+        <v>6.5145</v>
       </c>
       <c r="G76">
         <v>3.84</v>
@@ -7644,28 +7644,28 @@
         <v>1.262</v>
       </c>
       <c r="M76">
-        <v>0.412011724</v>
+        <v>0.41757945</v>
       </c>
       <c r="N76">
-        <v>0.8499882759999999</v>
+        <v>0.8444205499999999</v>
       </c>
       <c r="O76">
-        <v>0.2549964828</v>
+        <v>0.253326165</v>
       </c>
       <c r="P76">
-        <v>0.5949917932</v>
+        <v>0.5910943849999999</v>
       </c>
       <c r="Q76">
-        <v>0.6529917932</v>
+        <v>0.6490943849999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.261110308836247</v>
+        <v>0.2688592659666004</v>
       </c>
       <c r="T76">
-        <v>1.501238759826912</v>
+        <v>1.555267918278267</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.063019633878185</v>
+        <v>3.022179372093143</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1008673164916501</v>
+        <v>0.104791752685876</v>
       </c>
       <c r="C77">
-        <v>2.669909093160111</v>
+        <v>2.458794446232812</v>
       </c>
       <c r="D77">
-        <v>5.344409093160111</v>
+        <v>5.220154446232811</v>
       </c>
       <c r="E77">
-        <v>6.4885</v>
+        <v>6.57536</v>
       </c>
       <c r="F77">
-        <v>6.5145</v>
+        <v>6.60136</v>
       </c>
       <c r="G77">
         <v>3.84</v>
@@ -7726,45 +7726,45 @@
         <v>1.262</v>
       </c>
       <c r="M77">
-        <v>0.41757945</v>
+        <v>0.474637784</v>
       </c>
       <c r="N77">
-        <v>0.8444205499999999</v>
+        <v>0.787362216</v>
       </c>
       <c r="O77">
-        <v>0.253326165</v>
+        <v>0.2362086648</v>
       </c>
       <c r="P77">
-        <v>0.5910943849999999</v>
+        <v>0.5511535512</v>
       </c>
       <c r="Q77">
-        <v>0.6490943849999999</v>
+        <v>0.6091535512</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2688592659666004</v>
+        <v>0.2772539695244832</v>
       </c>
       <c r="T77">
-        <v>1.555267918278267</v>
+        <v>1.613799506600567</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.3</v>
       </c>
       <c r="W77">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.022179372093143</v>
+        <v>2.658869652905678</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.104791752685876</v>
+        <v>0.1046211888801018</v>
       </c>
       <c r="C78">
-        <v>2.458794446232812</v>
+        <v>2.377214580493923</v>
       </c>
       <c r="D78">
-        <v>5.220154446232811</v>
+        <v>5.225434580493923</v>
       </c>
       <c r="E78">
-        <v>6.57536</v>
+        <v>6.66222</v>
       </c>
       <c r="F78">
-        <v>6.60136</v>
+        <v>6.68822</v>
       </c>
       <c r="G78">
         <v>3.84</v>
@@ -7808,28 +7808,28 @@
         <v>1.262</v>
       </c>
       <c r="M78">
-        <v>0.474637784</v>
+        <v>0.4808830180000001</v>
       </c>
       <c r="N78">
-        <v>0.787362216</v>
+        <v>0.7811169819999999</v>
       </c>
       <c r="O78">
-        <v>0.2362086648</v>
+        <v>0.2343350946</v>
       </c>
       <c r="P78">
-        <v>0.5511535512</v>
+        <v>0.5467818873999999</v>
       </c>
       <c r="Q78">
-        <v>0.6091535512</v>
+        <v>0.6047818873999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2772539695244832</v>
+        <v>0.2863786473047906</v>
       </c>
       <c r="T78">
-        <v>1.613799506600567</v>
+        <v>1.677420798255242</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.658869652905678</v>
+        <v>2.624338878192616</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1046211888801018</v>
+        <v>0.1044506250743277</v>
       </c>
       <c r="C79">
-        <v>2.377214580493923</v>
+        <v>2.295645407176806</v>
       </c>
       <c r="D79">
-        <v>5.225434580493923</v>
+        <v>5.230725407176807</v>
       </c>
       <c r="E79">
-        <v>6.66222</v>
+        <v>6.74908</v>
       </c>
       <c r="F79">
-        <v>6.68822</v>
+        <v>6.77508</v>
       </c>
       <c r="G79">
         <v>3.84</v>
@@ -7890,28 +7890,28 @@
         <v>1.262</v>
       </c>
       <c r="M79">
-        <v>0.4808830180000001</v>
+        <v>0.487128252</v>
       </c>
       <c r="N79">
-        <v>0.7811169819999999</v>
+        <v>0.774871748</v>
       </c>
       <c r="O79">
-        <v>0.2343350946</v>
+        <v>0.2324615244</v>
       </c>
       <c r="P79">
-        <v>0.5467818873999999</v>
+        <v>0.5424102236</v>
       </c>
       <c r="Q79">
-        <v>0.6047818873999999</v>
+        <v>0.6004102236000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2863786473047906</v>
+        <v>0.2963328412469441</v>
       </c>
       <c r="T79">
-        <v>1.677420798255242</v>
+        <v>1.746825843696704</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.624338878192616</v>
+        <v>2.590693507959378</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1044506250743277</v>
+        <v>0.1042800612685536</v>
       </c>
       <c r="C80">
-        <v>2.295645407176806</v>
+        <v>2.214086958793066</v>
       </c>
       <c r="D80">
-        <v>5.230725407176807</v>
+        <v>5.236026958793067</v>
       </c>
       <c r="E80">
-        <v>6.74908</v>
+        <v>6.835940000000001</v>
       </c>
       <c r="F80">
-        <v>6.77508</v>
+        <v>6.861940000000001</v>
       </c>
       <c r="G80">
         <v>3.84</v>
@@ -7972,28 +7972,28 @@
         <v>1.262</v>
       </c>
       <c r="M80">
-        <v>0.487128252</v>
+        <v>0.4933734860000001</v>
       </c>
       <c r="N80">
-        <v>0.774871748</v>
+        <v>0.7686265139999999</v>
       </c>
       <c r="O80">
-        <v>0.2324615244</v>
+        <v>0.2305879542</v>
       </c>
       <c r="P80">
-        <v>0.5424102236</v>
+        <v>0.5380385597999999</v>
       </c>
       <c r="Q80">
-        <v>0.6004102236000001</v>
+        <v>0.5960385598</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2963328412469441</v>
+        <v>0.307235053659779</v>
       </c>
       <c r="T80">
-        <v>1.746825843696704</v>
+        <v>1.822840893465926</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.590693507959378</v>
+        <v>2.557899919251031</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1042800612685536</v>
+        <v>0.1041094974627794</v>
       </c>
       <c r="C81">
-        <v>2.214086958793066</v>
+        <v>2.13253926798625</v>
       </c>
       <c r="D81">
-        <v>5.236026958793067</v>
+        <v>5.24133926798625</v>
       </c>
       <c r="E81">
-        <v>6.835940000000001</v>
+        <v>6.922800000000001</v>
       </c>
       <c r="F81">
-        <v>6.861940000000001</v>
+        <v>6.9488</v>
       </c>
       <c r="G81">
         <v>3.84</v>
@@ -8054,28 +8054,28 @@
         <v>1.262</v>
       </c>
       <c r="M81">
-        <v>0.4933734860000001</v>
+        <v>0.4996187200000001</v>
       </c>
       <c r="N81">
-        <v>0.7686265139999999</v>
+        <v>0.7623812799999999</v>
       </c>
       <c r="O81">
-        <v>0.2305879542</v>
+        <v>0.228714384</v>
       </c>
       <c r="P81">
-        <v>0.5380385597999999</v>
+        <v>0.5336668959999999</v>
       </c>
       <c r="Q81">
-        <v>0.5960385598</v>
+        <v>0.591666896</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.307235053659779</v>
+        <v>0.3192274873138973</v>
       </c>
       <c r="T81">
-        <v>1.822840893465926</v>
+        <v>1.906457448212069</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.557899919251031</v>
+        <v>2.525926170260393</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1041094974627794</v>
+        <v>0.1061502336570053</v>
       </c>
       <c r="C82">
-        <v>2.13253926798625</v>
+        <v>1.982817934456307</v>
       </c>
       <c r="D82">
-        <v>5.24133926798625</v>
+        <v>5.178477934456308</v>
       </c>
       <c r="E82">
-        <v>6.922800000000001</v>
+        <v>7.00966</v>
       </c>
       <c r="F82">
-        <v>6.9488</v>
+        <v>7.03566</v>
       </c>
       <c r="G82">
         <v>3.84</v>
@@ -8136,45 +8136,45 @@
         <v>1.262</v>
       </c>
       <c r="M82">
-        <v>0.4996187200000001</v>
+        <v>0.5333030280000001</v>
       </c>
       <c r="N82">
-        <v>0.7623812799999999</v>
+        <v>0.7286969719999999</v>
       </c>
       <c r="O82">
-        <v>0.228714384</v>
+        <v>0.2186090916</v>
       </c>
       <c r="P82">
-        <v>0.5336668959999999</v>
+        <v>0.5100878804</v>
       </c>
       <c r="Q82">
-        <v>0.591666896</v>
+        <v>0.5680878804</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3192274873138973</v>
+        <v>0.3324822824052912</v>
       </c>
       <c r="T82">
-        <v>1.906457448212069</v>
+        <v>1.99887574556307</v>
       </c>
       <c r="U82">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V82">
         <v>0.3</v>
       </c>
       <c r="W82">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y82">
-        <v>2.525926170260393</v>
+        <v>2.366384463881198</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1061502336570053</v>
+        <v>0.1060069698512312</v>
       </c>
       <c r="C83">
-        <v>1.982817934456307</v>
+        <v>1.900321674557479</v>
       </c>
       <c r="D83">
-        <v>5.178477934456308</v>
+        <v>5.18284167455748</v>
       </c>
       <c r="E83">
-        <v>7.00966</v>
+        <v>7.096520000000001</v>
       </c>
       <c r="F83">
-        <v>7.03566</v>
+        <v>7.122520000000001</v>
       </c>
       <c r="G83">
         <v>3.84</v>
@@ -8218,28 +8218,28 @@
         <v>1.262</v>
       </c>
       <c r="M83">
-        <v>0.5333030280000001</v>
+        <v>0.5398870160000001</v>
       </c>
       <c r="N83">
-        <v>0.7286969719999999</v>
+        <v>0.7221129839999999</v>
       </c>
       <c r="O83">
-        <v>0.2186090916</v>
+        <v>0.2166338952</v>
       </c>
       <c r="P83">
-        <v>0.5100878804</v>
+        <v>0.5054790887999999</v>
       </c>
       <c r="Q83">
-        <v>0.5680878804</v>
+        <v>0.5634790888</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3324822824052912</v>
+        <v>0.3472098325068401</v>
       </c>
       <c r="T83">
-        <v>1.99887574556307</v>
+        <v>2.101562742619738</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.366384463881198</v>
+        <v>2.337526116760696</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1060069698512312</v>
+        <v>0.1058637060454571</v>
       </c>
       <c r="C84">
-        <v>1.900321674557479</v>
+        <v>1.817832775233607</v>
       </c>
       <c r="D84">
-        <v>5.18284167455748</v>
+        <v>5.187212775233607</v>
       </c>
       <c r="E84">
-        <v>7.096520000000001</v>
+        <v>7.183380000000001</v>
       </c>
       <c r="F84">
-        <v>7.122520000000001</v>
+        <v>7.20938</v>
       </c>
       <c r="G84">
         <v>3.84</v>
@@ -8300,28 +8300,28 @@
         <v>1.262</v>
       </c>
       <c r="M84">
-        <v>0.5398870160000001</v>
+        <v>0.546471004</v>
       </c>
       <c r="N84">
-        <v>0.7221129839999999</v>
+        <v>0.715528996</v>
       </c>
       <c r="O84">
-        <v>0.2166338952</v>
+        <v>0.2146586988</v>
       </c>
       <c r="P84">
-        <v>0.5054790887999999</v>
+        <v>0.5008702972</v>
       </c>
       <c r="Q84">
-        <v>0.5634790888</v>
+        <v>0.5588702972</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3472098325068401</v>
+        <v>0.3636700355615122</v>
       </c>
       <c r="T84">
-        <v>2.101562742619738</v>
+        <v>2.216330562859542</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.337526116760696</v>
+        <v>2.309363151498519</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1058637060454571</v>
+        <v>0.1057204422396829</v>
       </c>
       <c r="C85">
-        <v>1.817832775233607</v>
+        <v>1.735351255123671</v>
       </c>
       <c r="D85">
-        <v>5.187212775233607</v>
+        <v>5.191591255123671</v>
       </c>
       <c r="E85">
-        <v>7.183380000000001</v>
+        <v>7.270240000000001</v>
       </c>
       <c r="F85">
-        <v>7.20938</v>
+        <v>7.296240000000001</v>
       </c>
       <c r="G85">
         <v>3.84</v>
@@ -8382,28 +8382,28 @@
         <v>1.262</v>
       </c>
       <c r="M85">
-        <v>0.546471004</v>
+        <v>0.5530549920000001</v>
       </c>
       <c r="N85">
-        <v>0.715528996</v>
+        <v>0.7089450079999999</v>
       </c>
       <c r="O85">
-        <v>0.2146586988</v>
+        <v>0.2126835024</v>
       </c>
       <c r="P85">
-        <v>0.5008702972</v>
+        <v>0.4962615055999999</v>
       </c>
       <c r="Q85">
-        <v>0.5588702972</v>
+        <v>0.5542615056</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3636700355615122</v>
+        <v>0.3821877639980185</v>
       </c>
       <c r="T85">
-        <v>2.216330562859542</v>
+        <v>2.345444360629323</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.309363151498519</v>
+        <v>2.281870733028299</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1057204422396829</v>
+        <v>0.1055771784339088</v>
       </c>
       <c r="C86">
-        <v>1.735351255123672</v>
+        <v>1.652877132929647</v>
       </c>
       <c r="D86">
-        <v>5.191591255123671</v>
+        <v>5.195977132929647</v>
       </c>
       <c r="E86">
-        <v>7.27024</v>
+        <v>7.3571</v>
       </c>
       <c r="F86">
-        <v>7.29624</v>
+        <v>7.3831</v>
       </c>
       <c r="G86">
         <v>3.84</v>
@@ -8464,28 +8464,28 @@
         <v>1.262</v>
       </c>
       <c r="M86">
-        <v>0.5530549920000001</v>
+        <v>0.55963898</v>
       </c>
       <c r="N86">
-        <v>0.7089450079999999</v>
+        <v>0.70236102</v>
       </c>
       <c r="O86">
-        <v>0.2126835024</v>
+        <v>0.210708306</v>
       </c>
       <c r="P86">
-        <v>0.4962615055999999</v>
+        <v>0.491652714</v>
       </c>
       <c r="Q86">
-        <v>0.5542615056</v>
+        <v>0.549652714</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3821877639980182</v>
+        <v>0.4031745228927253</v>
       </c>
       <c r="T86">
-        <v>2.345444360629321</v>
+        <v>2.491773331435073</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.281870733028299</v>
+        <v>2.255025194992672</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1055771784339088</v>
+        <v>0.1054339146281347</v>
       </c>
       <c r="C87">
-        <v>1.652877132929647</v>
+        <v>1.570410427416756</v>
       </c>
       <c r="D87">
-        <v>5.195977132929647</v>
+        <v>5.200370427416756</v>
       </c>
       <c r="E87">
-        <v>7.3571</v>
+        <v>7.44396</v>
       </c>
       <c r="F87">
-        <v>7.3831</v>
+        <v>7.469959999999999</v>
       </c>
       <c r="G87">
         <v>3.84</v>
@@ -8546,28 +8546,28 @@
         <v>1.262</v>
       </c>
       <c r="M87">
-        <v>0.55963898</v>
+        <v>0.566222968</v>
       </c>
       <c r="N87">
-        <v>0.70236102</v>
+        <v>0.695777032</v>
       </c>
       <c r="O87">
-        <v>0.210708306</v>
+        <v>0.2087331096</v>
       </c>
       <c r="P87">
-        <v>0.491652714</v>
+        <v>0.4870439223999999</v>
       </c>
       <c r="Q87">
-        <v>0.549652714</v>
+        <v>0.5450439224</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4031745228927253</v>
+        <v>0.4271593902009619</v>
       </c>
       <c r="T87">
-        <v>2.491773331435073</v>
+        <v>2.659006440927359</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.255025194992672</v>
+        <v>2.228803971795083</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1054339146281347</v>
+        <v>0.1052906508223605</v>
       </c>
       <c r="C88">
-        <v>1.570410427416756</v>
+        <v>1.487951157413741</v>
       </c>
       <c r="D88">
-        <v>5.200370427416756</v>
+        <v>5.204771157413741</v>
       </c>
       <c r="E88">
-        <v>7.44396</v>
+        <v>7.53082</v>
       </c>
       <c r="F88">
-        <v>7.469959999999999</v>
+        <v>7.55682</v>
       </c>
       <c r="G88">
         <v>3.84</v>
@@ -8628,28 +8628,28 @@
         <v>1.262</v>
       </c>
       <c r="M88">
-        <v>0.566222968</v>
+        <v>0.5728069560000001</v>
       </c>
       <c r="N88">
-        <v>0.695777032</v>
+        <v>0.6891930439999999</v>
       </c>
       <c r="O88">
-        <v>0.2087331096</v>
+        <v>0.2067579132</v>
       </c>
       <c r="P88">
-        <v>0.4870439223999999</v>
+        <v>0.4824351307999999</v>
       </c>
       <c r="Q88">
-        <v>0.5450439224</v>
+        <v>0.5404351307999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4271593902009619</v>
+        <v>0.454834237095081</v>
       </c>
       <c r="T88">
-        <v>2.659006440927359</v>
+        <v>2.851967721110767</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.228803971795083</v>
+        <v>2.203185535337668</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1052906508223605</v>
+        <v>0.1051473870165864</v>
       </c>
       <c r="C89">
-        <v>1.487951157413741</v>
+        <v>1.405499341813131</v>
       </c>
       <c r="D89">
-        <v>5.204771157413741</v>
+        <v>5.209179341813131</v>
       </c>
       <c r="E89">
-        <v>7.53082</v>
+        <v>7.61768</v>
       </c>
       <c r="F89">
-        <v>7.55682</v>
+        <v>7.64368</v>
       </c>
       <c r="G89">
         <v>3.84</v>
@@ -8710,28 +8710,28 @@
         <v>1.262</v>
       </c>
       <c r="M89">
-        <v>0.5728069560000001</v>
+        <v>0.579390944</v>
       </c>
       <c r="N89">
-        <v>0.6891930439999999</v>
+        <v>0.682609056</v>
       </c>
       <c r="O89">
-        <v>0.2067579132</v>
+        <v>0.2047827168</v>
       </c>
       <c r="P89">
-        <v>0.4824351307999999</v>
+        <v>0.4778263392</v>
       </c>
       <c r="Q89">
-        <v>0.5404351307999999</v>
+        <v>0.5358263392</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.454834237095081</v>
+        <v>0.4871215584715535</v>
       </c>
       <c r="T89">
-        <v>2.851967721110767</v>
+        <v>3.077089214658077</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.203185535337668</v>
+        <v>2.178149336072467</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1051473870165864</v>
+        <v>0.1050041232108123</v>
       </c>
       <c r="C90">
-        <v>1.405499341813131</v>
+        <v>1.323054999571515</v>
       </c>
       <c r="D90">
-        <v>5.209179341813131</v>
+        <v>5.213594999571515</v>
       </c>
       <c r="E90">
-        <v>7.61768</v>
+        <v>7.704540000000001</v>
       </c>
       <c r="F90">
-        <v>7.64368</v>
+        <v>7.73054</v>
       </c>
       <c r="G90">
         <v>3.84</v>
@@ -8792,28 +8792,28 @@
         <v>1.262</v>
       </c>
       <c r="M90">
-        <v>0.579390944</v>
+        <v>0.5859749320000001</v>
       </c>
       <c r="N90">
-        <v>0.682609056</v>
+        <v>0.676025068</v>
       </c>
       <c r="O90">
-        <v>0.2047827168</v>
+        <v>0.2028075204</v>
       </c>
       <c r="P90">
-        <v>0.4778263392</v>
+        <v>0.4732175476</v>
       </c>
       <c r="Q90">
-        <v>0.5358263392</v>
+        <v>0.5312175476000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4871215584715535</v>
+        <v>0.5252793019164753</v>
       </c>
       <c r="T90">
-        <v>3.077089214658077</v>
+        <v>3.343141888850351</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.178149336072467</v>
+        <v>2.153675748026709</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1050041232108123</v>
+        <v>0.1048608594050381</v>
       </c>
       <c r="C91">
-        <v>1.323054999571515</v>
+        <v>1.240618149709813</v>
       </c>
       <c r="D91">
-        <v>5.213594999571515</v>
+        <v>5.218018149709813</v>
       </c>
       <c r="E91">
-        <v>7.704540000000001</v>
+        <v>7.7914</v>
       </c>
       <c r="F91">
-        <v>7.73054</v>
+        <v>7.8174</v>
       </c>
       <c r="G91">
         <v>3.84</v>
@@ -8874,28 +8874,28 @@
         <v>1.262</v>
       </c>
       <c r="M91">
-        <v>0.5859749320000001</v>
+        <v>0.5925589200000001</v>
       </c>
       <c r="N91">
-        <v>0.676025068</v>
+        <v>0.6694410799999999</v>
       </c>
       <c r="O91">
-        <v>0.2028075204</v>
+        <v>0.200832324</v>
       </c>
       <c r="P91">
-        <v>0.4732175476</v>
+        <v>0.468608756</v>
       </c>
       <c r="Q91">
-        <v>0.5312175476000001</v>
+        <v>0.526608756</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5252793019164753</v>
+        <v>0.5710685940503816</v>
       </c>
       <c r="T91">
-        <v>3.343141888850351</v>
+        <v>3.66240509788108</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.153675748026709</v>
+        <v>2.129746017493079</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1048608594050381</v>
+        <v>0.104717595599264</v>
       </c>
       <c r="C92">
-        <v>1.240618149709813</v>
+        <v>1.158188811313544</v>
       </c>
       <c r="D92">
-        <v>5.218018149709813</v>
+        <v>5.222448811313545</v>
       </c>
       <c r="E92">
-        <v>7.7914</v>
+        <v>7.87826</v>
       </c>
       <c r="F92">
-        <v>7.8174</v>
+        <v>7.90426</v>
       </c>
       <c r="G92">
         <v>3.84</v>
@@ -8956,28 +8956,28 @@
         <v>1.262</v>
       </c>
       <c r="M92">
-        <v>0.5925589200000001</v>
+        <v>0.599142908</v>
       </c>
       <c r="N92">
-        <v>0.6694410799999999</v>
+        <v>0.662857092</v>
       </c>
       <c r="O92">
-        <v>0.200832324</v>
+        <v>0.1988571276</v>
       </c>
       <c r="P92">
-        <v>0.468608756</v>
+        <v>0.4639999644</v>
       </c>
       <c r="Q92">
-        <v>0.526608756</v>
+        <v>0.5219999644000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5710685940503816</v>
+        <v>0.627033284436267</v>
       </c>
       <c r="T92">
-        <v>3.66240509788108</v>
+        <v>4.052615686696416</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.129746017493079</v>
+        <v>2.106342215103045</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.104717595599264</v>
+        <v>0.1045743317934899</v>
       </c>
       <c r="C93">
-        <v>1.158188811313544</v>
+        <v>1.075767003533111</v>
       </c>
       <c r="D93">
-        <v>5.222448811313545</v>
+        <v>5.226887003533112</v>
       </c>
       <c r="E93">
-        <v>7.87826</v>
+        <v>7.965120000000001</v>
       </c>
       <c r="F93">
-        <v>7.90426</v>
+        <v>7.99112</v>
       </c>
       <c r="G93">
         <v>3.84</v>
@@ -9038,28 +9038,28 @@
         <v>1.262</v>
       </c>
       <c r="M93">
-        <v>0.599142908</v>
+        <v>0.6057268960000001</v>
       </c>
       <c r="N93">
-        <v>0.662857092</v>
+        <v>0.6562731039999999</v>
       </c>
       <c r="O93">
-        <v>0.1988571276</v>
+        <v>0.1968819312</v>
       </c>
       <c r="P93">
-        <v>0.4639999644</v>
+        <v>0.4593911728</v>
       </c>
       <c r="Q93">
-        <v>0.5219999644000001</v>
+        <v>0.5173911728</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.627033284436267</v>
+        <v>0.6969891474186241</v>
       </c>
       <c r="T93">
-        <v>4.052615686696416</v>
+        <v>4.540378922715588</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.106342215103045</v>
+        <v>2.083447191025838</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1045743317934899</v>
+        <v>0.1044310679877158</v>
       </c>
       <c r="C94">
-        <v>1.075767003533111</v>
+        <v>0.9933527455840689</v>
       </c>
       <c r="D94">
-        <v>5.226887003533112</v>
+        <v>5.231332745584068</v>
       </c>
       <c r="E94">
-        <v>7.965120000000001</v>
+        <v>8.05198</v>
       </c>
       <c r="F94">
-        <v>7.99112</v>
+        <v>8.07798</v>
       </c>
       <c r="G94">
         <v>3.84</v>
@@ -9120,28 +9120,28 @@
         <v>1.262</v>
       </c>
       <c r="M94">
-        <v>0.6057268960000001</v>
+        <v>0.6123108840000001</v>
       </c>
       <c r="N94">
-        <v>0.6562731039999999</v>
+        <v>0.6496891159999999</v>
       </c>
       <c r="O94">
-        <v>0.1968819312</v>
+        <v>0.1949067348</v>
       </c>
       <c r="P94">
-        <v>0.4593911728</v>
+        <v>0.4547823811999999</v>
       </c>
       <c r="Q94">
-        <v>0.5173911728</v>
+        <v>0.5127823812</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6969891474186241</v>
+        <v>0.7869323998245114</v>
       </c>
       <c r="T94">
-        <v>4.540378922715588</v>
+        <v>5.167503083311664</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.083447191025838</v>
+        <v>2.061044533057818</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1044310679877158</v>
+        <v>0.1042878041819416</v>
       </c>
       <c r="C95">
-        <v>0.9933527455840689</v>
+        <v>0.910946056747397</v>
       </c>
       <c r="D95">
-        <v>5.231332745584068</v>
+        <v>5.235786056747396</v>
       </c>
       <c r="E95">
-        <v>8.05198</v>
+        <v>8.13884</v>
       </c>
       <c r="F95">
-        <v>8.07798</v>
+        <v>8.16484</v>
       </c>
       <c r="G95">
         <v>3.84</v>
@@ -9202,28 +9202,28 @@
         <v>1.262</v>
       </c>
       <c r="M95">
-        <v>0.6123108840000001</v>
+        <v>0.618894872</v>
       </c>
       <c r="N95">
-        <v>0.6496891159999999</v>
+        <v>0.643105128</v>
       </c>
       <c r="O95">
-        <v>0.1949067348</v>
+        <v>0.1929315384</v>
       </c>
       <c r="P95">
-        <v>0.4547823811999999</v>
+        <v>0.4501735896</v>
       </c>
       <c r="Q95">
-        <v>0.5127823812</v>
+        <v>0.5081735896</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7869323998245114</v>
+        <v>0.9068567363656946</v>
       </c>
       <c r="T95">
-        <v>5.167503083311664</v>
+        <v>6.0036686307731</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.061044533057818</v>
+        <v>2.03911852738699</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1042878041819416</v>
+        <v>0.1041445403761675</v>
       </c>
       <c r="C96">
-        <v>0.910946056747397</v>
+        <v>0.8285469563697898</v>
       </c>
       <c r="D96">
-        <v>5.235786056747396</v>
+        <v>5.24024695636979</v>
       </c>
       <c r="E96">
-        <v>8.13884</v>
+        <v>8.225700000000002</v>
       </c>
       <c r="F96">
-        <v>8.16484</v>
+        <v>8.251700000000001</v>
       </c>
       <c r="G96">
         <v>3.84</v>
@@ -9284,28 +9284,28 @@
         <v>1.262</v>
       </c>
       <c r="M96">
-        <v>0.618894872</v>
+        <v>0.6254788600000002</v>
       </c>
       <c r="N96">
-        <v>0.643105128</v>
+        <v>0.6365211399999998</v>
       </c>
       <c r="O96">
-        <v>0.1929315384</v>
+        <v>0.1909563419999999</v>
       </c>
       <c r="P96">
-        <v>0.4501735896</v>
+        <v>0.4455647979999999</v>
       </c>
       <c r="Q96">
-        <v>0.5081735896</v>
+        <v>0.5035647979999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9068567363656946</v>
+        <v>1.074750807523352</v>
       </c>
       <c r="T96">
-        <v>6.0036686307731</v>
+        <v>7.174300397219112</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.03911852738699</v>
+        <v>2.017654121835548</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1041445403761675</v>
+        <v>0.1135436765703934</v>
       </c>
       <c r="C97">
-        <v>0.8285469563697898</v>
+        <v>0.4642770091677555</v>
       </c>
       <c r="D97">
-        <v>5.24024695636979</v>
+        <v>4.962837009167756</v>
       </c>
       <c r="E97">
-        <v>8.225700000000002</v>
+        <v>8.312560000000001</v>
       </c>
       <c r="F97">
-        <v>8.251700000000001</v>
+        <v>8.338560000000001</v>
       </c>
       <c r="G97">
         <v>3.84</v>
@@ -9366,45 +9366,45 @@
         <v>1.262</v>
       </c>
       <c r="M97">
-        <v>0.6254788600000002</v>
+        <v>0.7504704000000001</v>
       </c>
       <c r="N97">
-        <v>0.6365211399999998</v>
+        <v>0.5115295999999999</v>
       </c>
       <c r="O97">
-        <v>0.1909563419999999</v>
+        <v>0.15345888</v>
       </c>
       <c r="P97">
-        <v>0.4455647979999999</v>
+        <v>0.35807072</v>
       </c>
       <c r="Q97">
-        <v>0.5035647979999999</v>
+        <v>0.4160707199999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.074750807523352</v>
+        <v>1.326591914259837</v>
       </c>
       <c r="T97">
-        <v>7.174300397219112</v>
+        <v>8.93024804688813</v>
       </c>
       <c r="U97">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V97">
         <v>0.3</v>
       </c>
       <c r="W97">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.017654121835548</v>
+        <v>1.681611959645577</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1135436765703934</v>
+        <v>0.1134998127646192</v>
       </c>
       <c r="C98">
-        <v>0.4642770091677573</v>
+        <v>0.378643391714963</v>
       </c>
       <c r="D98">
-        <v>4.962837009167756</v>
+        <v>4.964063391714963</v>
       </c>
       <c r="E98">
-        <v>8.31256</v>
+        <v>8.399419999999999</v>
       </c>
       <c r="F98">
-        <v>8.338559999999999</v>
+        <v>8.425419999999999</v>
       </c>
       <c r="G98">
         <v>3.84</v>
@@ -9448,28 +9448,28 @@
         <v>1.262</v>
       </c>
       <c r="M98">
-        <v>0.7504703999999999</v>
+        <v>0.7582877999999998</v>
       </c>
       <c r="N98">
-        <v>0.5115296000000001</v>
+        <v>0.5037122000000002</v>
       </c>
       <c r="O98">
-        <v>0.15345888</v>
+        <v>0.15111366</v>
       </c>
       <c r="P98">
-        <v>0.3580707200000001</v>
+        <v>0.3525985400000001</v>
       </c>
       <c r="Q98">
-        <v>0.4160707200000001</v>
+        <v>0.4105985400000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.326591914259833</v>
+        <v>1.746327092153974</v>
       </c>
       <c r="T98">
-        <v>8.930248046888105</v>
+        <v>11.85682746300312</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.681611959645577</v>
+        <v>1.664275753876035</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1134998127646192</v>
+        <v>0.1134559489588451</v>
       </c>
       <c r="C99">
-        <v>0.378643391714963</v>
+        <v>0.2930103805226203</v>
       </c>
       <c r="D99">
-        <v>4.964063391714963</v>
+        <v>4.965290380522621</v>
       </c>
       <c r="E99">
-        <v>8.399419999999999</v>
+        <v>8.486280000000001</v>
       </c>
       <c r="F99">
-        <v>8.425419999999999</v>
+        <v>8.512280000000001</v>
       </c>
       <c r="G99">
         <v>3.84</v>
@@ -9530,28 +9530,28 @@
         <v>1.262</v>
       </c>
       <c r="M99">
-        <v>0.7582877999999998</v>
+        <v>0.7661052</v>
       </c>
       <c r="N99">
-        <v>0.5037122000000002</v>
+        <v>0.4958948</v>
       </c>
       <c r="O99">
-        <v>0.15111366</v>
+        <v>0.14876844</v>
       </c>
       <c r="P99">
-        <v>0.3525985400000001</v>
+        <v>0.34712636</v>
       </c>
       <c r="Q99">
-        <v>0.4105985400000001</v>
+        <v>0.40512636</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.746327092153974</v>
+        <v>2.585797447942253</v>
       </c>
       <c r="T99">
-        <v>11.85682746300312</v>
+        <v>17.70998629523315</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.664275753876035</v>
+        <v>1.647293348224239</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1134559489588451</v>
+        <v>0.113412085153071</v>
       </c>
       <c r="C100">
-        <v>0.2930103805226203</v>
+        <v>0.2073779760403998</v>
       </c>
       <c r="D100">
-        <v>4.965290380522621</v>
+        <v>4.966517976040399</v>
       </c>
       <c r="E100">
-        <v>8.486280000000001</v>
+        <v>8.57314</v>
       </c>
       <c r="F100">
-        <v>8.512280000000001</v>
+        <v>8.59914</v>
       </c>
       <c r="G100">
         <v>3.84</v>
@@ -9612,28 +9612,28 @@
         <v>1.262</v>
       </c>
       <c r="M100">
-        <v>0.7661052</v>
+        <v>0.7739226</v>
       </c>
       <c r="N100">
-        <v>0.4958948</v>
+        <v>0.4880774</v>
       </c>
       <c r="O100">
-        <v>0.14876844</v>
+        <v>0.14642322</v>
       </c>
       <c r="P100">
-        <v>0.34712636</v>
+        <v>0.34165418</v>
       </c>
       <c r="Q100">
-        <v>0.40512636</v>
+        <v>0.39965418</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.585797447942253</v>
+        <v>5.104208515307095</v>
       </c>
       <c r="T100">
-        <v>17.70998629523315</v>
+        <v>35.26946279192325</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.647293348224239</v>
+        <v>1.630654021474499</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.113412085153071</v>
-      </c>
-      <c r="C101">
-        <v>0.2073779760403998</v>
-      </c>
-      <c r="D101">
-        <v>4.966517976040399</v>
-      </c>
-      <c r="E101">
-        <v>8.57314</v>
-      </c>
-      <c r="F101">
-        <v>8.59914</v>
-      </c>
-      <c r="G101">
-        <v>3.84</v>
-      </c>
-      <c r="H101">
-        <v>8.66</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.32</v>
-      </c>
-      <c r="K101">
-        <v>0.058</v>
-      </c>
-      <c r="L101">
-        <v>1.262</v>
-      </c>
-      <c r="M101">
-        <v>0.7739226</v>
-      </c>
-      <c r="N101">
-        <v>0.4880774</v>
-      </c>
-      <c r="O101">
-        <v>0.14642322</v>
-      </c>
-      <c r="P101">
-        <v>0.34165418</v>
-      </c>
-      <c r="Q101">
-        <v>0.39965418</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.104208515307095</v>
-      </c>
-      <c r="T101">
-        <v>35.26946279192325</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.630654021474499</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
